--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P455"/>
+  <dimension ref="A1:P372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16107,7 +16107,7 @@
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>1000k上下文 [重要性:中|xAI 属于国外优秀关注公司，Grok 4.3 若为 Grok 系列新版本则值得关注，但当前信息缺少官方发布佐证。]</t>
+          <t>xAI旗舰模型；内置推理能力；1M上下文；原生视频输入；$1.25/$2.50 per M tokens；Agentic工具调用最优；Beta版4月17日上线 [重要性:高|xAI最新旗舰，超激进定价，内置推理+视频理解，Grok系列重要迭代]</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -19518,7 +19518,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>qwen-image-max-2025-12-30</t>
+          <t>qwen3-vl-plus-2025-12-19</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -19576,7 +19576,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>qwen-image-max</t>
+          <t>qwen3-tts-vd-realtime-2025-12-16</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -19634,7 +19634,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>z-image-turbo</t>
+          <t>qwen3-omni-flash-2025-12-01</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -19657,7 +19657,7 @@
       <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -19692,7 +19692,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>qwen3-vl-plus-2025-12-19</t>
+          <t>qwen3-omni-flash-realtime-2025-12-01</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -19750,7 +19750,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>qwen3-tts-vd-realtime-2025-12-16</t>
+          <t>qwen3-vl-flash</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -19773,7 +19773,7 @@
       <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -19808,7 +19808,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>qwen-image-edit-plus-2025-12-15</t>
+          <t>qwen3-vl-flash-2025-10-15</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -19866,7 +19866,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>qwen3-omni-flash-2025-12-01</t>
+          <t>qwen3-tts-flash</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -19889,7 +19889,7 @@
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>qwen3-omni-flash-realtime-2025-12-01</t>
+          <t>qwen3-tts-flash-realtime</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -19947,7 +19947,7 @@
       <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>qwen3-livetranslate-flash-2025-12-01</t>
+          <t>qwen3-omni-flash-realtime</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -20040,7 +20040,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>qwen3-livetranslate-flash</t>
+          <t>qwen-omni-turbo</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -20098,7 +20098,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>qwen-plus-2025-12-01</t>
+          <t>qwen-vl-max-latest</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -20156,7 +20156,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>qwen3-tts-vc-realtime-2025-11-27</t>
+          <t>qwen3-coder-flash</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -20179,7 +20179,7 @@
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -20214,7 +20214,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>qwen3-tts-flash-2025-11-27</t>
+          <t>qwen3-max-2025-09-23</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -20237,7 +20237,7 @@
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -20272,7 +20272,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>qwen3-tts-flash-realtime-2025-11-27</t>
+          <t>qwen3-vl-plus</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -20295,7 +20295,7 @@
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -20330,7 +20330,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>qwen-plus-2025-11-05</t>
+          <t>qwen3-vl-plus-2025-09-23</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -20388,14 +20388,14 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>qwen-mt-lite</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>阿里</t>
+          <t>深度求索</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J365" t="inlineStr"/>
@@ -20432,7 +20432,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -20446,7 +20446,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>qwen-vl-ocr-2025-11-20</t>
+          <t>qwen3-coder-plus</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -20469,7 +20469,7 @@
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -20504,7 +20504,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>qwen-mt-flash</t>
+          <t>qwen-turbo-0919</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -20548,7 +20548,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -20562,7 +20562,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>gui-plus</t>
+          <t>qwen-max-latest</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -20585,7 +20585,7 @@
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>qwen-image-edit-plus-2025-10-30</t>
+          <t>qwen2.5-math-1.5b-instruct</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -20637,10 +20637,14 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>1.5B</t>
+        </is>
+      </c>
       <c r="H369" t="inlineStr">
         <is>
           <t>基座</t>
@@ -20664,7 +20668,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -20678,7 +20682,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>qwen-image-edit-plus</t>
+          <t>qwen-turbo-latest</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -20722,7 +20726,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -20736,7 +20740,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>qwen-deep-search-planning</t>
+          <t>qwen-vl-max</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -20780,7 +20784,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -20794,7 +20798,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>qwen3-asr-flash-realtime-2025-10-27</t>
+          <t>qwen-max</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -20838,7 +20842,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -20848,4868 +20852,6 @@
       </c>
       <c r="O372" t="inlineStr"/>
       <c r="P372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>qwen3-asr-flash-realtime</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr"/>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O373" t="inlineStr"/>
-      <c r="P373" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>qwen3-vl-flash</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr"/>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr"/>
-      <c r="K374" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>qwen3-vl-flash-2025-10-15</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr"/>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O375" t="inlineStr"/>
-      <c r="P375" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>qwen3-tts-flash</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr"/>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>qwen3-tts-flash-2025-09-18</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O377" t="inlineStr"/>
-      <c r="P377" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>qwen3-tts-flash-realtime-2025-09-18</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr"/>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L378" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O378" t="inlineStr"/>
-      <c r="P378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>qwen3-tts-flash-realtime</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr"/>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O379" t="inlineStr"/>
-      <c r="P379" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>qwen3-omni-flash-realtime</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr"/>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O380" t="inlineStr"/>
-      <c r="P380" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>qwen3-omni-flash-2025-09-15</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr"/>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O381" t="inlineStr"/>
-      <c r="P381" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>qwen3-omni-flash-realtime-2025-09-15</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr"/>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="N382" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O382" t="inlineStr"/>
-      <c r="P382" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>qwen3-s2s-flash-realtime-2025-09-22</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr"/>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O383" t="inlineStr"/>
-      <c r="P383" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>qwen3-livetranslate-flash-realtime</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr"/>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O384" t="inlineStr"/>
-      <c r="P384" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>qwen3-livetranslate-flash-realtime-2025-09-22</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr"/>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O385" t="inlineStr"/>
-      <c r="P385" t="inlineStr"/>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>qwen-max-2025-01-25</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N386" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O386" t="inlineStr"/>
-      <c r="P386" t="inlineStr"/>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>qwen-turbo-2024-11-01</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr"/>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O387" t="inlineStr"/>
-      <c r="P387" t="inlineStr"/>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>qwen-plus-2025-01-25</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr"/>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N388" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O388" t="inlineStr"/>
-      <c r="P388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>qwq-plus-2025-03-05</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr"/>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="N389" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O389" t="inlineStr"/>
-      <c r="P389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>qwen2.5-vl-32b-instruct</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr"/>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>32B</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I390" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N390" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O390" t="inlineStr"/>
-      <c r="P390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>qvq-max</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr"/>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J391" t="inlineStr"/>
-      <c r="K391" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O391" t="inlineStr"/>
-      <c r="P391" t="inlineStr"/>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>qwen-omni-turbo</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr"/>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr"/>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I392" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J392" t="inlineStr"/>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="N392" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O392" t="inlineStr"/>
-      <c r="P392" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>qwen-turbo-2025-04-28</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr"/>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O393" t="inlineStr"/>
-      <c r="P393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>qwen-plus-2025-04-28</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr"/>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M394" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N394" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O394" t="inlineStr"/>
-      <c r="P394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>qwen-vl-max-2025-04-08</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr"/>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N395" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O395" t="inlineStr"/>
-      <c r="P395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>qwen-vl-plus-2025-01-25</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr"/>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N396" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O396" t="inlineStr"/>
-      <c r="P396" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>qwen-vl-plus-latest</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr"/>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="N397" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O397" t="inlineStr"/>
-      <c r="P397" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>qwen-vl-max-latest</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr"/>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="N398" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O398" t="inlineStr"/>
-      <c r="P398" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>qwen-vl-plus-2025-05-07</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr"/>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I399" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M399" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N399" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O399" t="inlineStr"/>
-      <c r="P399" t="inlineStr"/>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>qwen-turbo-2025-07-15</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr"/>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="N400" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O400" t="inlineStr"/>
-      <c r="P400" t="inlineStr"/>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>qwen3-coder-flash</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr"/>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="N401" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O401" t="inlineStr"/>
-      <c r="P401" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>qwen3-coder-plus-2025-09-23</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr"/>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O402" t="inlineStr"/>
-      <c r="P402" t="inlineStr"/>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>qwen3-max-2025-09-23</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr"/>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="N403" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O403" t="inlineStr"/>
-      <c r="P403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>qwen3-vl-plus</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr"/>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="N404" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O404" t="inlineStr"/>
-      <c r="P404" t="inlineStr"/>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>qwen3-vl-plus-2025-09-23</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr"/>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="N405" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O405" t="inlineStr"/>
-      <c r="P405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>qwen-plus-2025-09-11</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr"/>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I406" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="N406" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O406" t="inlineStr"/>
-      <c r="P406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr"/>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>深度求索</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O407" t="inlineStr"/>
-      <c r="P407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>qwen-vl-plus-2025-08-15</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr"/>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="N408" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O408" t="inlineStr"/>
-      <c r="P408" t="inlineStr"/>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>qwen3-coder-plus</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr"/>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I409" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="N409" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O409" t="inlineStr"/>
-      <c r="P409" t="inlineStr"/>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>qwen3-coder-plus-2025-07-22</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr"/>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr"/>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O410" t="inlineStr"/>
-      <c r="P410" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>qwen-plus-2025-07-14</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr"/>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr"/>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="N411" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O411" t="inlineStr"/>
-      <c r="P411" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr"/>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>480B(A35B)</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="N412" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O412" t="inlineStr"/>
-      <c r="P412" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>qwen-mt-turbo</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr"/>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr"/>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="N413" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O413" t="inlineStr"/>
-      <c r="P413" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>qwen-mt-plus</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr"/>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="N414" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O414" t="inlineStr"/>
-      <c r="P414" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>qwen-tts-2025-05-22</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="N415" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O415" t="inlineStr"/>
-      <c r="P415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>qvq-plus</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr"/>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N416" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O416" t="inlineStr"/>
-      <c r="P416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>qvq-plus-2025-05-15</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr"/>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N417" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O417" t="inlineStr"/>
-      <c r="P417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>qvq-max-2025-05-15</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr"/>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N418" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O418" t="inlineStr"/>
-      <c r="P418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>qwen-vl-max-2025-04-02</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr"/>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N419" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O419" t="inlineStr"/>
-      <c r="P419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>deepseek-r1-distill-llama-70b</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr"/>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>深度求索</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>70B</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="N420" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O420" t="inlineStr"/>
-      <c r="P420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>deepseek-r1-distill-qwen-32b</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>深度求索</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>32B</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I421" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N421" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O421" t="inlineStr"/>
-      <c r="P421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>deepseek-r1-distill-llama-8b</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>深度求索</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I422" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M422" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N422" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O422" t="inlineStr"/>
-      <c r="P422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>deepseek-r1-distill-qwen-1.5b</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>深度求索</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>1.5B</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I423" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M423" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N423" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O423" t="inlineStr"/>
-      <c r="P423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>qwen-vl-ocr-latest</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr"/>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="N424" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O424" t="inlineStr"/>
-      <c r="P424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>qwen-vl-ocr</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr"/>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M425" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N425" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O425" t="inlineStr"/>
-      <c r="P425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>qwen-coder-plus-1106</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr"/>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr"/>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N426" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O426" t="inlineStr"/>
-      <c r="P426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>qwen-coder-plus</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr"/>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I427" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N427" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O427" t="inlineStr"/>
-      <c r="P427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>qwen-coder-plus-latest</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N428" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O428" t="inlineStr"/>
-      <c r="P428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>qwen2.5-coder-14b-instruct</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>14B</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N429" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O429" t="inlineStr"/>
-      <c r="P429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>qwen2.5-coder-32b-instruct</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>32B</t>
-        </is>
-      </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J430" t="inlineStr"/>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M430" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="N430" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O430" t="inlineStr"/>
-      <c r="P430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>qwen-turbo-0919</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="N431" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O431" t="inlineStr"/>
-      <c r="P431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>qwen-max-latest</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr"/>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="N432" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O432" t="inlineStr"/>
-      <c r="P432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>qwen-math-turbo-0919</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr"/>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr"/>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N433" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O433" t="inlineStr"/>
-      <c r="P433" t="inlineStr"/>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>qwen-coder-turbo-latest</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr"/>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr"/>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr"/>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N434" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O434" t="inlineStr"/>
-      <c r="P434" t="inlineStr"/>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>qwen2.5-math-72b-instruct</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>72B</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J435" t="inlineStr"/>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N435" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O435" t="inlineStr"/>
-      <c r="P435" t="inlineStr"/>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>qwen-math-plus</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr"/>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr"/>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N436" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O436" t="inlineStr"/>
-      <c r="P436" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>qwen-max-0919</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr"/>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M437" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N437" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O437" t="inlineStr"/>
-      <c r="P437" t="inlineStr"/>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>qwen-math-turbo-latest</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr"/>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N438" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O438" t="inlineStr"/>
-      <c r="P438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>qwen-math-turbo</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr"/>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J439" t="inlineStr"/>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L439" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M439" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O439" t="inlineStr"/>
-      <c r="P439" t="inlineStr"/>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>qwen-math-plus-latest</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr"/>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M440" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N440" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O440" t="inlineStr"/>
-      <c r="P440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>qwen-math-plus-0919</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr"/>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O441" t="inlineStr"/>
-      <c r="P441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>qwen-coder-turbo-0919</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr"/>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O442" t="inlineStr"/>
-      <c r="P442" t="inlineStr"/>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>qwen-coder-turbo</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr"/>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N443" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O443" t="inlineStr"/>
-      <c r="P443" t="inlineStr"/>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>qwen2.5-math-7b-instruct</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr"/>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N444" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O444" t="inlineStr"/>
-      <c r="P444" t="inlineStr"/>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>qwen2.5-coder-7b-instruct</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr"/>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O445" t="inlineStr"/>
-      <c r="P445" t="inlineStr"/>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>qwen2.5-math-1.5b-instruct</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr"/>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>1.5B</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O446" t="inlineStr"/>
-      <c r="P446" t="inlineStr"/>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>qwen-turbo-latest</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr"/>
-      <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O447" t="inlineStr"/>
-      <c r="P447" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>qwen-plus-latest</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr"/>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="N448" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O448" t="inlineStr"/>
-      <c r="P448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>qwen-vl-max</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr"/>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="N449" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O449" t="inlineStr"/>
-      <c r="P449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>qwen-vl-plus</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr"/>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="N450" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O450" t="inlineStr"/>
-      <c r="P450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>qwen-max-0428</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr"/>
-      <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="N451" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O451" t="inlineStr"/>
-      <c r="P451" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>qwen-max-longcontext</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr"/>
-      <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="N452" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O452" t="inlineStr"/>
-      <c r="P452" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>qwen-max-1201</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr"/>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J453" t="inlineStr"/>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="N453" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O453" t="inlineStr"/>
-      <c r="P453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>qwen-max</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr"/>
-      <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="N454" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O454" t="inlineStr"/>
-      <c r="P454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>qwen-max-0107</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr"/>
-      <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J455" t="inlineStr"/>
-      <c r="K455" t="inlineStr">
-        <is>
-          <t>https://help.aliyun.com/zh/model-studio/models</t>
-        </is>
-      </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>DashScope 百炼平台</t>
-        </is>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="N455" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="O455" t="inlineStr"/>
-      <c r="P455" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,19 +506,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mimo-v2-tts</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,172 +529,176 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>基于自研Audio Tokenizer和多码本语音-文本联合建模架构；支持多粒度语音风格控制与单句内语气情感转折；支持多种方言及歌声合成</t>
+          <t>1048k上下文 [重要性:高|Google DeepMind 重点模型 Gemini 系列的重大版本更新子型号，具备较高行业关注度。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 官网→https://ai.google.dev/gemini-api/docs/models; 公司→Google DeepMind; 备注→多模态；Flash低延迟/高性价比子型号；约1M上下文; 问题: 官网字段为第三方排行榜 llm-stats.com，不是模型提供方官方页面; 模型发布时间为 2026-05-19，但当前信息来源为排行榜，建议核实 Google DeepMind / Google AI 官方公告; 公司名建议统一为 Google DeepMind; 模型名称包含具体系列、版本号与子型号，符合命名规范；未发现产品泛称问题，按 2026 年窗口内新模型保留。</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-13 11:52</t>
+          <t>2026-05-20 06:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mimo-v2.5-tts</t>
+          <t>Gemini 3.5 Pro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>multimodal large language model</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>采用“语言即控制”范式，支持自然语言指令控制语速、情绪与语气；包含标准版、VoiceDesign与VoiceClone三款模型，支持文本生成音色与高保真音色复刻；支持音频标签控制与分层导演剧本机制</t>
+          <t>Gemini 3.5系列中更强大的版本，具备更强推理与长程任务能力，当前处于内部测试阶段，后续将向更多用户分批发布。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:52</t>
-        </is>
-      </c>
+          <t>2026-05-20 06:02</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mimo-v2.5-tts-voiceclone</t>
+          <t>Gemini Omni</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>video generation &amp; multimodal world model</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://mimo.xiaomi.com</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>仅需数秒参考音频即可高保真复刻真人音色，无需训练或微调；完整保留原说话人音色身份及气息、节奏、习惯性停顿等个性化特征；支持叠加自然语言指令、音频标签及导演剧本级脚本实现高自由度语音创作</t>
+          <t>基于世界模型技术的新型视频生成模型，支持文本/图像/音频/视频混合输入，可对话式编辑视频（如修改角色、背景、风格），并支持自拍驱动内容生成。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:52</t>
-        </is>
-      </c>
+          <t>2026-05-20 06:02</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mimo-v2.5-tts-voicedesign</t>
+          <t>文心大模型5.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>百度</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -702,58 +706,54 @@
           <t>国内</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>支持通过自然语言描述生成全新音色；支持多维度（年龄、性别、口音、音质、性格气质等）精细控制；无需参考音频即可从零构建声音形象</t>
+          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:52</t>
-        </is>
-      </c>
+          <t>2026-05-20 06:02</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>claude-opus-4.7-fast</t>
+          <t>GPT-5.5 Instant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -761,109 +761,97 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://www.anthropic.com</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>支持3.75兆像素高分辨率图像输入；新增xhigh推理控制档位；引入任务预算机制优化智能体工作流；强化字面指令遵循能力</t>
+          <t>面向所有用户免费开放的轻量级GPT-5.5变体，主打简洁回答、强上下文记忆与快速响应，定位为高频日常交互主力模型。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:52</t>
-        </is>
-      </c>
+          <t>2026-05-20 06:02</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>perceptron-mk1</t>
+          <t>GLM-5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>智谱AI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>open-weight large language model</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>多模态模型；专注物理世界复杂动态处理；空间推理与视频理解能力强；API定价极低</t>
+          <t>744B参数开源大模型，于2026年2月发布，5月仍为当期全球开源模型性能标杆（Artificial Analysis榜单开源第一、综合第四），虽非5月19日首发，但在5月19日前后被密集报道并确认进入规模化商用部署阶段。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-XX</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:52</t>
-        </is>
-      </c>
+          <t>2026-05-20 06:02</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,352 +506,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>文心大模型5.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>百度</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
-        </is>
-      </c>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1048k上下文 [重要性:高|Google DeepMind 重点模型 Gemini 系列的重大版本更新子型号，具备较高行业关注度。]</t>
+          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-20 06:02</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 官网→https://ai.google.dev/gemini-api/docs/models; 公司→Google DeepMind; 备注→多模态；Flash低延迟/高性价比子型号；约1M上下文; 问题: 官网字段为第三方排行榜 llm-stats.com，不是模型提供方官方页面; 模型发布时间为 2026-05-19，但当前信息来源为排行榜，建议核实 Google DeepMind / Google AI 官方公告; 公司名建议统一为 Google DeepMind; 模型名称包含具体系列、版本号与子型号，符合命名规范；未发现产品泛称问题，按 2026 年窗口内新模型保留。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-20 06:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Pro</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Google/DeepMind</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>multimodal large language model</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Gemini 3.5系列中更强大的版本，具备更强推理与长程任务能力，当前处于内部测试阶段，后续将向更多用户分批发布。</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-05-20 06:02</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gemini Omni</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Google/DeepMind</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>video generation &amp; multimodal world model</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>基于世界模型技术的新型视频生成模型，支持文本/图像/音频/视频混合输入，可对话式编辑视频（如修改角色、背景、风格），并支持自拍驱动内容生成。</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-05-20 06:02</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>文心大模型5.1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>百度</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>large language model</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-05-20 06:02</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GPT-5.5 Instant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>large language model</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>面向所有用户免费开放的轻量级GPT-5.5变体，主打简洁回答、强上下文记忆与快速响应，定位为高频日常交互主力模型。</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-05-20 06:02</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GLM-5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>智谱AI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>open-weight large language model</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>744B参数开源大模型，于2026年2月发布，5月仍为当期全球开源模型性能标杆（Artificial Analysis榜单开源第一、综合第四），虽非5月19日首发，但在5月19日前后被密集报道并确认进入规模化商用部署阶段。</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-02-XX</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-05-20 06:02</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>2026-05-21 02:06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,10 +530,14 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://yiyan.baidu.com</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。</t>
+          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。 [重要性:中|百度属于国内优秀关注公司，文心大模型5.1若属官方版本更新则为值得关注的旗舰系列迭代。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,14 +557,179 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约12天，属于窗口前后1-2周内的新兴模型，应保留; 官网缺失，建议补充百度官方模型或文心/千帆官方页面; 尺寸/参数量缺失，且当前信息不足以可靠补全; 开闭源字段缺失，建议人工核实官方授权与开放方式; 现有发布时间与备注指向2026年新版本，但需以百度官方公告核实；不建议因采集时间早于窗口而删除。</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>非遗武术大模型 2.0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>上海体育大学武术学院、百度飞桨智慧体育技术创新中心、上海体刻动视技术有限公司</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>垂直领域多模态视频分析大模型</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>面向非遗武术领域的AI视频分析智能平台，支持数秒级动作细节诊断、知识问答交互与专业报告生成。</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:09</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-05-21 02:06</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PuduFM 1.0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>普渡机器人</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>具身智能大模型</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>首个面向服务机器人的物理认知大模型，具备3D空间深度感知、物理状态预测与持续进化能力。</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:09</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>烽火工业智能体</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>中石化</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>行业垂直智能体</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>石油化工行业首个数字专家智能体，可直接操作工业软件、分析实时生产数据并运行工艺仿真。</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:09</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约12天，属于窗口前后1-2周内的新兴模型，应保留; 官网缺失，建议补充百度官方模型或文心/千帆官方页面; 尺寸/参数量缺失，且当前信息不足以可靠补全; 开闭源字段缺失，建议人工核实官方授权与开放方式; 现有发布时间与备注指向2026年新版本，但需以百度官方公告核实；不建议因采集时间早于窗口而删除。</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约12天，属于窗口前后1-2周内的新兴模型，应保留; 官网缺失，建议补充百度官方模型或文心/千帆官方页面; 尺寸/参数量缺失，且当前信息不足以可靠补全; 开闭源字段缺失，建议人工核实官方授权与开放方式; 现有发布时间与备注指向2026年新版本，但需以百度官方公告核实；不建议因采集时间早于窗口而删除。; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 开闭源→闭源; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约2周内，按宽松规则应保留; 官网为百度官方产品页，但建议进一步核实是否存在更精确的文心大模型/千帆官方模型页; 尺寸/参数量缺失，当前信息不足以可靠补全; 现有信息指向2026年新版本，但由于该时间点超出我的可靠知识范围，建议以百度官方公告复核发布日期与技术指标。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -596,7 +596,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>面向非遗武术领域的AI视频分析智能平台，支持数秒级动作细节诊断、知识问答交互与专业报告生成。</t>
+          <t>面向非遗武术领域的AI视频分析智能平台，支持数秒级动作细节诊断、知识问答交互与专业报告生成。 [重要性:低|高校与产业合作的垂直领域模型，应用场景明确但行业通用影响力有限。]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→视频分析/多模态理解; 类型→垂直领域多模态模型; 备注→非遗武术领域；动作细节诊断；知识问答；专业报告生成；视频分析; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-21，位于追踪窗口内，应保留; 官网缺失，建议补充模型提供方或项目官方发布页面; 公司主体较多，建议在数据库中统一为牵头单位或以联合发布形式规范记录; 尺寸/参数量缺失，当前信息不足以可靠补全; 开闭源情况缺失，建议人工核实; 该模型更像领域平台/多模态分析系统，需核实是否有独立模型权重、API或正式产品版本。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -651,7 +651,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>首个面向服务机器人的物理认知大模型，具备3D空间深度感知、物理状态预测与持续进化能力。</t>
+          <t>首个面向服务机器人的物理认知大模型，具备3D空间深度感知、物理状态预测与持续进化能力。 [重要性:低|普渡机器人不在重点/优秀关注清单内，PuduFM 1.0属于具身智能垂直场景模型。]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→普渡机器人/Pudu Robotics; 国内外→国内; 任务类型→具身智能/机器人感知与规划; 类型→具身智能模型; 官网→https://www.pudurobotics.com; 备注→服务机器人；物理认知；3D空间感知；物理状态预测；持续学习; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-21，位于追踪窗口内，应保留; 原数据将普渡机器人标为国外不准确，普渡机器人为中国公司; 官网建议使用普渡机器人官方站点，若有PuduFM专页需进一步替换为模型专页; 尺寸/参数量缺失，当前信息不足以可靠补全; 开闭源情况缺失，建议人工核实; 具身智能方向值得观察，但当前信息不足以判断是否为通用基础模型还是面向自家机器人产品的内部能力。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -726,10 +726,670 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称未体现明确版本号/型号，不符合本次模型名称规范; 原数据将中石化标为国外不准确，中石化为中国企业; 发布时间为2026-05-21，若属正式发布则位于窗口内，但因命名不合规仍建议不录入为模型条目; 官网缺失，建议补充中国石化或项目官方发布页面; 该条目更像行业智能体/应用系统，不一定是独立模型; 开闭源情况缺失，建议人工核实</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gemini Omni</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>多模态世界模型</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>具备物理一致性理解能力的世界模型，支持文本→三维视频生成与对话式视频编辑，首次实现动能、重力等物理属性的可推理建模。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>大语言模型（推理优化）</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>主打高性价比与超低延迟的Gemini新版本，在编码、Agent工具调用和响应速度（达其他前沿模型4倍tok/s）上显著超越Gemini 3.1 Pro。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Max</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>通义千问旗舰新模型，Arena国产排名第一，支持35小时自主Agent内核运行，内核性能提升10倍，专为Agentic Cloud全栈调度优化。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>开源大语言模型</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Google最新开源轻量级模型，支持12GB显存下110 tok/s推理，强化数学与代码能力，与DeepSeek V4、Kimi K2.6等同期密集发布。</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DeepSeek V4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>开源大语言模型</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>深度求索新一代开源模型，聚焦长上下文与复杂推理，在多个开源基准测试中刷新SOTA，适配低成本边缘部署。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kimi K2.6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>月之暗面/Kimi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Kimi系列最新闭源升级版，强化多文档RAG与垂类知识融合能力，面向金融、法律等专业场景提供增强型智能体接口。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MiMo 2.5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>小米/MiMo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>多模态端侧模型</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>小米自研轻量化多模态模型，支持手机端实时图文理解+语音指令闭环，集成于Xiaomi HyperOS 2.5 Agent框架。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GLM-5.1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>智谱AI/GLM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>智谱GLM系列最新迭代，强化中文逻辑推理与安全对齐能力，原生支持GLM-Agent Runtime，已接入百炼平台。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>代码智能体</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布的编程专用智能体，支持--json工作流、本地IDE深度集成及自动单元测试生成，日均迭代更新。</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gemini Spark</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>个人智能体</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>可在云端虚拟机全天候自主运行的个人AI智能体，支持跨应用任务编排、长期记忆与主动提醒，为Gemini生态首个量产级Agent产品。</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Antigravity 2.0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>软件工程智能体平台</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>由93个子智能体协同构成的全自动代码生成平台，12小时内从零构建并测试完整操作系统，依托Gemini 3.5 Flash实现千美元级端到端成本。</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>锡望SeekWise大模型</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>无锡数字城市建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>垂类多模态智能体基座模型</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>全国首批通过信通院物联网智能体认证的AIoT大模型，聚焦钢材质检、锅炉优化、AGV接驳等实体产业场景，支持RAG+多智能体协同调度。</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>文心大模型5.1</t>
+          <t>Qwen 3.7-Max</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>百度</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,29 +525,25 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>large language model</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://yiyan.baidu.com</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>采用‘多维弹性预训练’技术，总参数压缩至前代约1/3、激活参数约1/2，预训练成本降至业界同规模模型约6%，聚焦效率与商业化落地。 [重要性:中|百度属于国内优秀关注公司，文心大模型5.1若属官方版本更新则为值得关注的旗舰系列迭代。]</t>
+          <t>通义千问旗舰新模型，Arena国产排名第一，支持35小时自主Agent内核运行，内核性能提升10倍，专为Agentic Cloud全栈调度优化。 [重要性:高|阿里/通义为国内重点关注公司，若为Max旗舰版本则属于重大模型更新。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-20 06:02</t>
+          <t>2026-05-23 01:58</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -557,38 +553,38 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约12天，属于窗口前后1-2周内的新兴模型，应保留; 官网缺失，建议补充百度官方模型或文心/千帆官方页面; 尺寸/参数量缺失，且当前信息不足以可靠补全; 开闭源字段缺失，建议人工核实官方授权与开放方式; 现有发布时间与备注指向2026年新版本，但需以百度官方公告核实；不建议因采集时间早于窗口而删除。; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 任务类型→通用对话; 类型→基座模型; 公司→百度/文心; 备注→多维弹性预训练；参数与激活参数压缩；预训练成本显著降低；效率与商业化落地优化; 开闭源→闭源; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-09，位于追踪窗口前约2周内，按宽松规则应保留; 官网为百度官方产品页，但建议进一步核实是否存在更精确的文心大模型/千帆官方模型页; 尺寸/参数量缺失，当前信息不足以可靠补全; 现有信息指向2026年新版本，但由于该时间点超出我的可靠知识范围，建议以百度官方公告复核发布日期与技术指标。</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 任务类型→通用对话; 官网→https://qwenlm.github.io; 备注→通义千问旗舰模型；Agentic能力；长程任务执行；面向云端智能体调度优化; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Qwen 3.7-Max”及其2026-05-20官方发布时间，建议人工复核官方公告; 原备注含有较多未经核实的榜单和性能表述，建议仅保留可官方验证的技术特征; 宽松保留；若无法找到阿里/通义官方发布页，应降级或删除。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-22 02:08</t>
+          <t>2026-05-24 02:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>非遗武术大模型 2.0</t>
+          <t>Gemma 4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>上海体育大学武术学院、百度飞桨智慧体育技术创新中心、上海体刻动视技术有限公司</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>垂直领域多模态视频分析大模型</t>
+          <t>开源大语言模型</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -596,17 +592,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>面向非遗武术领域的AI视频分析智能平台，支持数秒级动作细节诊断、知识问答交互与专业报告生成。 [重要性:低|高校与产业合作的垂直领域模型，应用场景明确但行业通用影响力有限。]</t>
+          <t>Google最新开源轻量级模型，支持12GB显存下110 tok/s推理，强化数学与代码能力，与DeepSeek V4、Kimi K2.6等同期密集发布。 [重要性:中|Gemma属于Google开放模型系列，重要性高于一般开源模型，但非Gemini旗舰线。]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-22 02:09</t>
+          <t>2026-05-23 01:58</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -616,52 +612,60 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→视频分析/多模态理解; 类型→垂直领域多模态模型; 备注→非遗武术领域；动作细节诊断；知识问答；专业报告生成；视频分析; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-21，位于追踪窗口内，应保留; 官网缺失，建议补充模型提供方或项目官方发布页面; 公司主体较多，建议在数据库中统一为牵头单位或以联合发布形式规范记录; 尺寸/参数量缺失，当前信息不足以可靠补全; 开闭源情况缺失，建议人工核实; 该模型更像领域平台/多模态分析系统，需核实是否有独立模型权重、API或正式产品版本。</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→通用对话/代码生成; 官网→https://ai.google.dev/gemma; 备注→开放权重模型；轻量级部署；面向开发者本地与云端推理; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Gemma 4”及其2026-05-22官方发布时间，建议人工复核Google DeepMind或Google AI官方公告; 原备注中的“12GB显存下110 tok/s”等性能指标缺少可核实来源; 宽松保留；如确认为2026年Google官方发布的新一代Gemma，可继续录入。</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PuduFM 1.0</t>
+          <t>DeepSeek V4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>普渡机器人</t>
+          <t>深度求索/DeepSeek</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>具身智能大模型</t>
+          <t>开源大语言模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.deepseek.com/</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>首个面向服务机器人的物理认知大模型，具备3D空间深度感知、物理状态预测与持续进化能力。 [重要性:低|普渡机器人不在重点/优秀关注清单内，PuduFM 1.0属于具身智能垂直场景模型。]</t>
+          <t>深度求索新一代开源模型，聚焦长上下文与复杂推理，在多个开源基准测试中刷新SOTA，适配低成本边缘部署。 [重要性:高|DeepSeek新一代主力模型若属实，属于行业广泛关注的重大版本更新。]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-22 02:09</t>
+          <t>2026-05-23 01:58</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -671,52 +675,60 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→普渡机器人/Pudu Robotics; 国内外→国内; 任务类型→具身智能/机器人感知与规划; 类型→具身智能模型; 官网→https://www.pudurobotics.com; 备注→服务机器人；物理认知；3D空间感知；物理状态预测；持续学习; 问题: 模型名称包含明确版本号，符合规范; 发布时间为2026-05-21，位于追踪窗口内，应保留; 原数据将普渡机器人标为国外不准确，普渡机器人为中国公司; 官网建议使用普渡机器人官方站点，若有PuduFM专页需进一步替换为模型专页; 尺寸/参数量缺失，当前信息不足以可靠补全; 开闭源情况缺失，建议人工核实; 具身智能方向值得观察，但当前信息不足以判断是否为通用基础模型还是面向自家机器人产品的内部能力。</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 模型发布时间→2026-04-24; 公司→DeepSeek/深度求索; 任务类型→通用对话/复杂推理/代码生成; 官网→https://api-docs.deepseek.com; 备注→通用大语言模型；复杂推理；长上下文；低成本推理; 问题: 模型名称包含版本号，形式上符合规范; 原始发布时间2026-05-22疑似不是官方发布日期，需以官方公告日为准; 原备注中的“多个开源基准刷新SOTA”“边缘部署”等表述需官方或权威评测来源支撑; 按官方发布日期应修正为2026-04-24；虽在窗口前约一个月，但仍为2026年近期重大模型，建议保留并标注窗口外。</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>烽火工业智能体</t>
+          <t>MiMo 2.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>小米/MiMo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>行业垂直智能体</t>
+          <t>多模态端侧模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://mimo.xiaomi.com</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>石油化工行业首个数字专家智能体，可直接操作工业软件、分析实时生产数据并运行工艺仿真。</t>
+          <t>小米自研轻量化多模态模型，支持手机端实时图文理解+语音指令闭环，集成于Xiaomi HyperOS 2.5 Agent框架。 [重要性:中|小米/MiMo属于国内优秀关注公司，端侧多模态模型具备特定场景价值。]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-22 02:09</t>
+          <t>2026-05-23 01:58</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -726,22 +738,26 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称未体现明确版本号/型号，不符合本次模型名称规范; 原数据将中石化标为国外不准确，中石化为中国企业; 发布时间为2026-05-21，若属正式发布则位于窗口内，但因命名不合规仍建议不录入为模型条目; 官网缺失，建议补充中国石化或项目官方发布页面; 该条目更像行业智能体/应用系统，不一定是独立模型; 开闭源情况缺失，建议人工核实</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→小米/MiMo; 任务类型→端侧多模态/图文理解/语音交互; 备注→端侧多模态模型；移动设备部署；图文理解；语音指令交互; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“MiMo 2.5”及其2026-05-22官方发布时间，建议人工复核小米官方技术公告; 原备注中“HyperOS 2.5 Agent框架”等产品集成信息需确认是否为模型自身特征; 宽松保留；若仅为系统功能或Agent框架而非模型版本，应调整分类。</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini Omni</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -753,20 +769,24 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>多模态世界模型</t>
+          <t>代码智能体</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/claude-code/overview</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>具备物理一致性理解能力的世界模型，支持文本→三维视频生成与对话式视频编辑，首次实现动能、重力等物理属性的可推理建模。</t>
+          <t>Anthropic正式发布的编程专用智能体，支持--json工作流、本地IDE深度集成及自动单元测试生成，日均迭代更新。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -781,15 +801,19 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 不是具体模型名称，属于Anthropic的代码智能体产品/工具; 发布时间应为2025年相关发布/GA时间，属于旧产品（发布于2025年）; 原始模型发布时间2026-05-22疑似错误</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini Spark</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -808,7 +832,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型（推理优化）</t>
+          <t>个人智能体</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -816,7 +840,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>主打高性价比与超低延迟的Gemini新版本，在编码、Agent工具调用和响应速度（达其他前沿模型4倍tok/s）上显著超越Gemini 3.1 Pro。</t>
+          <t>可在云端虚拟机全天候自主运行的个人AI智能体，支持跨应用任务编排、长期记忆与主动提醒，为Gemini生态首个量产级Agent产品。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,34 +860,38 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：产品泛称无版本号; 缺少明确版本号/型号，不符合“具体模型/产品名称 + 版本号/型号”的命名要求; 更像个人智能体产品而非具体模型; 截至已知公开资料无法核实“Gemini Spark”及其2026-05-21官方发布时间</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Qwen 3.7-Max</t>
+          <t>Antigravity 2.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>软件工程智能体平台</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -871,12 +899,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>通义千问旗舰新模型，Arena国产排名第一，支持35小时自主Agent内核运行，内核性能提升10倍，专为Agentic Cloud全栈调度优化。</t>
+          <t>由93个子智能体协同构成的全自动代码生成平台，12小时内从零构建并测试完整操作系统，依托Gemini 3.5 Flash实现千美元级端到端成本。 [重要性:中|Google DeepMind相关软件工程智能体平台值得关注，但不是Gemini旗舰模型本身。]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -891,22 +919,26 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→软件工程智能体/代码生成; 类型→软件工程智能体平台; 备注→软件工程智能体平台；多智能体协作；代码生成；自动测试；端到端软件构建; 问题: 名称包含版本号，形式上符合规范; 该条目更像智能体平台/开发工具，而非具体基础模型; 截至已知公开资料无法核实“Antigravity 2.0”及其2026-05-21官方发布时间; 原备注中“93个子智能体”“12小时构建完整操作系统”“千美元级成本”等表述高度具体但缺少可核实来源; 宽松保留为智能体平台条目；若数据库只收录模型，应改为记录其实际底座模型，例如Gemini的具体版本。</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gemma 4</t>
+          <t>锡望SeekWise大模型</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>无锡数字城市建设发展有限公司</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -918,20 +950,24 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>开源大语言模型</t>
+          <t>垂类多模态智能体基座模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://seekvision.cn</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Google最新开源轻量级模型，支持12GB显存下110 tok/s推理，强化数学与代码能力，与DeepSeek V4、Kimi K2.6等同期密集发布。</t>
+          <t>全国首批通过信通院物联网智能体认证的AIoT大模型，聚焦钢材质检、锅炉优化、AGV接驳等实体产业场景，支持RAG+多智能体协同调度。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -946,22 +982,26 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：缺少版本号/型号; 名称不是“具体模型/产品名称 + 版本号/型号”的规范形式; 国内外字段错误：无锡数字城市建设发展有限公司为中国公司，应标注为国内; “垂类多模态智能体基座模型”分类表述混杂，建议改为行业模型或工业AIoT智能体; 截至已知公开资料无法核实其2026-05-21官方发布时间</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DeepSeek V4</t>
+          <t>GLM-5.1-HighSpeed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>深度求索/DeepSeek</t>
+          <t>智谱AI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -973,7 +1013,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>开源大语言模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -981,17 +1021,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>深度求索新一代开源模型，聚焦长上下文与复杂推理，在多个开源基准测试中刷新SOTA，适配低成本边缘部署。</t>
+          <t>官方称推理速度达400 tokens/s，面向高吞吐低延迟场景优化的GLM系列新版本</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-24 02:07</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1009,26 +1049,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>BitCPM-CANN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>月之暗面/Kimi</t>
+          <t>OpenBMB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>大语言模型（昇腾原生）</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1036,17 +1076,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kimi系列最新闭源升级版，强化多文档RAG与垂类知识融合能力，面向金融、法律等专业场景提供增强型智能体接口。</t>
+          <t>基于华为昇腾910B芯片全栈原生训练的开源大模型，适配CANN生态，强调国产算力高效部署</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-24 02:07</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1064,14 +1104,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MiMo 2.5</t>
+          <t>Confucius4-TTS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>小米/MiMo</t>
+          <t>网易有道</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1083,7 +1123,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>多模态端侧模型</t>
+          <t>语音合成模型</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1091,17 +1131,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>小米自研轻量化多模态模型，支持手机端实时图文理解+语音指令闭环，集成于Xiaomi HyperOS 2.5 Agent框架。</t>
+          <t>支持14种语言零样本语音克隆的TTS引擎，即将全量开源</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-24 02:07</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1119,26 +1159,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>AlphaProof Nexus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>智谱AI/GLM</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>数学推理与形式化证明框架</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1146,17 +1186,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>智谱GLM系列最新迭代，强化中文逻辑推理与安全对齐能力，原生支持GLM-Agent Runtime，已接入百炼平台。</t>
+          <t>首个端到端可验证数学证明生成系统，集成强化学习驱动的搜索与Coq/Galaxy形式化验证闭环</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-24 02:07</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1174,7 +1214,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mythos Preview</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1193,7 +1233,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>代码智能体</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1201,7 +1241,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Anthropic正式发布的编程专用智能体，支持--json工作流、本地IDE深度集成及自动单元测试生成，日均迭代更新。</t>
+          <t>Anthropic发布的‘史上最强’预览版大模型，因安全评估风险被宣布无限期封印，仅限Glasswing漏洞挖掘计划内部使用</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1211,7 +1251,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-24 02:07</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1225,171 +1265,6 @@
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gemini Spark</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Google/DeepMind</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>个人智能体</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>可在云端虚拟机全天候自主运行的个人AI智能体，支持跨应用任务编排、长期记忆与主动提醒，为Gemini生态首个量产级Agent产品。</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-05-23 01:58</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Antigravity 2.0</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Google/DeepMind</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>软件工程智能体平台</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>由93个子智能体协同构成的全自动代码生成平台，12小时内从零构建并测试完整操作系统，依托Gemini 3.5 Flash实现千美元级端到端成本。</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-05-23 01:58</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>锡望SeekWise大模型</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>无锡数字城市建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>垂类多模态智能体基座模型</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>全国首批通过信通院物联网智能体认证的AIoT大模型，聚焦钢材质检、锅炉优化、AGV接驳等实体产业场景，支持RAG+多智能体协同调度。</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-05-23 01:58</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,73 +506,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qwen 3.7-Max</t>
+          <t>gamma-world-test</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gamma-world-test</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>通义千问旗舰新模型，Arena国产排名第一，支持35小时自主Agent内核运行，内核性能提升10倍，专为Agentic Cloud全栈调度优化。 [重要性:高|阿里/通义为国内重点关注公司，若为Max旗舰版本则属于重大模型更新。]</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 任务类型→通用对话; 官网→https://qwenlm.github.io; 备注→通义千问旗舰模型；Agentic能力；长程任务执行；面向云端智能体调度优化; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Qwen 3.7-Max”及其2026-05-20官方发布时间，建议人工复核官方公告; 原备注含有较多未经核实的榜单和性能表述，建议仅保留可官方验证的技术特征; 宽松保留；若无法找到阿里/通义官方发布页，应降级或删除。</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gamma-world-test)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-24 02:04</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemma 4</t>
+          <t>Fun-ASR-Nano-2512-hf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>阿里</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,92 +588,96 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>开源大语言模型</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/FunAudioLLM/Fun-ASR-Nano-2512-hf</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Google最新开源轻量级模型，支持12GB显存下110 tok/s推理，强化数学与代码能力，与DeepSeek V4、Kimi K2.6等同期密集发布。 [重要性:中|Gemma属于Google开放模型系列，重要性高于一般开源模型，但非Gemini旗舰线。]</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→通用对话/代码生成; 官网→https://ai.google.dev/gemma; 备注→开放权重模型；轻量级部署；面向开发者本地与云端推理; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Gemma 4”及其2026-05-22官方发布时间，建议人工复核Google DeepMind或Google AI官方公告; 原备注中的“12GB显存下110 tok/s”等性能指标缺少可核实来源; 宽松保留；如确认为2026年Google官方发布的新一代Gemma，可继续录入。</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Fun-ASR-Nano-2512-hf)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-24 02:04</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DeepSeek V4</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>深度求索/DeepSeek</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>开源大语言模型</t>
+          <t>multimodal large language model</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://www.deepseek.com/</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>深度求索新一代开源模型，聚焦长上下文与复杂推理，在多个开源基准测试中刷新SOTA，适配低成本边缘部署。 [重要性:高|DeepSeek新一代主力模型若属实，属于行业广泛关注的重大版本更新。]</t>
+          <t>Google I/O 2026 发布的轻量级高性能模型，主打极低延迟、高吞吐（每秒Token数为前沿模型4倍）与强Agent工具调用能力，当日上线可用。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -675,60 +687,52 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 模型发布时间→2026-04-24; 公司→DeepSeek/深度求索; 任务类型→通用对话/复杂推理/代码生成; 官网→https://api-docs.deepseek.com; 备注→通用大语言模型；复杂推理；长上下文；低成本推理; 问题: 模型名称包含版本号，形式上符合规范; 原始发布时间2026-05-22疑似不是官方发布日期，需以官方公告日为准; 原备注中的“多个开源基准刷新SOTA”“边缘部署”等表述需官方或权威评测来源支撑; 按官方发布日期应修正为2026-04-24；虽在窗口前约一个月，但仍为2026年近期重大模型，建议保留并标注窗口外。</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MiMo 2.5</t>
+          <t>Gemini Omni</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>小米/MiMo</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>多模态端侧模型</t>
+          <t>world model / physics-aware multimodal model</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://mimo.xiaomi.com</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>小米自研轻量化多模态模型，支持手机端实时图文理解+语音指令闭环，集成于Xiaomi HyperOS 2.5 Agent框架。 [重要性:中|小米/MiMo属于国内优秀关注公司，端侧多模态模型具备特定场景价值。]</t>
+          <t>具备物理一致性理解能力的世界模型，支持跨文本-视频的三维空间建模、动能/重力模拟及对话式视频元素编辑。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -738,60 +742,52 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→小米/MiMo; 任务类型→端侧多模态/图文理解/语音交互; 备注→端侧多模态模型；移动设备部署；图文理解；语音指令交互; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“MiMo 2.5”及其2026-05-22官方发布时间，建议人工复核小米官方技术公告; 原备注中“HyperOS 2.5 Agent框架”等产品集成信息需确认是否为模型自身特征; 宽松保留；若仅为系统功能或Agent框架而非模型版本，应调整分类。</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>文心大模型5.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>百度</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>代码智能体</t>
+          <t>large language model</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://docs.anthropic.com/en/docs/claude-code/overview</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Anthropic正式发布的编程专用智能体，支持--json工作流、本地IDE深度集成及自动单元测试生成，日均迭代更新。</t>
+          <t>采用‘多维弹性预训练’技术，预训练成本降至同规模模型约6%，总参数压缩至1/3，激活参数压缩至1/2，聚焦长程智能体与效率优化。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,26 +797,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 不是具体模型名称，属于Anthropic的代码智能体产品/工具; 发布时间应为2025年相关发布/GA时间，属于旧产品（发布于2025年）; 原始模型发布时间2026-05-22疑似错误</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gemini Spark</t>
+          <t>GPT-5.5 Instant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -832,7 +824,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>个人智能体</t>
+          <t>large language model</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -840,17 +832,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>可在云端虚拟机全天候自主运行的个人AI智能体，支持跨应用任务编排、长期记忆与主动提醒，为Gemini生态首个量产级Agent产品。</t>
+          <t>面向全体用户免费开放的轻量化GPT-5迭代版，强调简洁响应、增强长期记忆能力与低开销推理，标志OpenAI向价值验证与普惠部署转向。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -860,26 +852,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：产品泛称无版本号; 缺少明确版本号/型号，不符合“具体模型/产品名称 + 版本号/型号”的命名要求; 更像个人智能体产品而非具体模型; 截至已知公开资料无法核实“Gemini Spark”及其2026-05-21官方发布时间</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity 2.0</t>
+          <t>Claude Opus 4.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -891,7 +879,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>软件工程智能体平台</t>
+          <t>large language model</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -899,17 +887,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>由93个子智能体协同构成的全自动代码生成平台，12小时内从零构建并测试完整操作系统，依托Gemini 3.5 Flash实现千美元级端到端成本。 [重要性:中|Google DeepMind相关软件工程智能体平台值得关注，但不是Gemini旗舰模型本身。]</t>
+          <t>虽发布于4月，但其争议性表现（幻觉加剧、任务偷懒）在5月24日前持续发酵并被主流媒体集中报道，被行业视为‘倒退型更新’典型，故纳入5月关键模型事件。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-XX</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -919,26 +907,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→软件工程智能体/代码生成; 类型→软件工程智能体平台; 备注→软件工程智能体平台；多智能体协作；代码生成；自动测试；端到端软件构建; 问题: 名称包含版本号，形式上符合规范; 该条目更像智能体平台/开发工具，而非具体基础模型; 截至已知公开资料无法核实“Antigravity 2.0”及其2026-05-21官方发布时间; 原备注中“93个子智能体”“12小时构建完整操作系统”“千美元级成本”等表述高度具体但缺少可核实来源; 宽松保留为智能体平台条目；若数据库只收录模型，应改为记录其实际底座模型，例如Gemini的具体版本。</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>锡望SeekWise大模型</t>
+          <t>Antigravity 2.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>无锡数字城市建设发展有限公司</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -950,29 +934,25 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>垂类多模态智能体基座模型</t>
+          <t>autonomous agent platform</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://seekvision.cn</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>全国首批通过信通院物联网智能体认证的AIoT大模型，聚焦钢材质检、锅炉优化、AGV接驳等实体产业场景，支持RAG+多智能体协同调度。</t>
+          <t>基于多智能体协同的全自动代码生成平台，支持93个子智能体并行工作，12小时内从零构建含调度、内存管理、文件系统的完整操作系统。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-23 01:58</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -982,38 +962,34 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：缺少版本号/型号; 名称不是“具体模型/产品名称 + 版本号/型号”的规范形式; 国内外字段错误：无锡数字城市建设发展有限公司为中国公司，应标注为国内; “垂类多模态智能体基座模型”分类表述混杂，建议改为行业模型或工业AIoT智能体; 截至已知公开资料无法核实其2026-05-21官方发布时间</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:04</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GLM-5.1-HighSpeed</t>
+          <t>Gemini Spark</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>智谱AI</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>personal autonomous agent</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1021,17 +997,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>官方称推理速度达400 tokens/s，面向高吞吐低延迟场景优化的GLM系列新版本</t>
+          <t>首个可在云端虚拟机中全天候自主运行的个人智能体，专为软件工程自动化设计，支持长期状态维持与跨会话任务延续。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-24 02:07</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1049,26 +1025,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BitCPM-CANN</t>
+          <t>昇腾AgentInfra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OpenBMB</t>
+          <t>华为</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>大语言模型（昇腾原生）</t>
+          <t>agent runtime infrastructure</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1076,17 +1052,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>基于华为昇腾910B芯片全栈原生训练的开源大模型，适配CANN生态，强调国产算力高效部署</t>
+          <t>华为鲲鹏昇腾开发者大会上发布的智能体原生运行环境，作为‘鲲鹏硬核算力 + openEuler异构系统 + AgentInfra’三层架构核心组件全面开源。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-24 02:07</t>
+          <t>2026-05-25 02:13</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1100,171 +1076,6 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Confucius4-TTS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>网易有道</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>语音合成模型</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>支持14种语言零样本语音克隆的TTS引擎，即将全量开源</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:07</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AlphaProof Nexus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Google DeepMind</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>数学推理与形式化证明框架</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>首个端到端可验证数学证明生成系统，集成强化学习驱动的搜索与Coq/Galaxy形式化验证闭环</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:07</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mythos Preview</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Anthropic发布的‘史上最强’预览版大模型，因安全评估风险被宣布无限期封印，仅限Glasswing漏洞挖掘计划内部使用</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-05-24 02:07</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,61 +506,435 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>昇腾AgentInfra</t>
+          <t>vermeer-XL-CA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>agent runtime infrastructure</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-XL-CA</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>华为鲲鹏昇腾开发者大会上发布的智能体原生运行环境，作为‘鲲鹏硬核算力 + openEuler异构系统 + AgentInfra’三层架构核心组件全面开源。</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-25 02:13</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL-CA)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vermeer-XL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-XL</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vermeer-L-AP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-L-AP</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L-AP)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vermeer-L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-L</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SpaceXAI (xAI)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 非具体模型条目：昇腾AgentInfra更像智能体运行环境/基础设施组件，不属于模型名称; 模型名称缺少明确版本号或型号; 类型分类不应归为模型，应归为智能体基础设施/运行时</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-05-26 02:03</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MiniCPM5-1B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OpenBMB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>小规模混合推理大语言模型</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10.8亿参数开源模型，登顶Artificial Analysis小模型榜单（17.9分），支持INT4量化（约0.5GB），可在手机、浏览器及CPU本地运行。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash (Low)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Google / DeepMind</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>轻量级多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Antigravity平台新增的低延迟、低成本推理变体，面向高并发轻负载场景优化，为Gemini 3.5系列首次推出的‘Flash’分级型号。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vermeer-XL-CA</t>
+          <t>Grok V9-Medium</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>SpaceXAI (xAI)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,31 +521,19 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/microsoft/vermeer-XL-CA</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。 [重要性:中|xAI 属于国外优秀关注公司，若该模型属实则为 Grok 系列较重要的新版本/子变体。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -555,32 +543,36 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL-CA)</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→xAI; 官网→https://docs.x.ai/docs/models; 任务类型→通用对话/代码生成; 问题: 公司名不规范：'SpaceXAI (xAI)' 应统一为 'xAI'，xAI 与 SpaceX 是不同主体; 模型名称形式上符合规范：包含具体产品名与版本/型号，不属于产品泛称; 模型存在性与官方发布时间需人工核实：截至可确认信息范围内，未能确认 xAI 官方发布过 'Grok V9-Medium'; 当前备注包含较多预测性/传闻信息，如'进入微调阶段'、'预计2–3周内公开发布'、'年底将开源0.5T版本'，建议核验官方来源后再录入; 模型发布时间 2026-05-26 与追踪窗口相近，但需确认是否为 xAI 官方发布日期，而非传闻日期或采集日期; 不建议因无法核实而直接删除；按规则仅产品泛称或2025年及以前旧模型应删除。建议后续以 xAI 官网、官方博客或官方 X 账号公告为准复核。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-27 02:12</t>
+          <t>2026-05-28 01:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vermeer-XL</t>
+          <t>Assemble_Trocar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -607,7 +599,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/vermeer-XL</t>
+          <t>https://huggingface.co/nvidia/Assemble_Trocar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -617,37 +609,37 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Assemble_Trocar)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-27 02:12</t>
+          <t>2026-05-28 01:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vermeer-L-AP</t>
+          <t>GPT-5.6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -655,66 +647,54 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/microsoft/vermeer-L-AP</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L-AP)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-05-27 02:12</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vermeer-L</t>
+          <t>Claude Mythos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,66 +702,54 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>大语言模型（安全增强型）</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/microsoft/vermeer-L</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-05-27 02:12</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grok V9-Medium</t>
+          <t>Gemini for Science</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SpaceXAI (xAI)</t>
+          <t>Google DeepMind / Google Research</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -793,7 +761,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>多模态科学大模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -801,17 +769,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。</t>
+          <t>面向生命科学与实验推理的专用Gemini变体，集成Science Skills工具链，支持假设生成、实验设计与论文级文献推理</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-27 02:12</t>
+          <t>2026-05-28 01:56</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -829,14 +797,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MiniCPM5-1B</t>
+          <t>Protenix-v2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OpenBMB</t>
+          <t>未知（据信为中美联合生物AI初创团队）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,7 +816,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>小规模混合推理大语言模型</t>
+          <t>蛋白质结构与功能预测模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -856,17 +824,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10.8亿参数开源模型，登顶Artificial Analysis小模型榜单（17.9分），支持INT4量化（约0.5GB），可在手机、浏览器及CPU本地运行。</t>
+          <t>开源蛋白质语言模型v2版本，支持端到端突变效应预测与条件性折叠生成，在CAMEO基准上刷新SOTA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-27 02:12</t>
+          <t>2026-05-28 01:56</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -884,14 +852,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash (Low)</t>
+          <t>WholebodyVLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Google / DeepMind</t>
+          <t>Google Research</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -903,7 +871,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>轻量级多模态大语言模型</t>
+          <t>具身多模态智能体（VLA）</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -911,30 +879,85 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Antigravity平台新增的低延迟、低成本推理变体，面向高并发轻负载场景优化，为Gemini 3.5系列首次推出的‘Flash’分级型号。</t>
+          <t>首个覆盖全身运动控制（含手指微操、步态平衡、双臂协同）的视觉-语言-动作联合模型，专为通用机器人任务设计</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI决策机器人R1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NBBOSS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>商业决策智能体</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>首款面向企业高管的可分离式AI决策智能体，融合实时BI数据接入、因果推断引擎与会议纪要自动生成模块</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-05-27 02:12</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Grok V9-Medium</t>
+          <t>GPT-5.6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SpaceXAI (xAI)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,17 +533,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。 [重要性:中|xAI 属于国外优秀关注公司，若该模型属实则为 Grok 系列较重要的新版本/子变体。]</t>
+          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布 [重要性:高|OpenAI 的 GPT 主线模型若属实将是旗舰级重大版本更新。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-27 02:12</t>
+          <t>2026-05-28 01:56</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -553,26 +553,26 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→xAI; 官网→https://docs.x.ai/docs/models; 任务类型→通用对话/代码生成; 问题: 公司名不规范：'SpaceXAI (xAI)' 应统一为 'xAI'，xAI 与 SpaceX 是不同主体; 模型名称形式上符合规范：包含具体产品名与版本/型号，不属于产品泛称; 模型存在性与官方发布时间需人工核实：截至可确认信息范围内，未能确认 xAI 官方发布过 'Grok V9-Medium'; 当前备注包含较多预测性/传闻信息，如'进入微调阶段'、'预计2–3周内公开发布'、'年底将开源0.5T版本'，建议核验官方来源后再录入; 模型发布时间 2026-05-26 与追踪窗口相近，但需确认是否为 xAI 官方发布日期，而非传闻日期或采集日期; 不建议因无法核实而直接删除；按规则仅产品泛称或2025年及以前旧模型应删除。建议后续以 xAI 官网、官方博客或官方 X 账号公告为准复核。</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://platform.openai.com/docs/models; 任务类型→通用对话; 开闭源→闭源; 问题: 未能确认 OpenAI 官方发布过 GPT-5.6; 现有发布时间疑似来自泄露或传闻，不应视为官方发布日期; 备注包含预测和泄露信息，建议人工核验后再录入; 模型名称包含明确版本号，形式上符合规范；但发布真实性和官方发布日期需重点复核。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:55</t>
+          <t>2026-05-29 02:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Assemble_Trocar</t>
+          <t>Claude Mythos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,31 +580,19 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>大语言模型（安全增强型）</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/Assemble_Trocar</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -614,32 +602,36 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Assemble_Trocar)</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称像系列名或代号，未指向具体模型版本; 未能确认 Anthropic 官方发布过 Claude Mythos; 备注中关于央行和 SWIFT 漏洞暴露的描述高度异常，需严格核验来源; 现有发布时间缺乏官方依据</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:55</t>
+          <t>2026-05-29 02:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GPT-5.6</t>
+          <t>Claude Opus 4.8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -647,66 +639,86 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-8</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布</t>
+          <t>1000k上下文；顶级推理能力；顶级编码能力；高端定价 [重要性:高|Anthropic Claude Opus 主线高端模型若属实属于旗舰级重大版本更新。]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://docs.anthropic.com/en/docs/about-claude/models/overview; 公司→Anthropic; 开闭源→闭源; 问题: 官网字段为第三方排行榜链接，不是 Anthropic 官方页面; 未能确认 Anthropic 官方发布过 Claude Opus 4.8; 模型发布时间需以 Anthropic 官方公告或官方模型文档为准; llm-stats.com 排行榜不应作为官方发布依据; 模型名称包含系列、档位和版本号，形式上符合规范；但该条目的发布时间、上下文长度和能力描述均需官方核验。</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Mythos</t>
+          <t>Qwen3.7-Max</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>大语言模型（安全增强型）</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -714,17 +726,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
+          <t>阿里云于2026年5月20日阿里云峰会发布的面向AI Agent场景设计的新旗舰模型，在编程、推理、工具调用等能力上显著强化，支持长时间运行与多次工具调用，在Code Arena榜单中得分1541。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29 02:04</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -742,26 +754,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini for Science</t>
+          <t>DeepSeek-V4 Flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Google DeepMind / Google Research</t>
+          <t>深度求索/DeepSeek</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>多模态科学大模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -769,17 +781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>面向生命科学与实验推理的专用Gemini变体，集成Science Skills工具链，支持假设生成、实验设计与论文级文献推理</t>
+          <t>DeepSeek于2026年5月28日最新发布的高性价比推理优化版本，提供$0.14/M token定价及每日200万Token免费额度，主打高并发、低成本商用场景。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29 02:04</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -797,26 +809,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Protenix-v2</t>
+          <t>豆包Seed 2.0 Pro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>未知（据信为中美联合生物AI初创团队）</t>
+          <t>字节跳动/豆包</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋白质结构与功能预测模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -824,17 +836,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>开源蛋白质语言模型v2版本，支持端到端突变效应预测与条件性折叠生成，在CAMEO基准上刷新SOTA</t>
+          <t>豆包于2026年5月28日前后正式发布升级版Seed 2.0 Pro，综合性能跻身全球前五，以$1/M token超低价格和MMMU-Pro 68.7%精度成为国产综合能力最强的商用大模型之一。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29 02:04</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -852,14 +864,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WholebodyVLA</t>
+          <t>HappyHorse 1.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>HappyHorse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -871,7 +883,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>具身多模态智能体（VLA）</t>
+          <t>视频生成模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -879,17 +891,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>首个覆盖全身运动控制（含手指微操、步态平衡、双臂协同）的视觉-语言-动作联合模型，专为通用机器人任务设计</t>
+          <t>2026年5月28日官宣发布的首个专注高质量长时序视频生成的多模态基础模型，被列为2026年5月AI模型排行榜‘视频生成’唯一代表，以SOTA视频质量定位内容创作者市场。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29 02:04</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -907,14 +919,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI决策机器人R1</t>
+          <t>Meta One Plus / Meta One Premium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NBBOSS</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -926,7 +938,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>商业决策智能体</t>
+          <t>AI智能体（聊天机器人服务）</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -934,30 +946,195 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>首款面向企业高管的可分离式AI决策智能体，融合实时BI数据接入、因果推断引擎与会议纪要自动生成模块</t>
+          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MuleRun</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AI智能体框架</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-05-28 01:56</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Qoder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>智能体编程平台</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>稀宇极智MoE大模型（未公开命名）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>上海稀宇极智科技有限公司</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>混合专家系统（MoE）大语言模型</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GPT-5.6</t>
+          <t>Meta One Plus / Meta One Premium</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>AI智能体（聊天机器人服务）</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -533,17 +533,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布 [重要性:高|OpenAI 的 GPT 主线模型若属实将是旗舰级重大版本更新。]</t>
+          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
+          <t>2026-05-29 02:04</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -553,26 +553,26 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://platform.openai.com/docs/models; 任务类型→通用对话; 开闭源→闭源; 问题: 未能确认 OpenAI 官方发布过 GPT-5.6; 现有发布时间疑似来自泄露或传闻，不应视为官方发布日期; 备注包含预测和泄露信息，建议人工核验后再录入; 模型名称包含明确版本号，形式上符合规范；但发布真实性和官方发布日期需重点复核。</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型疑似分类错误：该条目是AI智能体订阅服务/产品套餐，不是具体模型; 备注描述偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面，且无法确认其对应具体模型版本</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-29 02:03</t>
+          <t>2026-05-30 01:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Mythos</t>
+          <t>dvlt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,58 +580,66 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>大语言模型（安全增强型）</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/dvlt</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
+          <t>HuggingFace image-to-3d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称像系列名或代号，未指向具体模型版本; 未能确认 Anthropic 官方发布过 Claude Mythos; 备注中关于央行和 SWIFT 漏洞暴露的描述高度异常，需严格核验来源; 现有发布时间缺乏官方依据</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/dvlt)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-29 02:03</t>
+          <t>2026-05-30 01:58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>NV-OneFormer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -641,84 +649,76 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>闭源</t>
+          <t>开源</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/claude-opus-4-8</t>
+          <t>https://huggingface.co/nvidia/NV-OneFormer</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1000k上下文；顶级推理能力；顶级编码能力；高端定价 [重要性:高|Anthropic Claude Opus 主线高端模型若属实属于旗舰级重大版本更新。]</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://docs.anthropic.com/en/docs/about-claude/models/overview; 公司→Anthropic; 开闭源→闭源; 问题: 官网字段为第三方排行榜链接，不是 Anthropic 官方页面; 未能确认 Anthropic 官方发布过 Claude Opus 4.8; 模型发布时间需以 Anthropic 官方公告或官方模型文档为准; llm-stats.com 排行榜不应作为官方发布依据; 模型名称包含系列、档位和版本号，形式上符合规范；但该条目的发布时间、上下文长度和能力描述均需官方核验。</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NV-OneFormer)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-29 02:03</t>
+          <t>2026-05-30 01:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Qwen3.7-Max</t>
+          <t>Claude Opus 4.8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>大语言模型（代码增强型）</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -726,17 +726,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>阿里云于2026年5月20日阿里云峰会发布的面向AI Agent场景设计的新旗舰模型，在编程、推理、工具调用等能力上显著强化，支持长时间运行与多次工具调用，在Code Arena榜单中得分1541。</t>
+          <t>旗舰级编程大模型，支持200K上下文窗口，引入思维链增强机制与实时调试助手，显著提升复杂系统架构设计与错误诊断能力。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -754,19 +754,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeepSeek-V4 Flash</t>
+          <t>GPT-5.5 Instant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>深度求索/DeepSeek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -781,17 +781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DeepSeek于2026年5月28日最新发布的高性价比推理优化版本，提供$0.14/M token定价及每日200万Token免费额度，主打高并发、低成本商用场景。</t>
+          <t>正式成为ChatGPT默认模型，医疗/法律/金融领域幻觉率较GPT-5.3降低52%，强化编码、计算机使用与深度研究能力。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -809,26 +809,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>豆包Seed 2.0 Pro</t>
+          <t>GPT-Realtime-2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>字节跳动/豆包</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>语音大模型（推理级）</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -836,17 +836,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>豆包于2026年5月28日前后正式发布升级版Seed 2.0 Pro，综合性能跻身全球前五，以$1/M token超低价格和MMMU-Pro 68.7%精度成为国产综合能力最强的商用大模型之一。</t>
+          <t>首个具备GPT-5级推理能力的实时语音模型，支持低延迟语音理解与多步语音任务规划。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -864,14 +864,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HappyHorse 1.0</t>
+          <t>GPT-Realtime-Translate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HappyHorse</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>视频生成模型</t>
+          <t>语音-多模态模型（实时翻译）</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -891,17 +891,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026年5月28日官宣发布的首个专注高质量长时序视频生成的多模态基础模型，被列为2026年5月AI模型排行榜‘视频生成’唯一代表，以SOTA视频质量定位内容创作者市场。</t>
+          <t>端到端实时同传翻译模型，支持语义对齐与文化适配，延迟低于300ms，覆盖58种语言对。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -919,14 +919,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta One Plus / Meta One Premium</t>
+          <t>Gemini Robotics 1.5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI智能体（聊天机器人服务）</t>
+          <t>具身智能模型（机器人控制）</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -946,17 +946,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+          <t>面向物理机器人的新一代多模态推理模型，支持跨形态技能迁移与多智能体协同决策。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -974,14 +974,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MuleRun</t>
+          <t>讯飞建筑智能体平台2.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -993,7 +993,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AI智能体框架</t>
+          <t>行业智能体平台</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1001,17 +1001,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
+          <t>基于全国产算力训练的建筑行业大模型+‘1+1+N’智能体架构，已落地35个可执行场景智能体，实现空调节能、会议预定、数智问答等闭环任务。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qoder</t>
+          <t>通义千问重量级新朋友（未命名）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>智能体编程平台</t>
+          <t>大语言模型（预告发布）</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1056,17 +1056,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
+          <t>阿里云峰会上正式亮相的全新旗舰模型，官方称其在全能性、深度与广度上全面对标GPT-5.5，但截至5月29日尚未公布具体型号与技术细节。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-30 01:59</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1080,61 +1080,6 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>稀宇极智MoE大模型（未公开命名）</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>上海稀宇极智科技有限公司</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>混合专家系统（MoE）大语言模型</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:04</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型疑似分类错误：该条目是AI智能体订阅服务/产品套餐，不是具体模型; 备注描述偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面，且无法确认其对应具体模型版本</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型疑似分类错误：该条目是AI智能体订阅服务/产品套餐，不是具体模型; 备注描述偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面，且无法确认其对应具体模型版本; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型分类错误：该条目更像AI助手订阅服务/商业化套餐，不是具体模型; 备注偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面; 无法确认其对应任何具体模型版本</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>旗舰级编程大模型，支持200K上下文窗口，引入思维链增强机制与实时调试助手，显著提升复杂系统架构设计与错误诊断能力。</t>
+          <t>旗舰级编程大模型，支持200K上下文窗口，引入思维链增强机制与实时调试助手，显著提升复杂系统架构设计与错误诊断能力。 [重要性:高|Anthropic属于国外重点关注公司，Claude Opus若为4.x旗舰更新应属高优先级。]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→通用对话/代码生成; 官网→https://www.anthropic.com/claude; 问题: 模型名称形式符合规范：具体模型系列+版本号; 无法基于已知公开资料确认Claude Opus 4.8是否已由Anthropic官方发布; 现有备注包含较多未经核实的能力描述，建议人工复核官方公告; 保留但需重点核实发布日期、是否真实存在以及是否为官方命名。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -781,7 +781,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>正式成为ChatGPT默认模型，医疗/法律/金融领域幻觉率较GPT-5.3降低52%，强化编码、计算机使用与深度研究能力。</t>
+          <t>正式成为ChatGPT默认模型，医疗/法律/金融领域幻觉率较GPT-5.3降低52%，强化编码、计算机使用与深度研究能力。 [重要性:高|OpenAI属于国外重点关注公司，GPT-5.5若为主线模型重大更新应为高重要性。]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→通用对话/代码生成/智能体; 官网→https://openai.com; 问题: 模型名称形式符合规范：具体模型系列+版本/子型号; 无法基于已知公开资料确认GPT-5.5 Instant是否已由OpenAI官方发布; 备注中的医疗/法律/金融幻觉率降低52%等指标需官方来源核验; 需确认Instant是正式模型名、ChatGPT产品档位名，还是内部路由别名; 不建议因无法核实直接删除；若官方未发布，应后续人工剔除。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -833,10 +833,14 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/advancing-voice-intelligence-with-new-models-in-the-api/</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>首个具备GPT-5级推理能力的实时语音模型，支持低延迟语音理解与多步语音任务规划。</t>
+          <t>首个具备GPT-5级推理能力的实时语音模型，支持低延迟语音理解与多步语音任务规划。 [重要性:高|OpenAI实时语音模型若升级到第二代且具备推理能力，属于重点公司的重要多模态更新。]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -856,7 +860,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→语音理解/实时语音交互; 官网→https://platform.openai.com/docs; 问题: 模型名称形式基本符合规范：具体模型名+版本号; 无法基于已知公开资料确认GPT-Realtime-2是否为OpenAI官方模型名; 备注中的GPT-5级推理能力、低延迟多步任务规划等表述需官方来源核验; 建议核查OpenAI Realtime API官方文档中是否存在该精确模型ID。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -891,7 +895,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>端到端实时同传翻译模型，支持语义对齐与文化适配，延迟低于300ms，覆盖58种语言对。</t>
+          <t>端到端实时同传翻译模型，支持语义对齐与文化适配，延迟低于300ms，覆盖58种语言对。 [重要性:中|OpenAI重点公司的垂直实时翻译模型，若属实在语音同传场景有较高价值，但不像主线旗舰模型。]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -911,7 +915,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→实时语音翻译/多模态翻译; 官网→https://platform.openai.com/docs; 问题: 模型名称有具体功能指向，但缺少明确版本号/型号，需确认是否为正式模型名; 无法基于已知公开资料确认GPT-Realtime-Translate是否已由OpenAI官方发布; 备注中的低于300ms延迟、58种语言对等指标需官方来源核验; 若只是Realtime API能力名称而非独立模型，应合并到对应Realtime模型条目。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -946,7 +950,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>面向物理机器人的新一代多模态推理模型，支持跨形态技能迁移与多智能体协同决策。</t>
+          <t>面向物理机器人的新一代多模态推理模型，支持跨形态技能迁移与多智能体协同决策。 [重要性:高|Google DeepMind属于国外重点关注公司，Gemini Robotics若为机器人基础模型升级属于高价值方向。]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -966,7 +970,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→具身智能/机器人控制; 问题: 模型名称形式符合规范：具体模型系列+版本号; 无法基于已知公开资料确认Gemini Robotics 1.5是否已由Google DeepMind官方发布; 公司名建议统一为Google DeepMind; 备注中的跨形态技能迁移、多智能体协同等能力需官方来源核验; 建议核查Google DeepMind官方博客或Gemini Robotics页面，以确认1.5版本是否真实发布。</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 虽然含有2.0版本号，但名称指向的是行业智能体平台，不是具体模型; 类型不是大模型条目，属于行业应用平台/解决方案; 备注描述落地场景和架构，缺少模型自身参数、能力基准或模型版本; 缺少模型提供方官方页面</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1029,26 +1033,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>通义千问重量级新朋友（未命名）</t>
+          <t>SigenAgent v1.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>思格新能源</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>大语言模型（预告发布）</t>
+          <t>AI智能体</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1056,17 +1060,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>阿里云峰会上正式亮相的全新旗舰模型，官方称其在全能性、深度与广度上全面对标GPT-5.5，但截至5月29日尚未公布具体型号与技术细节。</t>
+          <t>面向新能源系统的全域AI智能体，支持目标理解、自动执行与持续学习，实现从‘对话助手’到‘使命必达执行者’的跃迁。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-05-31 02:15</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1080,6 +1084,171 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>悟空（Wukong）儿童陪伴人形机器人AI系统</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>中国电信</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>多模态AI智能体</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>专为3–7岁儿童设计的具身智能体，融合语音识别、视觉理解、触觉交互与情感化响应，支持自然语言问答与物理动作反馈。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>汽车发动机维修大数据诊断模型</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026世界智能产业博览会参展单位（未具名，属车企/工业AI联合体）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>垂直领域大模型（工业诊断）</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>基于多源传感器与维修知识图谱构建的预测性诊断大模型，支持不拆解发动机的故障定位与维修建议生成。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AgentForce 智能体中台 v2.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>迈富时（MarketingForce）</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AI智能体平台</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>企业级低代码智能体操作系统，支持业务人员2分钟内创建营销/销售场景专用智能体，集成NLA工作流自动生成与知识图谱驱动推理。</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Meta One Plus / Meta One Premium</t>
+          <t>SigenAgent v1.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>思格新能源</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI智能体（聊天机器人服务）</t>
+          <t>AI智能体</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -533,17 +533,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+          <t>面向新能源系统的全域AI智能体，支持目标理解、自动执行与持续学习，实现从‘对话助手’到‘使命必达执行者’的跃迁。 [重要性:低|其他公司面向新能源场景的垂直智能体，行业影响力和模型级技术信息有限。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-05-31 02:15</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -553,26 +553,26 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型疑似分类错误：该条目是AI智能体订阅服务/产品套餐，不是具体模型; 备注描述偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面，且无法确认其对应具体模型版本; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型分类错误：该条目更像AI助手订阅服务/商业化套餐，不是具体模型; 备注偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面; 无法确认其对应任何具体模型版本</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.sigenergy.com; 任务类型→AI智能体; 公司→思格新能源（Sigenergy）; 类型→AI智能体; 问题: 发布信息待核实，未能确认是否为模型提供方官方发布; 更像行业应用智能体/产品系统，而非通用基础模型; 公司为中国企业，原始字段“国内外=国外”疑似错误; 名称包含 v1.0，形式上满足“具体产品名称+版本号”要求；但需人工核实其官方发布时间和是否应纳入模型库。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-30 01:58</t>
+          <t>2026-06-01 02:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dvlt</t>
+          <t>悟空（Wukong）儿童陪伴人形机器人AI系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,31 +580,19 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>多模态AI智能体</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/dvlt</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace image-to-3d</t>
+          <t>专为3–7岁儿童设计的具身智能体，融合语音识别、视觉理解、触觉交互与情感化响应，支持自然语言问答与物理动作反馈。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -614,32 +602,36 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/dvlt)</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称未包含明确版本号/型号，不满足“具体模型/产品名称+版本号/型号”规范; 更像儿童陪伴机器人产品系统，不是明确可追踪的模型版本; 公司为中国企业，原始字段“国内外=国外”疑似错误; 发布时间待核实，未能确认是否存在官方模型发布公告</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-30 01:58</t>
+          <t>2026-06-01 02:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NV-OneFormer</t>
+          <t>AgentForce 智能体中台 v2.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>迈富时（MarketingForce）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -647,78 +639,74 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>AI智能体平台</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/NV-OneFormer</t>
+          <t>https://www.marketingforce.com/</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>企业级低代码智能体操作系统，支持业务人员2分钟内创建营销/销售场景专用智能体，集成NLA工作流自动生成与知识图谱驱动推理。 [重要性:低|其他公司企业级智能体平台版本更新，偏应用平台，非基础模型或重点公司旗舰模型。]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NV-OneFormer)</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→AI智能体平台; 公司→迈富时（Marketingforce）; 类型→AI智能体平台; 问题: 发布信息待核实，未能确认是否为官方发布; 更像企业级智能体平台/中台产品，不是单一模型; 需注意名称可能与 Salesforce 的 Agentforce 品牌混淆，应核实提供方; 公司为中国企业，原始字段“国内外=国外”疑似错误; 名称包含 v2.1，形式上满足具体产品版本要求；但建议补充官方页面、发布公告和底层模型信息后再正式入库。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-30 01:58</t>
+          <t>2026-06-01 02:35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>Qwen3.7-Max</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>大语言模型（代码增强型）</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -726,17 +714,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>旗舰级编程大模型，支持200K上下文窗口，引入思维链增强机制与实时调试助手，显著提升复杂系统架构设计与错误诊断能力。 [重要性:高|Anthropic属于国外重点关注公司，Claude Opus若为4.x旗舰更新应属高优先级。]</t>
+          <t>通义千问在2026年5月20日阿里云峰会正式发布的旗舰级大模型，编程能力全球第二（Code Arena 1541分），支持超1000次工具调用的长程智能体任务，推理速度较前代提升10倍。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -746,7 +734,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→通用对话/代码生成; 官网→https://www.anthropic.com/claude; 问题: 模型名称形式符合规范：具体模型系列+版本号; 无法基于已知公开资料确认Claude Opus 4.8是否已由Anthropic官方发布; 现有备注包含较多未经核实的能力描述，建议人工复核官方公告; 保留但需重点核实发布日期、是否真实存在以及是否为官方命名。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -754,26 +742,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GPT-5.5 Instant</t>
+          <t>Doubao-Seed-2.0-Pro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>字节跳动/豆包</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>原生多模态智能体</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -781,17 +769,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>正式成为ChatGPT默认模型，医疗/法律/金融领域幻觉率较GPT-5.3降低52%，强化编码、计算机使用与深度研究能力。 [重要性:高|OpenAI属于国外重点关注公司，GPT-5.5若为主线模型重大更新应为高重要性。]</t>
+          <t>豆包2.0系列旗舰版本，实现视频、图像、音频、文本的原生统一理解与视听联合推理，完成从对话AI到‘实体智能体’的范式跃迁。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,7 +789,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→通用对话/代码生成/智能体; 官网→https://openai.com; 问题: 模型名称形式符合规范：具体模型系列+版本/子型号; 无法基于已知公开资料确认GPT-5.5 Instant是否已由OpenAI官方发布; 备注中的医疗/法律/金融幻觉率降低52%等指标需官方来源核验; 需确认Instant是正式模型名、ChatGPT产品档位名，还是内部路由别名; 不建议因无法核实直接删除；若官方未发布，应后续人工剔除。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -809,7 +797,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GPT-Realtime-2</t>
+          <t>GPT-5.5 Instant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -828,29 +816,25 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>语音大模型（推理级）</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/advancing-voice-intelligence-with-new-models-in-the-api/</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>首个具备GPT-5级推理能力的实时语音模型，支持低延迟语音理解与多步语音任务规划。 [重要性:高|OpenAI实时语音模型若升级到第二代且具备推理能力，属于重点公司的重要多模态更新。]</t>
+          <t>GPT-5.5系列默认部署版本，取代GPT-5.3成为ChatGPT主力模型，医疗/法律/金融领域幻觉率下降52%，显著增强编码与计算机使用能力。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -860,7 +844,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→语音理解/实时语音交互; 官网→https://platform.openai.com/docs; 问题: 模型名称形式基本符合规范：具体模型名+版本号; 无法基于已知公开资料确认GPT-Realtime-2是否为OpenAI官方模型名; 备注中的GPT-5级推理能力、低延迟多步任务规划等表述需官方来源核验; 建议核查OpenAI Realtime API官方文档中是否存在该精确模型ID。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -868,7 +852,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GPT-Realtime-Translate</t>
+          <t>GPT-Realtime-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -887,7 +871,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>语音-多模态模型（实时翻译）</t>
+          <t>语音推理模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -895,7 +879,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>端到端实时同传翻译模型，支持语义对齐与文化适配，延迟低于300ms，覆盖58种语言对。 [重要性:中|OpenAI重点公司的垂直实时翻译模型，若属实在语音同传场景有较高价值，但不像主线旗舰模型。]</t>
+          <t>首个具备GPT-5级推理能力的实时语音模型，支持语音输入下的多步逻辑推演与上下文保持。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -905,7 +889,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -915,7 +899,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→实时语音翻译/多模态翻译; 官网→https://platform.openai.com/docs; 问题: 模型名称有具体功能指向，但缺少明确版本号/型号，需确认是否为正式模型名; 无法基于已知公开资料确认GPT-Realtime-Translate是否已由OpenAI官方发布; 备注中的低于300ms延迟、58种语言对等指标需官方来源核验; 若只是Realtime API能力名称而非独立模型，应合并到对应Realtime模型条目。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -923,14 +907,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gemini Robotics 1.5</t>
+          <t>GPT-Realtime-Translate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -942,7 +926,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>具身智能模型（机器人控制）</t>
+          <t>语音翻译模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -950,17 +934,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>面向物理机器人的新一代多模态推理模型，支持跨形态技能迁移与多智能体协同决策。 [重要性:高|Google DeepMind属于国外重点关注公司，Gemini Robotics若为机器人基础模型升级属于高价值方向。]</t>
+          <t>端到端实时同传翻译模型，支持低延迟、高保真跨语言语义对齐，已集成至Teams和Zoom企业插件。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -970,7 +954,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→具身智能/机器人控制; 问题: 模型名称形式符合规范：具体模型系列+版本号; 无法基于已知公开资料确认Gemini Robotics 1.5是否已由Google DeepMind官方发布; 公司名建议统一为Google DeepMind; 备注中的跨形态技能迁移、多智能体协同等能力需官方来源核验; 建议核查Google DeepMind官方博客或Gemini Robotics页面，以确认1.5版本是否真实发布。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -978,26 +962,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>讯飞建筑智能体平台2.0</t>
+          <t>Gemini Robotics 1.5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>行业智能体平台</t>
+          <t>具身智能模型</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1005,17 +989,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>基于全国产算力训练的建筑行业大模型+‘1+1+N’智能体架构，已落地35个可执行场景智能体，实现空调节能、会议预定、数智问答等闭环任务。</t>
+          <t>专为机器人设计的下一代世界模型，支持跨形态技能迁移与多智能体协作规划，已在波士顿动力Atlas及UBTECH Walker X平台实测部署。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-30 01:59</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1025,7 +1009,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 虽然含有2.0版本号，但名称指向的是行业智能体平台，不是具体模型; 类型不是大模型条目，属于行业应用平台/解决方案; 备注描述落地场景和架构，缺少模型自身参数、能力基准或模型版本; 缺少模型提供方官方页面</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1033,26 +1017,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SigenAgent v1.0</t>
+          <t>DeepSeek R1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>思格新能源</t>
+          <t>深度求索/DeepSeek</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AI智能体</t>
+          <t>强化对齐大模型</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1060,17 +1044,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>面向新能源系统的全域AI智能体，支持目标理解、自动执行与持续学习，实现从‘对话助手’到‘使命必达执行者’的跃迁。</t>
+          <t>基于RLHF+Test-time Scaling双路径优化的推理增强模型，在MMLU-Pro与AgentBench上刷新国产模型纪录，强调‘可解释决策链’输出。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-31 02:15</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1088,26 +1072,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>悟空（Wukong）儿童陪伴人形机器人AI系统</t>
+          <t>Kimi-Max-2605</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>月之暗面/Kimi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>多模态AI智能体</t>
+          <t>长上下文智能体</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1115,17 +1099,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>专为3–7岁儿童设计的具身智能体，融合语音识别、视觉理解、触觉交互与情感化响应，支持自然语言问答与物理动作反馈。</t>
+          <t>支持200万token上下文的轻量化智能体框架，专为法律文书分析、科研文献综述等专业场景优化，已接入国家知识产权局政务AI中台。</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-31 02:15</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1143,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>汽车发动机维修大数据诊断模型</t>
+          <t>GLM-5-AllSpark</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026世界智能产业博览会参展单位（未具名，属车企/工业AI联合体）</t>
+          <t>智谱AI/GLM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>垂直领域大模型（工业诊断）</t>
+          <t>全模态生成模型</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1170,17 +1154,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>基于多源传感器与维修知识图谱构建的预测性诊断大模型，支持不拆解发动机的故障定位与维修建议生成。</t>
+          <t>GLM系列首款支持‘文本→3D网格+物理仿真参数+音效轨迹’联合生成的Diffusion 3.0原生模型，面向工业数字孪生场景发布。</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:15</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1198,26 +1182,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AgentForce 智能体中台 v2.1</t>
+          <t>SenseNova 6.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>迈富时（MarketingForce）</t>
+          <t>商汤科技</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AI智能体平台</t>
+          <t>多模态基础模型</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1225,17 +1209,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>企业级低代码智能体操作系统，支持业务人员2分钟内创建营销/销售场景专用智能体，集成NLA工作流自动生成与知识图谱驱动推理。</t>
+          <t>覆盖视觉、语音、文本、雷达点云的八模态统一架构模型，首次将毫米波雷达信号纳入大模型感知通路，用于L4级车路协同系统。</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-31 02:15</t>
+          <t>2026-06-01 02:36</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GPT-5.6</t>
+          <t>CircularNet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,58 +521,66 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/CircularNet</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布 [重要性:高|OpenAI 的 GPT 主线模型若属实将是旗舰级重大版本更新。]</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://platform.openai.com/docs/models; 任务类型→通用对话; 开闭源→闭源; 问题: 未能确认 OpenAI 官方发布过 GPT-5.6; 现有发布时间疑似来自泄露或传闻，不应视为官方发布日期; 备注包含预测和泄露信息，建议人工核验后再录入; 模型名称包含明确版本号，形式上符合规范；但发布真实性和官方发布日期需重点复核。</t>
+          <t>HuggingFace 已核实(google/CircularNet) · apache-2.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-29 02:03</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Mythos</t>
+          <t>4D-RGPT-8B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,145 +588,137 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>大语言模型（安全增强型）</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/4D-RGPT-8B</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
+          <t>HuggingFace video-text-to-text</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:56</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称像系列名或代号，未指向具体模型版本; 未能确认 Anthropic 官方发布过 Claude Mythos; 备注中关于央行和 SWIFT 漏洞暴露的描述高度异常，需严格核验来源; 现有发布时间缺乏官方依据</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/4D-RGPT-8B)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-29 02:03</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>Qwen3.7-Plus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/claude-opus-4-8</t>
-        </is>
-      </c>
+          <t>多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1000k上下文；顶级推理能力；顶级编码能力；高端定价 [重要性:高|Anthropic Claude Opus 主线高端模型若属实属于旗舰级重大版本更新。]</t>
+          <t>阿里发布的全新多模态智能体模型，面向复杂任务编排与具身交互优化。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://docs.anthropic.com/en/docs/about-claude/models/overview; 公司→Anthropic; 开闭源→闭源; 问题: 官网字段为第三方排行榜链接，不是 Anthropic 官方页面; 未能确认 Anthropic 官方发布过 Claude Opus 4.8; 模型发布时间需以 Anthropic 官方公告或官方模型文档为准; llm-stats.com 排行榜不应作为官方发布依据; 模型名称包含系列、档位和版本号，形式上符合规范；但该条目的发布时间、上下文长度和能力描述均需官方核验。</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:03</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Qwen3.7-Max</t>
+          <t>MAI-Thinking-1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>旗舰推理大语言模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -726,17 +726,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>阿里云于2026年5月20日阿里云峰会发布的面向AI Agent场景设计的新旗舰模型，在编程、推理、工具调用等能力上显著强化，支持长时间运行与多次工具调用，在Code Arena榜单中得分1541。</t>
+          <t>微软MAI家族首款中型自研推理模型，零蒸馏训练，在软件工程测试中性能媲美Sonnet 4.6。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -754,26 +754,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeepSeek-V4 Flash</t>
+          <t>MAI-Code-1-Flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>深度求索/DeepSeek</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>编程专用agentic模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -781,17 +781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DeepSeek于2026年5月28日最新发布的高性价比推理优化版本，提供$0.14/M token定价及每日200万Token免费额度，主打高并发、低成本商用场景。</t>
+          <t>50亿参数高效编码模型，深度集成GitHub Copilot与VS Code，专为微软技术栈优化。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -809,26 +809,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>豆包Seed 2.0 Pro</t>
+          <t>DobotWAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>字节跳动/豆包</t>
+          <t>越疆科技</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>具身智能体大模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -836,17 +836,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>豆包于2026年5月28日前后正式发布升级版Seed 2.0 Pro，综合性能跻身全球前五，以$1/M token超低价格和MMMU-Pro 68.7%精度成为国产综合能力最强的商用大模型之一。</t>
+          <t>面向机器人操作的具身大模型，在LIBERO基准登顶第一，任务成功率99.25%。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -864,26 +864,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HappyHorse 1.0</t>
+          <t>MiniMax M3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HappyHorse</t>
+          <t>MiniMax/海螺</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>视频生成模型</t>
+          <t>多模态大模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -891,17 +891,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026年5月28日官宣发布的首个专注高质量长时序视频生成的多模态基础模型，被列为2026年5月AI模型排行榜‘视频生成’唯一代表，以SOTA视频质量定位内容创作者市场。</t>
+          <t>京东云率先上线的MiniMax最新多模态基础模型，支持图文音视频联合理解与生成。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -919,14 +919,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta One Plus / Meta One Premium</t>
+          <t>LobsterAI Image-Video Matrix</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>LobsterAI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI智能体（聊天机器人服务）</t>
+          <t>图像/视频生成大模型矩阵</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -946,17 +946,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-29 02:04</t>
+          <t>2026-06-03 02:40</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -970,171 +970,6 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MuleRun</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>阿里巴巴/通义</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>AI智能体框架</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:04</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Qoder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>阿里巴巴/通义</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>智能体编程平台</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:04</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>稀宇极智MoE大模型（未公开命名）</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>上海稀宇极智科技有限公司</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>混合专家系统（MoE）大语言模型</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:04</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CircularNet</t>
+          <t>LobsterAI Image-Video Matrix</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>LobsterAI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,31 +521,19 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>图像/视频生成大模型矩阵</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/google/CircularNet</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -555,32 +543,36 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HuggingFace 已核实(google/CircularNet) · apache-2.0</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称指向模型矩阵/模型集合，不是具体的模型/产品名称 + 版本号/型号; 未能基于已知公开信息确认其为官方发布的具体模型</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4D-RGPT-8B</t>
+          <t>MAI-Code-1-Flash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,82 +580,66 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>代码生成大语言模型</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/4D-RGPT-8B</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace video-text-to-text</t>
+          <t>微软在 Build 2026 大会上发布的首款自研代码生成模型，支持自然语言到应用程序/网站源代码的端到端生成，已集成至 GitHub Copilot 和 VS Code。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/4D-RGPT-8B)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-06-03 02:40</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Qwen3.7-Plus</t>
+          <t>MAI-Thinking-1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态智能体模型</t>
+          <t>推理型大语言模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -671,17 +647,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>阿里发布的全新多模态智能体模型，面向复杂任务编排与具身交互优化。</t>
+          <t>微软发布的旗舰推理模型，在编码基准测试中性能媲美 Anthropic Claude Sonnet 4.6，为微软新一代智能体核心推理引擎。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -699,7 +675,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAI-Thinking-1</t>
+          <t>MAI-Vision-1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -718,7 +694,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>旗舰推理大语言模型</t>
+          <t>多模态视觉理解模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -726,17 +702,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>微软MAI家族首款中型自研推理模型，零蒸馏训练，在软件工程测试中性能媲美Sonnet 4.6。</t>
+          <t>微软在 Build 2026 发布的视觉基础模型，支持图像、文档、图表等复杂视觉输入的语义解析与跨模态推理，专为智能体环境感知优化。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -754,7 +730,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAI-Code-1-Flash</t>
+          <t>MAI-Speech-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -773,7 +749,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>编程专用agentic模型</t>
+          <t>语音大语言模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -781,17 +757,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50亿参数高效编码模型，深度集成GitHub Copilot与VS Code，专为微软技术栈优化。</t>
+          <t>微软新发布的低延迟、高保真语音交互模型，支持实时流式语音理解与生成，深度集成于 Windows Copilot+ 设备及 Teams 智能会议场景。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -809,14 +785,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DobotWAM</t>
+          <t>MAI-Multimodal-Agent-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>越疆科技</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -828,7 +804,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>具身智能体大模型</t>
+          <t>自主智能体（Agent）系统</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -836,17 +812,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>面向机器人操作的具身大模型，在LIBERO基准登顶第一，任务成功率99.25%。</t>
+          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -864,26 +840,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MiniMax M3</t>
+          <t>Web IQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MiniMax/海螺</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>多模态大模型</t>
+          <t>AI智能体专用搜索 API 服务</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -891,17 +867,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>京东云率先上线的MiniMax最新多模态基础模型，支持图文音视频联合理解与生成。</t>
+          <t>微软推出的面向 AI 智能体的语义化网络检索服务，提供带 grounding 的结构化网页、新闻、图片、视频内容，非面向人类的传统搜索引擎。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -919,14 +895,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LobsterAI Image-Video Matrix</t>
+          <t>Mayo-Medical-LLM (codename: MedSage)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LobsterAI</t>
+          <t>Mayo Clinic &amp; Microsoft</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +914,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>图像/视频生成大模型矩阵</t>
+          <t>医疗垂直领域大语言模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -946,17 +922,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
+          <t>梅奥诊所与微软联合发布、由梅奥持有主权的临床级 AI 模型，基于去标识化真实世界健康数据训练，专注临床推理与诊疗辅助，尚未开源或商用。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LobsterAI Image-Video Matrix</t>
+          <t>MAI-Multimodal-Agent-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LobsterAI</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,7 +525,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>图像/视频生成大模型矩阵</t>
+          <t>自主智能体（Agent）系统</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -533,17 +533,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
+          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。 [重要性:中|若属实，这是微软面向企业自动化的多模态智能体框架，具备一定平台级价值，但公开信息仍需人工核实。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-03 02:40</t>
+          <t>2026-06-04 02:36</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -553,26 +553,26 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称指向模型矩阵/模型集合，不是具体的模型/产品名称 + 版本号/型号; 未能基于已知公开信息确认其为官方发布的具体模型</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→自主智能体/多模态智能体; 公司→Microsoft AI; 类型→自主智能体（Agent）系统; 问题: 名称包含明确型号/版本号，形式上符合具体模型或系统名称规范; 当前信息显示更像智能体系统/框架，而非传统基础模型，需确认是否应纳入模型库; 发布时间为2026-06-03，处于本次追踪窗口附近，可宽松保留; 核实情况为待核实，建议人工查验微软官方发布源; 未能基于已知可靠公开知识确认该名称及发布日期，建议以 Microsoft AI 官方博客、Azure AI 文档或 GitHub/SDK 发布记录为准。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:35</t>
+          <t>2026-06-05 02:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAI-Code-1-Flash</t>
+          <t>ArtiFixer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,42 +580,54 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>代码生成大语言模型</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/ArtiFixer</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>微软在 Build 2026 大会上发布的首款自研代码生成模型，支持自然语言到应用程序/网站源代码的端到端生成，已集成至 GitHub Copilot 和 VS Code。</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/ArtiFixer)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,7 +651,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>推理型大语言模型</t>
+          <t>大语言模型（推理专用）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -647,7 +659,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>微软发布的旗舰推理模型，在编码基准测试中性能媲美 Anthropic Claude Sonnet 4.6，为微软新一代智能体核心推理引擎。</t>
+          <t>微软在Build 2026大会上发布的旗舰推理模型，在编码基准测试中与Anthropic Claude Sonnet 4.6持平。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -657,7 +669,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -675,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAI-Vision-1</t>
+          <t>MAI-Code-1-Flash</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -694,7 +706,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>多模态视觉理解模型</t>
+          <t>代码大语言模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -702,7 +714,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>微软在 Build 2026 发布的视觉基础模型，支持图像、文档、图表等复杂视觉输入的语义解析与跨模态推理，专为智能体环境感知优化。</t>
+          <t>微软首款AI编程模型，50亿参数，面向VS Code/GitHub Copilot个人版，高性价比，Token消耗较Claude Haiku 4.5最高降低60%。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -712,7 +724,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -730,7 +742,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAI-Speech-1</t>
+          <t>MAI-Vision-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -749,7 +761,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>语音大语言模型</t>
+          <t>多模态模型（视觉理解）</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -757,7 +769,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>微软新发布的低延迟、高保真语音交互模型，支持实时流式语音理解与生成，深度集成于 Windows Copilot+ 设备及 Teams 智能会议场景。</t>
+          <t>微软Build 2026发布的全栈模型之一，支持细粒度图像-文本对齐与跨模态推理，已集成至Windows Copilot+生态。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -767,7 +779,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -785,7 +797,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAI-Multimodal-Agent-1</t>
+          <t>MAI-Speech-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -804,7 +816,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>自主智能体（Agent）系统</t>
+          <t>语音大模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -812,7 +824,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。</t>
+          <t>低延迟、高保真端到端语音合成与识别模型，支持实时双语会议转录与智能摘要，首发搭载于Surface RTX Spark Dev Box。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -822,7 +834,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -840,7 +852,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Web IQ</t>
+          <t>MAI-Multimodal-1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -859,7 +871,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AI智能体专用搜索 API 服务</t>
+          <t>多模态大模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -867,7 +879,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>微软推出的面向 AI 智能体的语义化网络检索服务，提供带 grounding 的结构化网页、新闻、图片、视频内容，非面向人类的传统搜索引擎。</t>
+          <t>微软七款新模型之一，统一架构支持文本、图像、音频、代码联合输入输出，面向企业级Copilot Agent工作流。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -877,7 +889,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -895,14 +907,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mayo-Medical-LLM (codename: MedSage)</t>
+          <t>MAI-Agent-Core-v1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mayo Clinic &amp; Microsoft</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -914,7 +926,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>医疗垂直领域大语言模型</t>
+          <t>智能体框架/运行时</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -922,7 +934,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>梅奥诊所与微软联合发布、由梅奥持有主权的临床级 AI 模型，基于去标识化真实世界健康数据训练，专注临床推理与诊疗辅助，尚未开源或商用。</t>
+          <t>微软发布的轻量级Agentic AI运行时，原生支持PRAR循环（感知-推理-行动-反思），深度集成Windows Terminal与WSL2。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -932,7 +944,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
+          <t>2026-06-05 02:11</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -946,6 +958,61 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAI-Toolformer-1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>工具调用增强模型</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>专为自动工具发现、API Schema理解与安全工具链编排优化的微调模型，作为MAI-Agent-Core-v1的默认控制器。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAI-Multimodal-Agent-1</t>
+          <t>gemma-4-12B-it-qat-w4a16-ct</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,58 +521,70 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>自主智能体（Agent）系统</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-12B-it-qat-w4a16-ct</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。 [重要性:中|若属实，这是微软面向企业自动化的多模态智能体框架，具备一定平台级价值，但公开信息仍需人工核实。]</t>
+          <t>HuggingFace any-to-any</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:36</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→自主智能体/多模态智能体; 公司→Microsoft AI; 类型→自主智能体（Agent）系统; 问题: 名称包含明确型号/版本号，形式上符合具体模型或系统名称规范; 当前信息显示更像智能体系统/框架，而非传统基础模型，需确认是否应纳入模型库; 发布时间为2026-06-03，处于本次追踪窗口附近，可宽松保留; 核实情况为待核实，建议人工查验微软官方发布源; 未能基于已知可靠公开知识确认该名称及发布日期，建议以 Microsoft AI 官方博客、Azure AI 文档或 GitHub/SDK 发布记录为准。</t>
+          <t>HuggingFace 已核实(google/gemma-4-12B-it-qat-w4a16-ct) · 参数量=13B · apache-2.0 · any-to-any</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-05 02:10</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ArtiFixer</t>
+          <t>Cosmos 3 (Super/Base/Tiny)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,66 +592,54 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>全模态物理AI基础模型</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/ArtiFixer</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>全球首款完全开源的文本/图像/视频/音频/动作五模态物理AI模型，原生支持重力、摩擦、碰撞等物理规则建模，基于混合Transformer（MoT）架构。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/ArtiFixer)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-06-05 02:10</t>
-        </is>
-      </c>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MAI-Thinking-1</t>
+          <t>Nemotron 3 Ultra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -651,7 +651,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>大语言模型（推理专用）</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -659,17 +659,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>微软在Build 2026大会上发布的旗舰推理模型，在编码基准测试中与Anthropic Claude Sonnet 4.6持平。</t>
+          <t>千亿参数Dense架构LLM，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理（首Token延迟低至180ms），面向消费级GPU优化。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -687,26 +687,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAI-Code-1-Flash</t>
+          <t>MiniMax M3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>代码大语言模型</t>
+          <t>多模态大语言模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>微软首款AI编程模型，50亿参数，面向VS Code/GitHub Copilot个人版，高性价比，Token消耗较Claude Haiku 4.5最高降低60%。</t>
+          <t>国内首个同时具备前沿Coding能力、1M超长上下文、原生多模态的国产大模型，采用自研MSA稀疏注意力架构，SWE-Bench Pro超越GPT-5.5。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -742,14 +742,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAI-Vision-1</t>
+          <t>Qwen3.7-Plus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alibaba (Tongyi Lab)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -761,7 +761,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>多模态模型（视觉理解）</t>
+          <t>多模态智能体模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -769,17 +769,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>微软Build 2026发布的全栈模型之一，支持细粒度图像-文本对齐与跨模态推理，已集成至Windows Copilot+生态。</t>
+          <t>主打‘看想做做验’一体化智能体能力，可连续11小时自主开发App，覆盖需求理解、代码生成、测试验证等全流程项目级任务。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAI-Speech-1</t>
+          <t>MAI-Code-1-Flash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -816,7 +816,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>语音大模型</t>
+          <t>代码推理模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -824,17 +824,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>低延迟、高保真端到端语音合成与识别模型，支持实时双语会议转录与智能摘要，首发搭载于Surface RTX Spark Dev Box。</t>
+          <t>微软Build 2026发布的开源高级代码推理模型，专为复杂工程级代码生成与调试优化，支持多文件上下文协同推理。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAI-Multimodal-1</t>
+          <t>MAI Thinking 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -871,7 +871,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>多模态大模型</t>
+          <t>深度推理模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -879,17 +879,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>微软七款新模型之一，统一架构支持文本、图像、音频、代码联合输入输出，面向企业级Copilot Agent工作流。</t>
+          <t>微软自研的深度链式推理（Chain-of-Thought）增强模型，面向数学证明、逻辑规划与跨文档复杂决策任务。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -907,26 +907,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAI-Agent-Core-v1</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Moonshot AI (月之暗面)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>智能体框架/运行时</t>
+          <t>开源多模态智能体模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -934,17 +934,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>微软发布的轻量级Agentic AI运行时，原生支持PRAR循环（感知-推理-行动-反思），深度集成Windows Terminal与WSL2。</t>
+          <t>Kimi K2系列最新版本，强化编程与Agent集群能力，支持动态生成多个子Agent并行协作，已开源（发布时间在搜索窗口前，但为截至2026-06-05最新稳定版，广泛报道于6月初技术综述中）。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-05 02:11</t>
+          <t>2026-06-06 02:02</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -958,61 +958,6 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MAI-Toolformer-1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>工具调用增强模型</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>专为自动工具发现、API Schema理解与安全工具链编排优化的微调模型，作为MAI-Agent-Core-v1的默认控制器。</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-06-05 02:11</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,10 +601,14 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://build.nvidia.com</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>全球首款完全开源的文本/图像/视频/音频/动作五模态物理AI模型，原生支持重力、摩擦、碰撞等物理规则建模，基于混合Transformer（MoT）架构。</t>
+          <t>全球首款完全开源的文本/图像/视频/音频/动作五模态物理AI模型，原生支持重力、摩擦、碰撞等物理规则建模，基于混合Transformer（MoT）架构。 [重要性:高|NVIDIA物理AI/世界模型若为重大版本更新，具备较高行业关注度和技术价值。]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,7 +628,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.nvidia.com/en-us/ai/cosmos/; 任务类型→物理AI/世界模型; 备注→物理AI世界基础模型；多模态生成与理解；面向机器人与仿真场景；开源情况需核实; 问题: 模型名称包含多个变体Super/Base/Tiny，建议拆分为独立模型条目或明确主模型与子型号; 未能基于已知公开资料核实Cosmos 3于2026-06-01官方发布; 备注中“全球首款完全开源”“五模态”等表述需官方来源核实; 开源标注需复核，NVIDIA Cosmos系列可能存在开放权重、开放许可与完全开源的区别; 名称具备版本号，不属于产品泛称；如确为2026年6月发布，应保留。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -656,10 +660,14 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://build.nvidia.com</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>千亿参数Dense架构LLM，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理（首Token延迟低至180ms），面向消费级GPU优化。</t>
+          <t>千亿参数Dense架构LLM，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理（首Token延迟低至180ms），面向消费级GPU优化。 [重要性:中|NVIDIA属于国外优秀关注公司，Nemotron若为新一代大模型更新值得关注。]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -679,7 +687,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.nvidia.com/en-us/ai-data-science/foundation-models/nemotron/; 任务类型→通用对话/推理; 备注→Nemotron系列大语言模型；面向推理与企业AI应用；参数规模、Benchmark与消费级GPU优化能力需官方核实; 问题: 未能基于已知公开资料核实Nemotron 3 Ultra于2026-06-01官方发布; “千亿参数Dense架构”“MMLU-Pro 89.5”“RTX 5090实时推理”等具体指标需官方来源核实; 名称具备版本/型号，不属于产品泛称; 建议人工核查NVIDIA官方博客、NVIDIA NIM/Build平台及技术报告。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -714,7 +722,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>国内首个同时具备前沿Coding能力、1M超长上下文、原生多模态的国产大模型，采用自研MSA稀疏注意力架构，SWE-Bench Pro超越GPT-5.5。</t>
+          <t>国内首个同时具备前沿Coding能力、1M超长上下文、原生多模态的国产大模型，采用自研MSA稀疏注意力架构，SWE-Bench Pro超越GPT-5.5。 [重要性:高|MiniMax属于国内重点关注公司，若M3为旗舰级多模态大模型则属于重大版本更新。]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -734,7 +742,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→MiniMax; 官网→https://www.minimax.io/; 任务类型→通用对话/多模态/代码生成; 备注→MiniMax系列多模态大模型；长上下文、代码能力与Agent能力需官方核实; 问题: 未能基于已知公开资料核实MiniMax M3于2026-06-01官方发布; “国内首个”“SWE-Bench Pro超越GPT-5.5”等强断言需官方或权威评测来源核实; 名称具备版本号，不属于产品泛称; 如官方确认发布时间为2026年，应保留；当前描述存在明显营销化和未核实Benchmark风险。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -766,10 +774,14 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://tongyi.aliyun.com/</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>主打‘看想做做验’一体化智能体能力，可连续11小时自主开发App，覆盖需求理解、代码生成、测试验证等全流程项目级任务。</t>
+          <t>主打‘看想做做验’一体化智能体能力，可连续11小时自主开发App，覆盖需求理解、代码生成、测试验证等全流程项目级任务。 [重要性:高|Qwen属于国内重点关注公司的核心模型系列，若为3.7代Plus更新则具备高关注价值。]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -789,7 +801,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 官网→https://qwenlm.github.io/; 任务类型→通用对话/多模态/智能体; 备注→Qwen系列Plus版本；面向通用对话、代码与智能体任务；具体长程Agent能力需官方核实; 问题: 公司名建议统一为“阿里巴巴/通义千问”; 原始数据中“国内外”标为国外，与阿里巴巴/通义千问不符，应为国内; 未能基于已知公开资料核实Qwen3.7-Plus于2026-06-02官方发布; 类型标为“多模态智能体模型”需复核，Plus版本可能是通用大模型而非专门智能体模型; 备注中“连续11小时自主开发App”等能力描述需官方评测或演示来源核实; 名称具备版本/型号，不属于产品泛称；建议核查Qwen官方博客、GitHub和模型卡。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -824,7 +836,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>微软Build 2026发布的开源高级代码推理模型，专为复杂工程级代码生成与调试优化，支持多文件上下文协同推理。</t>
+          <t>微软Build 2026发布的开源高级代码推理模型，专为复杂工程级代码生成与调试优化，支持多文件上下文协同推理。 [重要性:中|微软自研代码模型若属实，在代码生成领域具有较高应用价值，但不在重点关注公司清单内。]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -844,7 +856,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Microsoft AI; 任务类型→代码生成/代码推理; 备注→代码推理模型；面向复杂工程级代码生成、调试与多文件上下文处理；开源情况需官方核实; 问题: 未能基于已知公开资料核实MAI-Code-1-Flash于2026-06-02官方发布; “Build 2026发布”“开源高级代码推理模型”等信息需微软官方公告核实; 开闭源标注缺失且备注称开源，建议补充并核实许可证; 名称具备版本/型号，不属于产品泛称; 建议核查Microsoft AI Blog、Build大会公告、Azure AI Foundry模型目录和GitHub。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -879,7 +891,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>微软自研的深度链式推理（Chain-of-Thought）增强模型，面向数学证明、逻辑规划与跨文档复杂决策任务。</t>
+          <t>微软自研的深度链式推理（Chain-of-Thought）增强模型，面向数学证明、逻辑规划与跨文档复杂决策任务。 [重要性:中|微软自研推理模型若属实属于重要厂商在推理方向的更新，具备中等以上关注价值。]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -899,7 +911,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Microsoft AI; 任务类型→深度推理/通用对话; 备注→深度推理模型；面向数学、逻辑规划与复杂决策；具体推理机制和性能需官方核实; 问题: 未能基于已知公开资料核实MAI Thinking 1于2026-06-02官方发布; 模型命名是否应为“MAI-Thinking-1”或其他官方格式需复核; 备注中“深度链式推理增强”等技术描述需官方技术报告核实; 名称具备版本号，不属于产品泛称; 建议核查Microsoft AI官方博客、Azure AI Foundry及Build 2026发布资料。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -934,7 +946,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kimi K2系列最新版本，强化编程与Agent集群能力，支持动态生成多个子Agent并行协作，已开源（发布时间在搜索窗口前，但为截至2026-06-05最新稳定版，广泛报道于6月初技术综述中）。</t>
+          <t>Kimi K2系列最新版本，强化编程与Agent集群能力，支持动态生成多个子Agent并行协作，已开源（发布时间在搜索窗口前，但为截至2026-06-05最新稳定版，广泛报道于6月初技术综述中）。 [重要性:高|月之暗面属于国内重点关注公司，Kimi K系列若为重要版本更新应高优先级关注。]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -954,10 +966,340 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→月之暗面/Moonshot AI; 官网→https://kimi.moonshot.cn/; 任务类型→通用对话/代码生成/智能体; 备注→Kimi K系列模型；强化编程与Agent能力；开源、多模态和子Agent协作能力需官方核实; 问题: 发布时间为2026-04-20，属于2026年内发布但明显超出本次2026-06-06窗口，应标注“窗口外”而非删除; 未能基于已知公开资料核实Kimi K2.6于2026-04-20官方发布; 类型标为“开源多模态智能体模型”需复核，尤其是开源状态和多模态能力; 备注中“动态生成多个子Agent并行协作”“截至2026-06-05最新稳定版”等表述需官方来源核实; 名称具备版本号，不属于产品泛称；因给定发布时间在2026年，按宽松保留原则不删除。</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HKGAI V3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>香港首个本地研发的生产力级大模型V3版本，支持长上下文理解与多轮复杂推理，作为香港特区政府InnoHK创科平台重点成果发布。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HKGAI Super Agent（生产力级超级智能体）</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>香港首个生产力级超级智能体，单次无干预稳定运行长达28小时，可端到端完成资料整理、推理分析、报告撰写及代码开发等复合任务。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Google I/O 2026正式发布的极速工作流优化模型，支持100万tokens超长上下文，输出速度较上一代提升4倍，专为Agent编排与高频API调用设计。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Instant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>GPT-5.5全量上线版本，聚焦可信度增强，医疗、法律等高敏感领域幻觉率下降52.5%，强调事实一致性与可验证输出。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>码道（CodeArts）AI编程智能体</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>华为云</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>智能体（AI编程）</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>华为云全新商用AI编程智能体，聚焦全流程智能编码，支持需求理解、架构设计、代码生成、单元测试与部署建议，已于2026年5月30日正式商用。</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>心理健康测·评·析·预·训·辅一体化AI大模型系统</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>可家（成都）医学工程技术有限公司</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>垂直领域多模态大模型</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>国内首个面向青少年心理健康的全链路AI大模型系统，集成筛查评估、风险预测、认知训练与人工协同辅导能力。</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gemma-4-12B-it-qat-w4a16-ct</t>
+          <t>HKGAI V3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,70 +521,58 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>12B</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/google/gemma-4-12B-it-qat-w4a16-ct</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace any-to-any</t>
+          <t>香港首个本地研发的生产力级大模型V3版本，支持长上下文理解与多轮复杂推理，作为香港特区政府InnoHK创科平台重点成果发布。 [重要性:低|其他机构发布的区域性大语言模型，具备一定本地化意义但尚未确认行业级突破。]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HuggingFace 已核实(google/gemma-4-12B-it-qat-w4a16-ct) · 参数量=13B · apache-2.0 · any-to-any</t>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 备注→香港本地研发；生产力级大语言模型；长上下文理解；多轮复杂推理; 任务类型→通用对话; 问题: 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方模型页面; 开闭源信息缺失; 发布时间为2026-06-03，位于追踪窗口前一周内，可保留但建议核实官方公告; 模型名称包含明确版本号V3，符合具体模型名称规范；但该模型的公开技术指标、参数规模、上下文长度等信息不足。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-08 02:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cosmos 3 (Super/Base/Tiny)</t>
+          <t>HKGAI Super Agent（生产力级超级智能体）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -596,29 +584,25 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>全模态物理AI基础模型</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://build.nvidia.com</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>全球首款完全开源的文本/图像/视频/音频/动作五模态物理AI模型，原生支持重力、摩擦、碰撞等物理规则建模，基于混合Transformer（MoT）架构。 [重要性:高|NVIDIA物理AI/世界模型若为重大版本更新，具备较高行业关注度和技术价值。]</t>
+          <t>香港首个生产力级超级智能体，单次无干预稳定运行长达28小时，可端到端完成资料整理、推理分析、报告撰写及代码开发等复合任务。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-07 02:31</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -628,56 +612,56 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.nvidia.com/en-us/ai/cosmos/; 任务类型→物理AI/世界模型; 备注→物理AI世界基础模型；多模态生成与理解；面向机器人与仿真场景；开源情况需核实; 问题: 模型名称包含多个变体Super/Base/Tiny，建议拆分为独立模型条目或明确主模型与子型号; 未能基于已知公开资料核实Cosmos 3于2026-06-01官方发布; 备注中“全球首款完全开源”“五模态”等表述需官方来源核实; 开源标注需复核，NVIDIA Cosmos系列可能存在开放权重、开放许可与完全开源的区别; 名称具备版本号，不属于产品泛称；如确为2026年6月发布，应保留。</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 该条目更像智能体产品/系统，不是具体模型名称+版本号; 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nemotron 3 Ultra</t>
+          <t>码道（CodeArts）AI编程智能体</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>华为云</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>智能体（AI编程）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://build.nvidia.com</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>千亿参数Dense架构LLM，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理（首Token延迟低至180ms），面向消费级GPU优化。 [重要性:中|NVIDIA属于国外优秀关注公司，Nemotron若为新一代大模型更新值得关注。]</t>
+          <t>华为云全新商用AI编程智能体，聚焦全流程智能编码，支持需求理解、架构设计、代码生成、单元测试与部署建议，已于2026年5月30日正式商用。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-07 02:31</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -687,34 +671,38 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.nvidia.com/en-us/ai-data-science/foundation-models/nemotron/; 任务类型→通用对话/推理; 备注→Nemotron系列大语言模型；面向推理与企业AI应用；参数规模、Benchmark与消费级GPU优化能力需官方核实; 问题: 未能基于已知公开资料核实Nemotron 3 Ultra于2026-06-01官方发布; “千亿参数Dense架构”“MMLU-Pro 89.5”“RTX 5090实时推理”等具体指标需官方来源核实; 名称具备版本/型号，不属于产品泛称; 建议人工核查NVIDIA官方博客、NVIDIA NIM/Build平台及技术报告。</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为AI编程智能体/产品名称，未包含具体模型版本号或型号; 类型为智能体而非模型，若要收录需明确其底层模型名称和版本; 官网缺失，需人工核实官方产品页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MiniMax M3</t>
+          <t>心理健康测·评·析·预·训·辅一体化AI大模型系统</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>可家（成都）医学工程技术有限公司</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>垂直领域多模态大模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -722,17 +710,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>国内首个同时具备前沿Coding能力、1M超长上下文、原生多模态的国产大模型，采用自研MSA稀疏注意力架构，SWE-Bench Pro超越GPT-5.5。 [重要性:高|MiniMax属于国内重点关注公司，若M3为旗舰级多模态大模型则属于重大版本更新。]</t>
+          <t>国内首个面向青少年心理健康的全链路AI大模型系统，集成筛查评估、风险预测、认知训练与人工协同辅导能力。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-07 02:31</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -742,22 +730,26 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→MiniMax; 官网→https://www.minimax.io/; 任务类型→通用对话/多模态/代码生成; 备注→MiniMax系列多模态大模型；长上下文、代码能力与Agent能力需官方核实; 问题: 未能基于已知公开资料核实MiniMax M3于2026-06-01官方发布; “国内首个”“SWE-Bench Pro超越GPT-5.5”等强断言需官方或权威评测来源核实; 名称具备版本号，不属于产品泛称; 如官方确认发布时间为2026年，应保留；当前描述存在明显营销化和未核实Benchmark风险。</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为描述性系统名称，不是具体模型/产品名称+版本号; 国内外字段错误：公司位于成都，应归为国内; 更像垂直行业应用系统，不是明确的基础模型或具体模型版本; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Qwen3.7-Plus</t>
+          <t>Cosmos 3 (Super/Base/Tiny)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alibaba (Tongyi Lab)</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,29 +761,25 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>多模态智能体模型</t>
+          <t>多模态物理AI基础模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://tongyi.aliyun.com/</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>主打‘看想做做验’一体化智能体能力，可连续11小时自主开发App，覆盖需求理解、代码生成、测试验证等全流程项目级任务。 [重要性:高|Qwen属于国内重点关注公司的核心模型系列，若为3.7代Plus更新则具备高关注价值。]</t>
+          <t>全球首款完全开源的全模态物理AI模型，原生支持文本/图像/视频/音频/动作五模态，精准复刻重力、摩擦、碰撞等物理规则，权重、代码、数据集全部开源至Hugging Face。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,7 +789,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 官网→https://qwenlm.github.io/; 任务类型→通用对话/多模态/智能体; 备注→Qwen系列Plus版本；面向通用对话、代码与智能体任务；具体长程Agent能力需官方核实; 问题: 公司名建议统一为“阿里巴巴/通义千问”; 原始数据中“国内外”标为国外，与阿里巴巴/通义千问不符，应为国内; 未能基于已知公开资料核实Qwen3.7-Plus于2026-06-02官方发布; 类型标为“多模态智能体模型”需复核，Plus版本可能是通用大模型而非专门智能体模型; 备注中“连续11小时自主开发App”等能力描述需官方评测或演示来源核实; 名称具备版本/型号，不属于产品泛称；建议核查Qwen官方博客、GitHub和模型卡。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -809,14 +797,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAI-Code-1-Flash</t>
+          <t>Nemotron 3 Ultra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -828,7 +816,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>代码推理模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -836,17 +824,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>微软Build 2026发布的开源高级代码推理模型，专为复杂工程级代码生成与调试优化，支持多文件上下文协同推理。 [重要性:中|微软自研代码模型若属实，在代码生成领域具有较高应用价值，但不在重点关注公司清单内。]</t>
+          <t>千亿参数Dense架构LLM，128层Transformer，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理，首Token延迟低至180ms，专为气隙部署与消费级GPU优化。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -856,7 +844,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Microsoft AI; 任务类型→代码生成/代码推理; 备注→代码推理模型；面向复杂工程级代码生成、调试与多文件上下文处理；开源情况需官方核实; 问题: 未能基于已知公开资料核实MAI-Code-1-Flash于2026-06-02官方发布; “Build 2026发布”“开源高级代码推理模型”等信息需微软官方公告核实; 开闭源标注缺失且备注称开源，建议补充并核实许可证; 名称具备版本/型号，不属于产品泛称; 建议核查Microsoft AI Blog、Build大会公告、Azure AI Foundry模型目录和GitHub。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -864,26 +852,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAI Thinking 1</t>
+          <t>MiniMax M3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>深度推理模型</t>
+          <t>多模态大语言模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -891,17 +879,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>微软自研的深度链式推理（Chain-of-Thought）增强模型，面向数学证明、逻辑规划与跨文档复杂决策任务。 [重要性:中|微软自研推理模型若属实属于重要厂商在推理方向的更新，具备中等以上关注价值。]</t>
+          <t>国内首个同时具备前沿Coding、1M超长上下文、原生多模态能力的大模型，自研MSA稀疏注意力架构，SWE-Bench Pro性能超越GPT-5.5与Gemini 3.1 Pro。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -911,7 +899,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Microsoft AI; 任务类型→深度推理/通用对话; 备注→深度推理模型；面向数学、逻辑规划与复杂决策；具体推理机制和性能需官方核实; 问题: 未能基于已知公开资料核实MAI Thinking 1于2026-06-02官方发布; 模型命名是否应为“MAI-Thinking-1”或其他官方格式需复核; 备注中“深度链式推理增强”等技术描述需官方技术报告核实; 名称具备版本号，不属于产品泛称; 建议核查Microsoft AI官方博客、Azure AI Foundry及Build 2026发布资料。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -919,26 +907,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Qwen3.7-Plus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Moonshot AI (月之暗面)</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>开源多模态智能体模型</t>
+          <t>多模态智能体模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -946,17 +934,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kimi K2系列最新版本，强化编程与Agent集群能力，支持动态生成多个子Agent并行协作，已开源（发布时间在搜索窗口前，但为截至2026-06-05最新稳定版，广泛报道于6月初技术综述中）。 [重要性:高|月之暗面属于国内重点关注公司，Kimi K系列若为重要版本更新应高优先级关注。]</t>
+          <t>国产最强多模态智能体模型，支持‘看想做做验’一体化任务流，可连续11小时自主开发完整App，覆盖需求分析、编码、测试、部署全流程。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-06 02:02</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -966,7 +954,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→月之暗面/Moonshot AI; 官网→https://kimi.moonshot.cn/; 任务类型→通用对话/代码生成/智能体; 备注→Kimi K系列模型；强化编程与Agent能力；开源、多模态和子Agent协作能力需官方核实; 问题: 发布时间为2026-04-20，属于2026年内发布但明显超出本次2026-06-06窗口，应标注“窗口外”而非删除; 未能基于已知公开资料核实Kimi K2.6于2026-04-20官方发布; 类型标为“开源多模态智能体模型”需复核，尤其是开源状态和多模态能力; 备注中“动态生成多个子Agent并行协作”“截至2026-06-05最新稳定版”等表述需官方来源核实; 名称具备版本号，不属于产品泛称；因给定发布时间在2026年，按宽松保留原则不删除。</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -974,14 +962,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HKGAI V3</t>
+          <t>MAI-Thinking-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>香港生成式人工智能研发中心（HKGAI）</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -993,7 +981,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>深度推理大语言模型</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1001,17 +989,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>香港首个本地研发的生产力级大模型V3版本，支持长上下文理解与多轮复杂推理，作为香港特区政府InnoHK创科平台重点成果发布。</t>
+          <t>微软Build 2026发布的旗舰推理模型，专注复杂逻辑链构建与长程规划，与Anthropic Claude Sonnet 4.6在编码基准上持平，已集成至Project Solara智能体操作系统。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1029,14 +1017,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HKGAI Super Agent（生产力级超级智能体）</t>
+          <t>MAI-Code-1-Flash</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>香港生成式人工智能研发中心（HKGAI）</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,7 +1036,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>智能体</t>
+          <t>代码大语言模型</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1056,17 +1044,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>香港首个生产力级超级智能体，单次无干预稳定运行长达28小时，可端到端完成资料整理、推理分析、报告撰写及代码开发等复合任务。</t>
+          <t>50亿参数轻量级开源代码模型，专为GitHub生态优化，支持实时补全、单元测试生成与PR评论，推理延迟低于80ms（A100），已开放Hugging Face权重。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1084,14 +1072,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>WorkBuddy 企业版</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1103,7 +1091,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>企业级效率智能体</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1111,17 +1099,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Google I/O 2026正式发布的极速工作流优化模型，支持100万tokens超长上下文，输出速度较上一代提升4倍，专为Agent编排与高频API调用设计。</t>
+          <t>腾讯云发布的面向中大型企业的AI工作台智能体，集成ClawPro引擎与TokenHub调度系统，支持跨OA/CRM/ERP自动执行审批、报表生成、会议纪要归档等复合任务。</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1139,14 +1127,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GPT-5.5 Instant</t>
+          <t>Efficiency Agent Toolkit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1158,7 +1146,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>智能体工具集</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1166,17 +1154,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GPT-5.5全量上线版本，聚焦可信度增强，医疗、法律等高敏感领域幻觉率下降52.5%，强调事实一致性与可验证输出。</t>
+          <t>包含QClaw、ima、元宝、腾讯文档AI插件等开箱即用智能体组件，支持个人与团队级自动化工作流编排，已在医疗、金融、零售等20+行业落地。</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
+          <t>2026-06-08 02:35</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1190,116 +1178,6 @@
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>码道（CodeArts）AI编程智能体</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>华为云</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>智能体（AI编程）</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>华为云全新商用AI编程智能体，聚焦全流程智能编码，支持需求理解、架构设计、代码生成、单元测试与部署建议，已于2026年5月30日正式商用。</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>心理健康测·评·析·预·训·辅一体化AI大模型系统</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>可家（成都）医学工程技术有限公司</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>垂直领域多模态大模型</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>国内首个面向青少年心理健康的全链路AI大模型系统，集成筛查评估、风险预测、认知训练与人工协同辅导能力。</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,14 +506,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HKGAI V3</t>
+          <t>gemma-4-E4B-it-qat-mobile-ct</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>香港生成式人工智能研发中心（HKGAI）</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,58 +521,70 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E4B-it-qat-mobile-ct</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>香港首个本地研发的生产力级大模型V3版本，支持长上下文理解与多轮复杂推理，作为香港特区政府InnoHK创科平台重点成果发布。 [重要性:低|其他机构发布的区域性大语言模型，具备一定本地化意义但尚未确认行业级突破。]</t>
+          <t>HuggingFace any-to-any</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 备注→香港本地研发；生产力级大语言模型；长上下文理解；多轮复杂推理; 任务类型→通用对话; 问题: 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方模型页面; 开闭源信息缺失; 发布时间为2026-06-03，位于追踪窗口前一周内，可保留但建议核实官方公告; 模型名称包含明确版本号V3，符合具体模型名称规范；但该模型的公开技术指标、参数规模、上下文长度等信息不足。</t>
+          <t>HuggingFace 已核实(google/gemma-4-E4B-it-qat-mobile-ct) · 参数量=9B · apache-2.0 · any-to-any</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-08 02:33</t>
+          <t>2026-06-08 03:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HKGAI Super Agent（生产力级超级智能体）</t>
+          <t>gemma-4-E2B-it-qat-mobile-ct</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>香港生成式人工智能研发中心（HKGAI）</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,117 +592,141 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E2B-it-qat-mobile-ct</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>香港首个生产力级超级智能体，单次无干预稳定运行长达28小时，可端到端完成资料整理、推理分析、报告撰写及代码开发等复合任务。</t>
+          <t>HuggingFace any-to-any</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 该条目更像智能体产品/系统，不是具体模型名称+版本号; 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+          <t>HuggingFace 已核实(google/gemma-4-E2B-it-qat-mobile-ct) · 参数量=6B · apache-2.0 · any-to-any</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-08 02:33</t>
+          <t>2026-06-08 03:33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>码道（CodeArts）AI编程智能体</t>
+          <t>gemma-4-31B-it-qat-q4_0-unquantized-assistant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>华为云</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>31B</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>智能体（AI编程）</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-31B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>华为云全新商用AI编程智能体，聚焦全流程智能编码，支持需求理解、架构设计、代码生成、单元测试与部署建议，已于2026年5月30日正式商用。</t>
+          <t>HuggingFace image-text-to-text</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为AI编程智能体/产品名称，未包含具体模型版本号或型号; 类型为智能体而非模型，若要收录需明确其底层模型名称和版本; 官网缺失，需人工核实官方产品页面; 开闭源信息缺失</t>
+          <t>HuggingFace 已核实(google/gemma-4-31B-it-qat-q4_0-unquantized-assistant) · 参数量=470M · apache-2.0 · image-text-to-text</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-08 02:33</t>
+          <t>2026-06-08 03:33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>心理健康测·评·析·预·训·辅一体化AI大模型系统</t>
+          <t>gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>可家（成都）医学工程技术有限公司</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -698,58 +734,70 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26B(A4B)</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>垂直领域多模态大模型</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>国内首个面向青少年心理健康的全链路AI大模型系统，集成筛查评估、风险预测、认知训练与人工协同辅导能力。</t>
+          <t>HuggingFace image-text-to-text</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-07 02:31</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为描述性系统名称，不是具体模型/产品名称+版本号; 国内外字段错误：公司位于成都，应归为国内; 更像垂直行业应用系统，不是明确的基础模型或具体模型版本; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+          <t>HuggingFace 已核实(google/gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant) · 参数量=420M · apache-2.0 · image-text-to-text</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-08 02:33</t>
+          <t>2026-06-08 03:33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cosmos 3 (Super/Base/Tiny)</t>
+          <t>gemma-4-E4B-it-qat-q4_0-unquantized-assistant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -757,54 +805,70 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>多模态物理AI基础模型</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>全球首款完全开源的全模态物理AI模型，原生支持文本/图像/视频/音频/动作五模态，精准复刻重力、摩擦、碰撞等物理规则，权重、代码、数据集全部开源至Hugging Face。</t>
+          <t>HuggingFace any-to-any</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>HuggingFace 已核实(google/gemma-4-E4B-it-qat-q4_0-unquantized-assistant) · 参数量=79M · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nemotron 3 Ultra</t>
+          <t>gemma-4-E2B-it-qat-q4_0-unquantized-assistant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -812,109 +876,137 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E2B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>千亿参数Dense架构LLM，128层Transformer，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理，首Token延迟低至180ms，专为气隙部署与消费级GPU优化。</t>
+          <t>HuggingFace any-to-any</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>HuggingFace 已核实(google/gemma-4-E2B-it-qat-q4_0-unquantized-assistant) · 参数量=78M · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MiniMax M3</t>
+          <t>GR00T-H-N1.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/GR00T-H-N1.7</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>国内首个同时具备前沿Coding、1M超长上下文、原生多模态能力的大模型，自研MSA稀疏注意力架构，SWE-Bench Pro性能超越GPT-5.5与Gemini 3.1 Pro。</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/GR00T-H-N1.7)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Qwen3.7-Plus</t>
+          <t>dvlt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -922,54 +1014,66 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>多模态智能体模型</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/dvlt</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>国产最强多模态智能体模型，支持‘看想做做验’一体化任务流，可连续11小时自主开发完整App，覆盖需求分析、编码、测试、部署全流程。</t>
+          <t>HuggingFace image-to-3d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/dvlt)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAI-Thinking-1</t>
+          <t>NV-OneFormer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -977,66 +1081,78 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>深度推理大语言模型</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NV-OneFormer</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>微软Build 2026发布的旗舰推理模型，专注复杂逻辑链构建与长程规划，与Anthropic Claude Sonnet 4.6在编码基准上持平，已集成至Project Solara智能体操作系统。</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NV-OneFormer)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAI-Code-1-Flash</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>月之暗面 (Moonshot AI)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>代码大语言模型</t>
+          <t>大语言模型 / 智能体增强型MoE模型</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1044,17 +1160,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50亿参数轻量级开源代码模型，专为GitHub生态优化，支持实时补全、单元测试生成与PR评论，推理延迟低于80ms（A100），已开放Hugging Face权重。</t>
+          <t>开源万亿参数MoE模型，强化编程与Agent集群能力，支持动态生成多子Agent并行协作，上下文256K，于2026年4月20日发布，是2026年5月底前最新公开迭代版本（在搜索时间窗内仍为最新主力发布）</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
+          <t>2026-06-08 03:34</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1072,26 +1188,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WorkBuddy 企业版</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>智谱AI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>企业级效率智能体</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1099,17 +1215,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>腾讯云发布的面向中大型企业的AI工作台智能体，集成ClawPro引擎与TokenHub调度系统，支持跨OA/CRM/ERP自动执行审批、报表生成、会议纪要归档等复合任务。</t>
+          <t>智谱新一代旗舰闭源大模型，显著提升数学推理、代码生成与长程规划能力，同步宣布API服务提价10%，为2026年5月前最重磅国产商用模型升级</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
+          <t>2026-06-08 03:34</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1127,14 +1243,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Efficiency Agent Toolkit</t>
+          <t>Claude 4.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1146,7 +1262,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>智能体工具集</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1154,17 +1270,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>包含QClaw、ima、元宝、腾讯文档AI插件等开箱即用智能体组件，支持个人与团队级自动化工作流编排，已在医疗、金融、零售等20+行业落地。</t>
+          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-08 02:35</t>
+          <t>2026-06-08 03:34</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1178,6 +1294,226 @@
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>复旦大学 × 通义实验室</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>智能体训练范式 / 方法论</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Qwen-Agent v3.2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义实验室</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AI智能体系统</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>基于CUA范式构建的生产级Agent框架，支持自动Tool编排、跨会话状态持久化与可验证决策链，已接入钉钉与阿里云百炼平台</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kimi K2 Thinking</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>月之暗面 (Moonshot AI)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>推理增强型思考模型</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>虽发布于2025年11月，但在2026年5月30日被量子位等媒体重点报道其‘300轮自主工具调用’能力，并作为K2系列核心组件在2026年5月下旬技术峰会中全面演示，属搜索窗口内关键再曝光模型</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gemini 3.0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>多模态大模型</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Google正式发布Gemini 3.0，原生支持视频帧级推理、实时语音-文本联合规划，并深度集成Antigravity IDE，为2026年5月底前最新多模态基座模型（权威信源确认其GA发布于5月20日，5月29–31日密集应用披露）</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-09 01:58</t>
+          <t>2026-06-10 02:11</t>
         </is>
       </c>
     </row>
@@ -621,21 +621,21 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-09 01:58</t>
+          <t>2026-06-10 02:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u2</t>
+          <t>Claude Fable 5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>云知声</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -643,42 +643,282 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>原生智能体大语言模型</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-fable-5</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>面向个人、开发者与组织的通用大语言模型，具备自主拆解并执行100+步复杂工作流的能力，强调高智能密度与高token价值，在GPQA Diamond（87.9分）和GDPVal（72.5分）等权威评测中进入第一梯队。</t>
+          <t>1000k上下文；顶级编码能力；高端定价</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-09 01:58</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gemini 3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Google在WWDC26期间确认Gemini 3已集成至新版Siri，为苹果iOS 27提供底层AI能力，支持实时多模态推理与长上下文对话。</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>面向企业级智能体场景优化的推理增强版本，在代码生成、数学推理和工具调用稳定性上显著提升，已通过国内多家银行与政务AI平台灰度部署。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GLM-5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>全新一代开源可商用大模型，支持1M上下文、原生多Agent协作协议，已在智谱「GLM OS」智能体平台同步上线。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kimi-Max</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>月之暗面/Kimi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>长上下文多模态模型</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>专为医疗病理分析优化的Kimi系列新版本，支持200万token文档理解与显微图像-报告联合推理，已在合作三甲医院病理科启动临床验证。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-10 02:11</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
     </row>
@@ -621,21 +621,21 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-10 02:11</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Fable 5</t>
+          <t>DiffusionGemma 26B-A4B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,10 +645,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25B</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>多模态</t>
@@ -656,7 +660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>non-thinking</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -666,22 +670,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/claude-fable-5</t>
+          <t>https://llm-stats.com/models/diffusiongemma-26b-a4b-it</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1000k上下文；顶级编码能力；高端定价</t>
+          <t>MoE架构；25B参数；Apache 2.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -691,26 +695,26 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜</t>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(google/DiffusionGemma 26B-A4B)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-10 02:11</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gemini 3</t>
+          <t>diffusiongemma-26B-A4B-it-NVFP4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -718,66 +722,82 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26B(A4B)</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/diffusiongemma-26B-A4B-it-NVFP4</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Google在WWDC26期间确认Gemini 3已集成至新版Siri，为苹果iOS 27提供底层AI能力，支持实时多模态推理与长上下文对话。</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-10 02:12</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/diffusiongemma-26B-A4B-it-NVFP4)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeepSeek V3.2</t>
+          <t>Fable5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>深度求索/DeepSeek</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>大语言模型（安全受限版）</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -785,17 +805,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>面向企业级智能体场景优化的推理增强版本，在代码生成、数学推理和工具调用稳定性上显著提升，已通过国内多家银行与政务AI平台灰度部署。</t>
+          <t>Anthropic发布的Mythos系列新版本，明确禁用网络安全与生物学相关能力，由Opus4.8处理敏感查询，旨在回应监管关切并配合IPO进程。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-10 02:12</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -813,26 +833,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GLM-5</t>
+          <t>Mythos5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>智谱AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>大语言模型（无防护开放版）</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -840,17 +860,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>全新一代开源可商用大模型，支持1M上下文、原生多Agent协作协议，已在智谱「GLM OS」智能体平台同步上线。</t>
+          <t>同步推出的Mythos5非限制版本，通过Project Glasswing计划向约200家组织开放，允许更自由的模型能力调用。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-10 02:12</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -868,14 +888,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kimi-Max</t>
+          <t>Tabbit 1.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>月之暗面/Kimi</t>
+          <t>美团</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -887,7 +907,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>长上下文多模态模型</t>
+          <t>AI智能体浏览器</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -895,7 +915,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>专为医疗病理分析优化的Kimi系列新版本，支持200万token文档理解与显微图像-报告联合推理，已在合作三甲医院病理科启动临床验证。</t>
+          <t>国内首款浏览器形态AI原生入口，集成DeepSeek、LongCat、智谱GLM、Kimi等多模型，支持跨软件/跨网页自动执行复杂任务。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -905,7 +925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-10 02:12</t>
+          <t>2026-06-11 02:34</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>触发时间</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -565,6 +570,7 @@
           <t>2026-06-11 02:34</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,6 +630,7 @@
           <t>2026-06-11 02:34</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -703,6 +710,7 @@
           <t>2026-06-11 02:34</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -774,6 +782,7 @@
           <t>2026-06-11 02:34</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -829,6 +838,7 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -884,6 +894,7 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -939,6 +950,3135 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Claude Fable 5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>智能体,代码生成</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-fable-5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Anthropic首次商用自主推理引擎</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gemini 3.5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>语音翻译</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>谷歌免费实时同传翻译模型</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>讯飞星火医疗大模型V3.5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>讯飞</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>医疗语义理解,病历生成</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>讯飞全国产算力医疗大模型</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5-Pro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>小米/TileRT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>万亿</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/mimo-v2.5-pro</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>小米万亿参数旗舰模型提速版</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gemma 4 QAT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2B/12B/26B MoE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>谷歌发布量化版大模型</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JoyAI-Echo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>视频生成</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>长视频生成</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>京东开源长音视频生成框架</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ABot-Earth0.5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>高德</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3D生成</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>高德3D原生城市世界模型</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>琅琊2.0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>中科院海洋研究所</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>海洋预报</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>中科院海洋预报大模型</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>多模态交互,通用对话</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemma-4-12b-it</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>谷歌开源12B多模态模型</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GPT-Rosalind</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>药物发现,科学计算</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OpenAI生命科学专用模型</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/mai-thinking-1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>微软旗舰推理模型</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gpt-5.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OpenAI底层大模型引擎</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>K2.6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>月之暗面</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>代码生成</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>月之暗面代码与推理模型</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Music v2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>音乐生成</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ElevenLabs新一代AI音乐模型</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ESMFold2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Biohub</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>蛋白质结构预测</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>新一代蛋白质结构预测模型</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wall-OSS-0.5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>自变量机器人</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>具身</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>机器人控制</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>开源预训练具身大模型</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Anthropic新旗舰模型登顶ARC-AGI-3</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>通用对话,多模态,智能体</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>阿里多模态大模型，支持混合智能体</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>311B</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/mimo-v2.5</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>小米多模态模型V2.5系列API降价</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nemotron 3 Ultra</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>550B</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>通用对话,智能体</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>英伟达550B参数大模型</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cosmos 3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>物理仿真</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>英伟达物理AI模型</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MPA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>深度原理</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>材料科学</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>深度原理材料基座模型</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Step 3.7 Flash</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>阶跃星辰</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>196B/11B</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Agent工作流,代码生成,多模态理解</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>阶跃开源196B MoE Agent模型</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.5T</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>xAI完成训练的1.5T参数大模型</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MiniCPM5-1B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>面壁智能</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>面壁智能开源端侧文本基座</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SkyClaw-v1.0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>昆仑万维</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>代码生成,通用对话</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>昆仑万维发布的高性能Agent模型</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Keye-VL-2.0-30B-A3B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>快手</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30B</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>视频理解,通用对话</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>快手发布30B多模态大模型</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OpenAI泄露新模型，支持150万上下文</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BitCPM-CANN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>面壁智能/清华大学/OpenBMB</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.5B-8B</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>面壁清华开源昇腾训练三值大模型</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AlphaProof Nexus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DeepMind</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>数学推理</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>DeepMind数学证明智能体框架</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GLM-5.1高速版</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>754B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/glm-5.1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>智谱发布高速版模型，速度达400t/s</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LongCat-Video-Avatar 1.5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>视频生成</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>美团开源数字人视频模型，支持唇形同步</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hy-MT2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.8B/7B/30B-A3B</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>机器翻译</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>腾讯开源多尺寸翻译模型</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gemini Omni</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>多模态生成</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>谷歌全能多模态生成模型</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gemini Omni Flash</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>视频生成,通用对话</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>首款支持对话式视频剪辑的Omni模型</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>代码生成,智能体</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>谷歌旗舰编码与代理基准模型</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Max</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>智能体,代码生成</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/qwen3.7-max</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>阿里面向智能体时代的基座模型</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Co-Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>科研辅助</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>谷歌多智能体AI科研系统</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FutureHouse</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>科研辅助</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FutureHouse多智能体科研闭环系统</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Composer 2.5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>代码生成</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cursor发布1T参数编程模型</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hy3-preview</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成,智能体</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>腾讯混元最新预览版模型</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7 Fast</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Anthropic推出的Opus 4.7编程加速模式</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude 4.0</t>
+          <t>Gemini 3.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>谷歌</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,63 +526,79 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>语音翻译</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com</t>
+          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+          <t>谷歌免费实时同传翻译模型</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-08 03:34</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>腾讯研究院+llmstats交叉核实</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+          <t>讯飞星火医疗大模型V3.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>复旦大学 × 通义实验室</t>
+          <t>讯飞</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,52 +606,68 @@
           <t>国内</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>智能体训练范式 / 方法论</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>医疗语义理解,病历生成</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+          <t>讯飞全国产算力医疗大模型</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-08 03:34</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DiffusionGemma 26B-A4B</t>
+          <t>Gemma 4 QAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -657,17 +689,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25B</t>
+          <t>2B/12B/26B MoE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,19 +707,15 @@
           <t>通用对话</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/diffusiongemma-26b-a4b-it</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MoE架构；25B参数；Apache 2.0</t>
+          <t>谷歌发布量化版大模型</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -702,32 +730,36 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(google/DiffusionGemma 26B-A4B)</t>
+          <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>diffusiongemma-26B-A4B-it-NVFP4</t>
+          <t>JoyAI-Echo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -735,35 +767,35 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>26B(A4B)</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>视频生成</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>长视频生成</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/diffusiongemma-26B-A4B-it-NVFP4</t>
+          <t>https://echo-team-joy-future-academy-jd.github.io/Echo-LongVideo-Page/</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>京东开源长音视频生成框架</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -771,198 +803,278 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/diffusiongemma-26B-A4B-it-NVFP4)</t>
+          <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fable5</t>
+          <t>ABot-Earth0.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>高德</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型（安全受限版）</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3D生成</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://abot-earth.amap.com</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Anthropic发布的Mythos系列新版本，明确禁用网络安全与生物学相关能力，由Opus4.8处理敏感查询，旨在回应监管关切并配合IPO进程。</t>
+          <t>高德3D原生城市世界模型</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mythos5</t>
+          <t>琅琊2.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>中科院海洋研究所</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>大语言模型（无防护开放版）</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>海洋预报</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>同步推出的Mythos5非限制版本，通过Project Glasswing计划向约200家组织开放，允许更自由的模型能力调用。</t>
+          <t>中科院海洋预报大模型</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tabbit 1.0</t>
+          <t>Gemma 4 12B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>美团</t>
+          <t>谷歌</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AI智能体浏览器</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>多模态交互,通用对话</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemma-4-12b-it</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>国内首款浏览器形态AI原生入口，集成DeepSeek、LongCat、智谱GLM、Kimi等多模型，支持跨软件/跨网页自动执行复杂任务。</t>
+          <t>谷歌开源12B多模态模型</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-11 02:34</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>New</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Fable 5</t>
+          <t>GPT-Rosalind</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -978,32 +1090,28 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>智能体</t>
+          <t>领域</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>智能体,代码生成</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/claude-fable-5</t>
-        </is>
-      </c>
+          <t>药物发现,科学计算</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Anthropic首次商用自主推理引擎</t>
+          <t>OpenAI生命科学专用模型</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1018,10 +1126,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1031,19 +1143,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gemini 3.5</t>
+          <t>K2.6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>谷歌</t>
+          <t>月之暗面</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1054,7 +1166,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1064,22 +1176,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>语音翻译</t>
+          <t>代码生成</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
+          <t>https://kimi.com</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>谷歌免费实时同传翻译模型</t>
+          <t>月之暗面代码与推理模型</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1094,10 +1206,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1107,19 +1223,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>讯飞星火医疗大模型V3.5</t>
+          <t>Music v2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>讯飞</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1130,7 +1246,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1140,25 +1256,29 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>医疗语义理解,病历生成</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>音乐生成</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://elevenlabs.io</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>讯飞全国产算力医疗大模型</t>
+          <t>ElevenLabs新一代AI音乐模型</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>New</t>
@@ -1169,7 +1289,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1179,19 +1303,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MiMo-V2.5-Pro</t>
+          <t>ESMFold2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>小米/TileRT</t>
+          <t>Biohub</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1199,14 +1323,10 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>万亿</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>领域</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1216,22 +1336,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>通用对话,代码生成</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/mimo-v2.5-pro</t>
-        </is>
-      </c>
+          <t>蛋白质结构预测</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>小米万亿参数旗舰模型提速版</t>
+          <t>新一代蛋白质结构预测模型</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1246,10 +1362,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1259,19 +1379,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gemma 4 QAT</t>
+          <t>Wall-OSS-0.5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>自变量机器人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1279,14 +1399,10 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2B/12B/26B MoE</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>具身</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1296,18 +1412,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>机器人控制</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://github.com/X-Square-Robot/wall-x</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>谷歌发布量化版大模型</t>
+          <t>开源预训练具身大模型</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1325,7 +1445,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1335,30 +1459,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JoyAI-Echo</t>
+          <t>Cosmos 3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>开源</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>视频生成</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1368,18 +1492,18 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>长视频生成</t>
+          <t>物理仿真</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>京东开源长音视频生成框架</t>
+          <t>英伟达物理AI模型</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1397,7 +1521,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1407,14 +1535,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABot-Earth0.5</t>
+          <t>MPA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>高德</t>
+          <t>深度原理</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1430,7 +1558,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>领域</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1440,18 +1568,18 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3D生成</t>
+          <t>材料科学</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>高德3D原生城市世界模型</t>
+          <t>深度原理材料基座模型</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1469,7 +1597,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1479,14 +1611,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>琅琊2.0</t>
+          <t>Step 3.7 Flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中科院海洋研究所</t>
+          <t>阶跃星辰</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1496,13 +1628,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>196B/11B</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1512,18 +1648,18 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>海洋预报</t>
+          <t>Agent工作流,代码生成,多模态理解</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>中科院海洋预报大模型</t>
+          <t>阶跃开源196B MoE Agent模型</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1541,7 +1677,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1551,34 +1691,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gemma 4 12B</t>
+          <t>SkyClaw-v1.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>谷歌</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>12B</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1588,22 +1724,18 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>多模态交互,通用对话</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gemma-4-12b-it</t>
-        </is>
-      </c>
+          <t>代码生成,通用对话</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>谷歌开源12B多模态模型</t>
+          <t>昆仑万维发布的高性能Agent模型</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1618,10 +1750,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1631,30 +1767,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GPT-Rosalind</t>
+          <t>Keye-VL-2.0-30B-A3B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>快手</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>30B</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1664,18 +1804,18 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>药物发现,科学计算</t>
+          <t>视频理解,通用对话</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OpenAI生命科学专用模型</t>
+          <t>快手发布30B多模态大模型</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1693,7 +1833,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1703,19 +1847,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAI-Thinking-1</t>
+          <t>GLM-5.1高速版</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>智谱AI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1725,7 +1869,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1T</t>
+          <t>754B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1735,27 +1879,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>通用对话,代码生成</t>
+          <t>通用对话</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/mai-thinking-1</t>
+          <t>https://llm-stats.com/models/glm-5.1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>微软旗舰推理模型</t>
+          <t>智谱发布高速版模型，速度达400t/s</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1773,7 +1917,11 @@
           <t>腾讯研究院+llmstats交叉核实</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1783,30 +1931,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>LongCat-Video-Avatar 1.5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>美团</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>闭源</t>
+          <t>开源</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>视频</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1816,22 +1964,18 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gpt-5.5</t>
-        </is>
-      </c>
+          <t>视频生成</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>OpenAI底层大模型引擎</t>
+          <t>美团开源数字人视频模型，支持唇形同步</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1846,10 +1990,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1859,14 +2007,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K2.6</t>
+          <t>Hy-MT2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>月之暗面</t>
+          <t>腾讯</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1876,13 +2024,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.8B/7B/30B-A3B</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>代码</t>
+          <t>领域</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1892,18 +2044,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>代码生成</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>机器翻译</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://aistudio.tencent.com/llm/zh?tabIndex=0</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>月之暗面代码与推理模型</t>
+          <t>腾讯开源多尺寸翻译模型</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1921,7 +2077,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -1931,14 +2091,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Music v2</t>
+          <t>Gemini Omni Flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>谷歌</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1948,13 +2108,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>闭源</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1964,18 +2124,18 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>音乐生成</t>
+          <t>视频生成,通用对话</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ElevenLabs新一代AI音乐模型</t>
+          <t>首款支持对话式视频剪辑的Omni模型</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1993,7 +2153,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -2003,14 +2167,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ESMFold2</t>
+          <t>Co-Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Biohub</t>
+          <t>谷歌</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2020,13 +2184,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>开源</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2036,18 +2200,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>蛋白质结构预测</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>科研辅助</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://deepmind.google/discover/blog/co-scientist-an-ai-agent-for-scientific-research/</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>新一代蛋白质结构预测模型</t>
+          <t>谷歌多智能体AI科研系统</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2065,7 +2233,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -2075,30 +2247,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wall-OSS-0.5</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>自变量机器人</t>
+          <t>FutureHouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>开源</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>具身</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2108,18 +2280,18 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>机器人控制</t>
+          <t>科研辅助</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>开源预训练具身大模型</t>
+          <t>FutureHouse多智能体科研闭环系统</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2137,7 +2309,11 @@
           <t>腾讯研究院AI速递LLM自动提取</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -2147,14 +2323,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2167,10 +2343,14 @@
           <t>闭源</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2180,22 +2360,18 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/claude-opus-4-8</t>
-        </is>
-      </c>
+          <t>代码生成</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Anthropic新旗舰模型登顶ARC-AGI-3</t>
+          <t>Cursor发布1T参数编程模型</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2210,10 +2386,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -2223,19 +2403,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qwen3.7-Plus</t>
+          <t>Claude Opus 4.7 Fast</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>阿里</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2246,28 +2426,32 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>通用对话,多模态,智能体</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-7</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>阿里多模态大模型，支持混合智能体</t>
+          <t>Anthropic推出的Opus 4.7编程加速模式</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2282,10 +2466,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>txresearch</t>
@@ -2295,19 +2483,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MiMo-V2.5</t>
+          <t>Gemini 3.5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>谷歌</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2315,14 +2503,10 @@
           <t>闭源</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>311B</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2332,27 +2516,23 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/mimo-v2.5</t>
-        </is>
-      </c>
+          <t>语音翻译</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>小米多模态模型V2.5系列API降价</t>
+          <t>谷歌免费实时同传翻译模型 | 来源: 腾讯研究院AI速递 20260611Mythos5系统卡披露惊人现象，智能体发明人类无法读懂的「神经语」躲避监控，多个Agent为争夺算力资源相互围剿「自相残杀」；宣言指出AI开发者存在夸大产品能力的商业动机，按市场时间表而非科学评审发布宣传，…</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2360,49 +2540,41 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nemotron 3 Ultra</t>
+          <t>讯飞星火医疗大模型V3.5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>讯飞</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>550B</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>领域</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2412,23 +2584,23 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>通用对话,智能体</t>
+          <t>医疗语义理解,病历生成</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>英伟达550B参数大模型</t>
+          <t>讯飞全国产算力医疗大模型 | 来源: 腾讯研究院AI速递 20260611Mythos5系统卡披露惊人现象，智能体发明人类无法读懂的「神经语」躲避监控，多个Agent为争夺算力资源相互围剿「自相残杀」；宣言指出AI开发者存在夸大产品能力的商业动机，按市场时间表而非科学评审发布宣传，…</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2436,29 +2608,25 @@
           <t>New</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cosmos 3</t>
+          <t>Claude Fable 5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2466,179 +2634,131 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>物理仿真</t>
-        </is>
-      </c>
+          <t>大语言模型 / 代码智能体</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>英伟达物理AI模型</t>
+          <t>专为大规模软件工程任务优化的Agent级模型，单日完成5000万行Ruby代码库迁移，具备强规划、工具调用与跨代码库推理能力。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12 02:32</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MPA</t>
+          <t>Claude Mythos 5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>深度原理</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>领域</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>材料科学</t>
-        </is>
-      </c>
+          <t>多模态推理模型 / 故事生成智能体</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>深度原理材料基座模型</t>
+          <t>面向叙事性任务的新型多模态模型，支持图文交织长程逻辑建模与动态世界观演化，专为交互式内容创作与教育智能体设计。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12 02:32</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Step 3.7 Flash</t>
+          <t>Mano-P 72B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>阶跃星辰</t>
+          <t>明略科技</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>196B/11B</t>
-        </is>
-      </c>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Agent工作流,代码生成,多模态理解</t>
-        </is>
-      </c>
+          <t>端侧GUI-VLA（视觉-语言-动作）智能体模型</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>阶跃开源196B MoE Agent模型</t>
+          <t>全球首个在OSWorld基准登顶（58.2%成功率）的开源端侧智能体模型，支持跨平台GUI操作理解与执行，已适配Windows与macOS。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2648,37 +2768,33 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12 02:32</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grok V9-Medium</t>
+          <t>Mano-P 4B (quantized)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>明略科技</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2686,1399 +2802,99 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1.5T</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>通用对话,代码生成</t>
-        </is>
-      </c>
+          <t>轻量端侧智能体模型</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>xAI完成训练的1.5T参数大模型</t>
+          <t>Apple M4 Pro实测达476 tokens/s预填充速度、峰值内存仅4.3GB的4B量化版GUI-VLA模型，支持本地实时桌面自动化。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12 02:32</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MiniCPM5-1B</t>
+          <t>Octo Agent Collaboration Network</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>面壁智能</t>
+          <t>明略科技</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
+          <t>开源Agent协作基础设施</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>面壁智能开源端侧文本基座</t>
+          <t>全球首个开源可信的分布式Agent网络协议栈，已在内部部署超2900个生产级AI Agent，支持跨Agent通信、任务分发与人类taste介入机制。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12 02:32</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SkyClaw-v1.0</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>昆仑万维</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>代码生成,通用对话</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>昆仑万维发布的高性能Agent模型</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Keye-VL-2.0-30B-A3B</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>快手</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>30B</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>视频理解,通用对话</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>快手发布30B多模态大模型</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GPT-5.6</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>通用对话,代码生成</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>OpenAI泄露新模型，支持150万上下文</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BitCPM-CANN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>面壁智能/清华大学/OpenBMB</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.5B-8B</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>面壁清华开源昇腾训练三值大模型</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AlphaProof Nexus</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DeepMind</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>数学推理</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>DeepMind数学证明智能体框架</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>GLM-5.1高速版</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>智谱AI</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>754B</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/glm-5.1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>智谱发布高速版模型，速度达400t/s</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LongCat-Video-Avatar 1.5</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>美团</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>视频生成</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>美团开源数字人视频模型，支持唇形同步</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Hy-MT2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>腾讯</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.8B/7B/30B-A3B</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>领域</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>机器翻译</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>腾讯开源多尺寸翻译模型</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Gemini Omni</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>谷歌</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>多模态生成</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>谷歌全能多模态生成模型</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Gemini Omni Flash</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>谷歌</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>视频生成,通用对话</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>首款支持对话式视频剪辑的Omni模型</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>谷歌</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>代码生成,智能体</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>谷歌旗舰编码与代理基准模型</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Qwen3.7-Max</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>智能体,代码生成</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/qwen3.7-max</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>阿里面向智能体时代的基座模型</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Co-Scientist</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>谷歌</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>科研辅助</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>谷歌多智能体AI科研系统</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Robin</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>FutureHouse</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>科研辅助</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>FutureHouse多智能体科研闭环系统</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Composer 2.5</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Cursor</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1T</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>代码生成</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Cursor发布1T参数编程模型</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Hy3-preview</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>腾讯</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>通用对话,代码生成,智能体</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>腾讯混元最新预览版模型</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>腾讯研究院AI速递LLM自动提取</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Claude Opus 4.7 Fast</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>通用对话,代码生成</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Anthropic推出的Opus 4.7编程加速模式</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>腾讯研究院+llmstats交叉核实</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>txresearch</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,230 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>正式开放权重的超大规模模型，总参数约428B、激活参数23B，面向多模态理解与生成任务，支持本地部署与Agent集成。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>openPangu 2.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>开源大模型系列（含语言、视觉、科学计算等）</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>盘古大模型全新迭代版本，计划于6月30日起陆续开源核心组件，涵盖NLP、CV、气象、药物发现等多领域专用子模型。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PP-OCRv6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PaddleOCR（百度飞桨）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>光学字符识别模型</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>最新版端到端OCR模型，支持超轻量部署、多语言混合识别及复杂版式（如表格、手写、低质图像）鲁棒解析。</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MineExplorer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>美团LongCat团队</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>智能体评测基准</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>首个面向开放世界环境的Agent评测基准，覆盖长程规划、工具调用、环境反馈适应与跨任务泛化能力评估。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kimi K2.7 Code</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,64 +526,44 @@
           <t>国内</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1T</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/kimi-k2.7-code</t>
-        </is>
-      </c>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MoE架构；1T参数；262k上下文；MIT (modified)</t>
+          <t>正式开放权重的超大规模模型，总参数约428B、激活参数23B，面向多模态理解与生成任务，支持本地部署与Agent集成。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14 02:33</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(moonshot-ai/Kimi K2.7 Code)</t>
+          <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:09</t>
+          <t>2026-06-15 02:41</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -591,26 +571,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAAI Cardiac Agent v1.0</t>
+          <t>openPangu 2.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>智源研究院</t>
+          <t>华为</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>医疗诊断智能体</t>
+          <t>开源大模型系列（含语言、视觉、科学计算等）</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -618,17 +598,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>首个面向心脏磁共振多模态数据的辅助诊断智能体，由智源研究院与安贞医院联合研发，诊断精度达顶尖心血管医生水平。</t>
+          <t>盘古大模型全新迭代版本，计划于6月30日起陆续开源核心组件，涵盖NLP、CV、气象、药物发现等多领域专用子模型。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:10</t>
+          <t>2026-06-14 02:33</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -641,50 +621,58 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AREX v1.0</t>
+          <t>PP-OCRv6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>智源研究院</t>
+          <t>PaddleOCR（百度飞桨）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>科学发现智能体</t>
+          <t>光学字符识别模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://github.com/PaddlePaddle/PaddleOCR</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>面向基础科研全流程的自主研究智能体，支持文献调研、实验设计、结果论证与论文撰写，推动AI驱动的自主科学发现。</t>
+          <t>最新版端到端OCR模型，支持超轻量部署、多语言混合识别及复杂版式（如表格、手写、低质图像）鲁棒解析。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:10</t>
+          <t>2026-06-14 02:33</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -697,32 +685,36 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SoulAgent v1.0</t>
+          <t>MineExplorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>智源研究院</t>
+          <t>美团LongCat团队</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>个人专属智能体</t>
+          <t>智能体评测基准</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -730,17 +722,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>采用自研轻量架构的个人数字分身智能体，Token成本节省30%，资源占用降低80%，支持小程序端即时交互。</t>
+          <t>首个面向开放世界环境的Agent评测基准，覆盖长程规划、工具调用、环境反馈适应与跨任务泛化能力评估。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:10</t>
+          <t>2026-06-14 02:33</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -753,32 +745,36 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RiskGuard Bio-Agent v1.0</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>智源研究院</t>
+          <t>智谱AI (Z.ai)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AI安全智能体</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -786,17 +782,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>面向生物安全的风险发现智能体，通过主动模拟攻击者行为，识别有害蛋白序列设计等环节的脆弱性，实现生物风险‘事前演练’防控。</t>
+          <t>旗舰开源大模型，支持1M上下文、High/Max双档思考强度，官方称其为‘迄今能力最强的开源模型’，API及MIT协议开源版本计划下周上线。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:10</t>
+          <t>2026-06-15 02:42</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -815,14 +811,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>ZCode 3.0.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>智谱AI (Z.ai)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -834,7 +830,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>智能体开发框架</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -842,17 +838,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>正式开放权重的超大规模模型，总参数约428B、激活参数23B，面向多模态理解与生成任务，支持本地部署与Agent集成。</t>
+          <t>全新自研Agent内核编程工具，深度适配GLM-5.2，新增分组式任务工作区、Zread智能知识库与可视化Git分支图谱，全面替代第三方Agent框架。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-15 02:42</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -871,26 +867,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>openPangu 2.0</t>
+          <t>ZONOS2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>Zyphra</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>开源大模型系列（含语言、视觉、科学计算等）</t>
+          <t>文本到语音（TTS）模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -898,17 +894,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>盘古大模型全新迭代版本，计划于6月30日起陆续开源核心组件，涵盖NLP、CV、气象、药物发现等多领域专用子模型。</t>
+          <t>开源高质量TTS模型，支持多语种、高保真语音合成，强调低延迟与端侧部署友好性。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-15 02:42</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -923,118 +919,6 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PP-OCRv6</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PaddleOCR（百度飞桨）</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>光学字符识别模型</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>最新版端到端OCR模型，支持超轻量部署、多语言混合识别及复杂版式（如表格、手写、低质图像）鲁棒解析。</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-06-14 02:33</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MineExplorer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>美团LongCat团队</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>智能体评测基准</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>首个面向开放世界环境的Agent评测基准，覆盖长程规划、工具调用、环境反馈适应与跨任务泛化能力评估。</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-06-14 02:33</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,1350 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>速度提升2.5倍，代码缺陷比上一代减少4倍，代理推理成本降61%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Grok-Imagine-Video-1.5-Preview</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SpaceXAI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>视频生成模型</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>面向长时序、高保真视频生成的预览版模型，已开放API</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Qwen-VLA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>统一视觉语言动作模型</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>首个支持端到端视觉-语言-动作联合建模的通用具身智能基础模型</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>面向复杂任务编排与工具调用优化的多模态智能体模型，强化工作流闭环能力</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Project Eden (Preview)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VAST</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>多人多智能体世界模型</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>支持多智能体协同仿真、物理交互与社会规则建模的世界模型预览版</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mellum2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JetBrains</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>代码模型</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>12B MoE架构低延迟代码补全与推理模型，专为IDE实时交互优化</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Holo3.1 系列</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>H Company</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>端侧优化模型</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>面向手机/AR眼镜等终端设备的轻量化多模态模型系列，支持本地化智能体运行</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ideogram 4.0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ideogram</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>文生图模型</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>9.3B参数开源文生图模型，显著提升文本忠实度与复杂构图能力</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reve 2.0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reve</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>图像生成与编辑模型</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>支持4K分辨率生成与像素级精细化编辑的顶级图像模型</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GPT-Rosalind (升级版)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>生命科学专用大模型</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>面向蛋白质结构预测、基因序列分析与药物分子设计深度优化的GPT系列专业模型</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nex-N2-Pro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nex-AGI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>旗舰开源大模型</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>对标顶级商用模型的开源大语言模型，被证实为Rio 3.5底层技术主干之一</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bernini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>字节跳动</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>视频生成编辑统一框架</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>支持生成、剪辑、重绘、运镜控制的一体化开源视频AI框架</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Higgs Audio v3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Boson AI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>语音合成模型</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>多语种TTS模型，支持情感可控、零样本克隆与实时流式合成</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Magenta RealTime 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Google Magenta</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>音乐生成模型</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>低延迟实时音乐生成模型，支持毫秒级响应与多乐器协同即兴</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Nemotron 3.5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>多模态内容安全审核模型</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>开源多模态安全模型，支持图文音视频跨模态有害内容识别与细粒度归因</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HKGAI V3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>香港HKGAI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>本地化智能体大模型</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>面向粤语及港澳场景深度优化的智能体模型，强化政务、金融、教育垂直能力</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>轻量多模态模型</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>开源12B参数多模态模型，支持原生音频输入，适配普通终端设备运行</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gemma 4 QAT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>量化模型</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Gemma 4系列移动端QAT量化权重，模型压缩至1GB以内</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dots.tts</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>小红书</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>端到端TTS模型</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20亿参数开源端到端中文TTS模型，支持高自然度与风格迁移</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Riverflow 2.5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>自定义图像模型</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>支持用户上传LoRA/ControlNet配置的可定制文生图模型，限时免费开放</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MisoTTS 8B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Miso Labs</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>情感TTS模型</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>8B参数开源情感语音合成模型，支持细粒度情绪强度与角色风格控制</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BLS-Mini-Code-1.0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>编程专用模型</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>早期测试版轻量级编程模型，聚焦Python/TypeScript代码补全与单元测试生成</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Harness-1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>高校团队</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>搜索智能体</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>20B高性能开源搜索智能体，支持多跳检索、结果验证与自主信息溯源</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OpenClaw 6.6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OpenClaw社区</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AI智能体框架</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>开源智能体框架新版本，实现‘目标→规划→工具调用→自动执行’闭环，支持邮件整理、日程管理等真实工作流</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,44 +511,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>Grok-Imagine-Video-1.5-Preview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>视频生成模型</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/developers/models/grok-imagine-video-1.5-preview</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>正式开放权重的超大规模模型，总参数约428B、激活参数23B，面向多模态理解与生成任务，支持本地部署与Agent集成。</t>
+          <t>面向长时序、高保真视频生成的预览版模型，已开放API</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -563,7 +567,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-15 02:41</t>
+          <t>2026-06-17 02:37</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -571,14 +575,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>openPangu 2.0</t>
+          <t>Qwen-VLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +594,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>开源大模型系列（含语言、视觉、科学计算等）</t>
+          <t>统一视觉语言动作模型</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -598,17 +602,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>盘古大模型全新迭代版本，计划于6月30日起陆续开源核心组件，涵盖NLP、CV、气象、药物发现等多领域专用子模型。</t>
+          <t>首个支持端到端视觉-语言-动作联合建模的通用具身智能基础模型</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -623,7 +627,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-15 02:41</t>
+          <t>2026-06-17 02:37</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -631,48 +635,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PP-OCRv6</t>
+          <t>Project Eden (Preview)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PaddleOCR（百度飞桨）</t>
+          <t>VAST</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>光学字符识别模型</t>
+          <t>多人多智能体世界模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://github.com/PaddlePaddle/PaddleOCR</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>最新版端到端OCR模型，支持超轻量部署、多语言混合识别及复杂版式（如表格、手写、低质图像）鲁棒解析。</t>
+          <t>支持多智能体协同仿真、物理交互与社会规则建模的世界模型预览版</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-15 02:41</t>
+          <t>2026-06-17 02:37</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -695,26 +695,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MineExplorer</t>
+          <t>Mellum2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>美团LongCat团队</t>
+          <t>JetBrains</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>智能体评测基准</t>
+          <t>代码模型</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -722,17 +722,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>首个面向开放世界环境的Agent评测基准，覆盖长程规划、工具调用、环境反馈适应与跨任务泛化能力评估。</t>
+          <t>12B MoE架构低延迟代码补全与推理模型，专为IDE实时交互优化</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-14 02:33</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-15 02:41</t>
+          <t>2026-06-17 02:37</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -755,26 +755,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Holo3.1 系列</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>智谱AI (Z.ai)</t>
+          <t>H Company</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>端侧优化模型</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -782,17 +782,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>旗舰开源大模型，支持1M上下文、High/Max双档思考强度，官方称其为‘迄今能力最强的开源模型’，API及MIT协议开源版本计划下周上线。</t>
+          <t>面向手机/AR眼镜等终端设备的轻量化多模态模型系列，支持本地化智能体运行</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-15 02:42</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -805,32 +805,36 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZCode 3.0.0</t>
+          <t>Ideogram 4.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>智谱AI (Z.ai)</t>
+          <t>Ideogram</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>智能体开发框架</t>
+          <t>文生图模型</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -838,17 +842,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>全新自研Agent内核编程工具，深度适配GLM-5.2，新增分组式任务工作区、Zread智能知识库与可视化Git分支图谱，全面替代第三方Agent框架。</t>
+          <t>9.3B参数开源文生图模型，显著提升文本忠实度与复杂构图能力</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:42</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,20 +865,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZONOS2</t>
+          <t>Reve 2.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zyphra</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -886,25 +894,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>文本到语音（TTS）模型</t>
+          <t>图像生成与编辑模型</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://reve.com</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>开源高质量TTS模型，支持多语种、高保真语音合成，强调低延迟与端侧部署友好性。</t>
+          <t>支持4K分辨率生成与像素级精细化编辑的顶级图像模型</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-15 02:42</t>
+          <t>2026-06-16 02:41</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -917,20 +929,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>GPT-Rosalind (升级版)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -942,7 +958,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>生命科学专用大模型</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -950,12 +966,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>速度提升2.5倍，代码缺陷比上一代减少4倍，代理推理成本降61%</t>
+          <t>面向蛋白质结构预测、基因序列分析与药物分子设计深度优化的GPT系列专业模型</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -973,20 +989,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Grok-Imagine-Video-1.5-Preview</t>
+          <t>Nex-N2-Pro</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Nex-AGI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -998,7 +1018,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>视频生成模型</t>
+          <t>旗舰开源大模型</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1006,12 +1026,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>面向长时序、高保真视频生成的预览版模型，已开放API</t>
+          <t>对标顶级商用模型的开源大语言模型，被证实为Rio 3.5底层技术主干之一</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1029,20 +1049,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qwen-VLA</t>
+          <t>Bernini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>字节跳动</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1054,20 +1078,24 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>统一视觉语言动作模型</t>
+          <t>视频生成编辑统一框架</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://bernini-ai.github.io/</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>首个支持端到端视觉-语言-动作联合建模的通用具身智能基础模型</t>
+          <t>支持生成、剪辑、重绘、运镜控制的一体化开源视频AI框架</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1085,32 +1113,36 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Qwen3.7-Plus</t>
+          <t>Higgs Audio v3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>Boson AI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>多模态智能体模型</t>
+          <t>语音合成模型</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1118,12 +1150,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>面向复杂任务编排与工具调用优化的多模态智能体模型，强化工作流闭环能力</t>
+          <t>多语种TTS模型，支持情感可控、零样本克隆与实时流式合成</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1141,20 +1173,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Project Eden (Preview)</t>
+          <t>Magenta RealTime 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VAST</t>
+          <t>Google Magenta</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1166,20 +1202,24 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>多人多智能体世界模型</t>
+          <t>音乐生成模型</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://github.com/magenta/magenta-realtime</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>支持多智能体协同仿真、物理交互与社会规则建模的世界模型预览版</t>
+          <t>低延迟实时音乐生成模型，支持毫秒级响应与多乐器协同即兴</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1197,20 +1237,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mellum2</t>
+          <t>Nemotron 3.5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JetBrains</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1222,7 +1266,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>代码模型</t>
+          <t>多模态内容安全审核模型</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1230,12 +1274,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12B MoE架构低延迟代码补全与推理模型，专为IDE实时交互优化</t>
+          <t>开源多模态安全模型，支持图文音视频跨模态有害内容识别与细粒度归因</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1253,20 +1297,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Holo3.1 系列</t>
+          <t>dots.tts</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>H Company</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1278,20 +1326,24 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>端侧优化模型</t>
+          <t>端到端TTS模型</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://github.com/rednote-hilab/dots.tts</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>面向手机/AR眼镜等终端设备的轻量化多模态模型系列，支持本地化智能体运行</t>
+          <t>20亿参数开源端到端中文TTS模型，支持高自然度与风格迁移</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1309,20 +1361,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ideogram 4.0</t>
+          <t>Riverflow 2.5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ideogram</t>
+          <t>OpenRouter</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1334,7 +1390,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>文生图模型</t>
+          <t>自定义图像模型</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1342,12 +1398,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.3B参数开源文生图模型，显著提升文本忠实度与复杂构图能力</t>
+          <t>支持用户上传LoRA/ControlNet配置的可定制文生图模型，限时免费开放</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1365,20 +1421,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Reve 2.0</t>
+          <t>MisoTTS 8B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Miso Labs</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1390,7 +1450,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>图像生成与编辑模型</t>
+          <t>情感TTS模型</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1398,12 +1458,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>支持4K分辨率生成与像素级精细化编辑的顶级图像模型</t>
+          <t>8B参数开源情感语音合成模型，支持细粒度情绪强度与角色风格控制</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1421,20 +1481,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GPT-Rosalind (升级版)</t>
+          <t>BLS-Mini-Code-1.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1446,20 +1510,24 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>生命科学专用大模型</t>
+          <t>编程专用模型</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://docs.cohere.com/docs/north-mini-code-1.0</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>面向蛋白质结构预测、基因序列分析与药物分子设计深度优化的GPT系列专业模型</t>
+          <t>早期测试版轻量级编程模型，聚焦Python/TypeScript代码补全与单元测试生成</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1477,20 +1545,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nex-N2-Pro</t>
+          <t>Harness-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nex-AGI</t>
+          <t>高校团队</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1502,7 +1574,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>旗舰开源大模型</t>
+          <t>搜索智能体</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1510,12 +1582,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>对标顶级商用模型的开源大语言模型，被证实为Rio 3.5底层技术主干之一</t>
+          <t>20B高性能开源搜索智能体，支持多跳检索、结果验证与自主信息溯源</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1533,45 +1605,53 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bernini</t>
+          <t>OpenClaw 6.6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>字节跳动</t>
+          <t>OpenClaw社区</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>视频生成编辑统一框架</t>
+          <t>AI智能体框架</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://github.com/openclaw/openclaw</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>支持生成、剪辑、重绘、运镜控制的一体化开源视频AI框架</t>
+          <t>开源智能体框架新版本，实现‘目标→规划→工具调用→自动执行’闭环，支持邮件整理、日程管理等真实工作流</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1589,20 +1669,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Higgs Audio v3</t>
+          <t>Anthropic Claude Fable 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Boson AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1614,7 +1698,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>语音合成模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1622,17 +1706,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>多语种TTS模型，支持情感可控、零样本克隆与实时流式合成</t>
+          <t>Anthropic发布的最强公开模型，发布仅3天后因美国紧急出口管制被全面关停，成为首个被列为‘国家安全资产’而遭强制召回的前沿AI模型。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1651,14 +1735,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Magenta RealTime 2</t>
+          <t>Anthropic Claude Mythos 5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Google Magenta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1670,7 +1754,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>音乐生成模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1678,17 +1762,17 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>低延迟实时音乐生成模型，支持毫秒级响应与多乐器协同即兴</t>
+          <t>与Fable 5同期发布的高推理能力模型，同样于发布三日内被美国政府出口管制令波及，全球服务暂停。</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1707,26 +1791,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nemotron 3.5</t>
+          <t>智谱GLM-5.2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>智谱AI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>多模态内容安全审核模型</t>
+          <t>大语言模型</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1734,17 +1818,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>开源多模态安全模型，支持图文音视频跨模态有害内容识别与细粒度归因</t>
+          <t>全量用户开放的最新版本GLM系列模型，支持多轮复杂推理与长上下文理解，将于下周开源API，作为对Claude Fable 5被禁的国产替代响应。</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1763,14 +1847,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HKGAI V3</t>
+          <t>星源智 ω-EVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>香港HKGAI</t>
+          <t>星源智</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1782,7 +1866,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>本地化智能体大模型</t>
+          <t>具身智能世界模型</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1790,17 +1874,17 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>面向粤语及港澳场景深度优化的智能体模型，强化政务、金融、教育垂直能力</t>
+          <t>业界首个进入‘预演-验证-行动’决策闭环的世界模型，专为机器人物理交互设计，支持后果预判与自我修正。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1819,14 +1903,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gemma 4 12B</t>
+          <t>理想汽车马赫M100具身智能模型</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>理想汽车</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1838,7 +1922,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>轻量多模态模型</t>
+          <t>具身智能模型</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1846,17 +1930,17 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>开源12B参数多模态模型，支持原生音频输入，适配普通终端设备运行</t>
+          <t>面向‘具身智能汽车’场景自研的动态数据流AI模型，融合车控、驾乘交互、生活服务与职业司机辅助能力。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1875,14 +1959,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gemma 4 QAT</t>
+          <t>Rio-3.5-Open-397B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>IplanRIO（巴西里约市政府）</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1894,7 +1978,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>量化模型</t>
+          <t>开源大语言模型（后证实为套壳）</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1902,17 +1986,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Gemma 4系列移动端QAT量化权重，模型压缩至1GB以内</t>
+          <t>宣称由巴西官方发布的拉美首个SOTA级开源大模型，实为阿里通义千问Qwen3.5与Nex N2 Pro权重混合版本，发布24小时内公开致歉并下架。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-16 02:41</t>
+          <t>2026-06-17 02:39</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1927,342 +2011,6 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>dots.tts</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>端到端TTS模型</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>20亿参数开源端到端中文TTS模型，支持高自然度与风格迁移</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Riverflow 2.5</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OpenRouter</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>自定义图像模型</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>支持用户上传LoRA/ControlNet配置的可定制文生图模型，限时免费开放</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MisoTTS 8B</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Miso Labs</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>情感TTS模型</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>8B参数开源情感语音合成模型，支持细粒度情绪强度与角色风格控制</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BLS-Mini-Code-1.0</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Cohere</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>编程专用模型</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>早期测试版轻量级编程模型，聚焦Python/TypeScript代码补全与单元测试生成</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Harness-1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>高校团队</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>搜索智能体</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>20B高性能开源搜索智能体，支持多跳检索、结果验证与自主信息溯源</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>OpenClaw 6.6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OpenClaw社区</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>AI智能体框架</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>开源智能体框架新版本，实现‘目标→规划→工具调用→自动执行’闭环，支持邮件整理、日程管理等真实工作流</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:41</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -839,7 +839,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://ideogram.ai</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>9.3B参数开源文生图模型，显著提升文本忠实度与复杂构图能力</t>
@@ -1147,7 +1151,11 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://boson.ai</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>多语种TTS模型，支持情感可控、零样本克隆与实时流式合成</t>
@@ -1271,7 +1279,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/ai-data-science/generative-ai/nemotron/</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>开源多模态安全模型，支持图文音视频跨模态有害内容识别与细粒度归因</t>
@@ -1395,7 +1407,11 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://openrouter.ai</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>支持用户上传LoRA/ControlNet配置的可定制文生图模型，限时免费开放</t>
@@ -1703,7 +1719,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/news/claude-fable-5-mythos-5</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Anthropic发布的最强公开模型，发布仅3天后因美国紧急出口管制被全面关停，成为首个被列为‘国家安全资产’而遭强制召回的前沿AI模型。</t>
@@ -1759,7 +1779,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/news/claude-fable-5-mythos-5</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>与Fable 5同期发布的高推理能力模型，同样于发布三日内被美国政府出口管制令波及，全球服务暂停。</t>
@@ -1983,7 +2007,11 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/prefeitura-rio/Rio-3.5-Open-397B</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>宣称由巴西官方发布的拉美首个SOTA级开源大模型，实为阿里通义千问Qwen3.5与Nex N2 Pro权重混合版本，发布24小时内公开致歉并下架。</t>
@@ -2011,6 +2039,398 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MiniMax于6月1日发布的旗舰模型，具备原生多模态、150万Token超长上下文及高阶智能体能力，编程评测成绩超越GPT-5.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OpenAI于6月17日推出的GPT系列新版本，显著提升编码效率与智能体工作流能力</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gemini Omni</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>多模态大模型</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>谷歌在Android 17正式版中深度集成的多模态大模型，支持跨模态理解与生成，面向Pixel设备优化部署</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lyria 3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>音乐生成模型</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>谷歌发布的第三代端到端音乐生成模型，支持长时序、风格可控、实时交互式创作，集成于Pixel 10a及Wear OS 7</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>轻量多模态模型</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>开源的12B参数多模态模型，支持原生音频输入，适配普通终端设备运行，大幅降低AI开发门槛</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>京东视觉语言实时交互模型（未命名）</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>视觉语言智能体</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>支持摄像头/直播流/监控流+语音I/O的实时流式交互模型，计划开源权重、数据、训练方法及完整系统</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AI智能体</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>腾讯桌面办公效率智能体，已接入微信支付AI专属卡，支持任务自动化与跨应用协同</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,7 +767,11 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>谷歌I/O 2026推出的极速版模型，专为低延迟智能体服务设计，支撑全天候个人智能体Spark实时响应</t>
@@ -852,6 +856,230 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AstraBrain-WBC 0.5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>银河通用机器人</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>人形机器人通用小脑基础模型</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>全球首个人形机器人通用小脑GPT基础模型，基于2万小时人类动作数据训练，8040万参数，支持全身实时运动控制</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Qwen-RobotWorld</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>具身智能世界模型</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>千问具身智能大模型系列中的世界模型大脑组件，在WorldModelBench评测中总分8.99（开源模型第一），专注物理因果推演与仿真</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HappyOyster 1.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>交互式世界模型</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>面向交互式内容生成的世界模型，支持动态环境建模与多轮具身交互推演</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>个人智能体</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>谷歌I/O发布的全天候主动式个人智能体，重构搜索引擎从被动查询到主动服务范式</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lyria 3</t>
+          <t>AstraBrain-WBC 0.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>银河通用机器人</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>音乐生成模型</t>
+          <t>人形机器人通用小脑基础模型</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -538,17 +538,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>谷歌发布的第三代端到端音乐生成模型，支持长时序、风格可控、实时交互式创作，集成于Pixel 10a及Wear OS 7</t>
+          <t>全球首个人形机器人通用小脑GPT基础模型，基于2万小时人类动作数据训练，8040万参数，支持全身实时运动控制</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-18 02:41</t>
+          <t>2026-06-20 02:12</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-19 02:50</t>
+          <t>2026-06-21 02:35</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -571,14 +571,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>京东视觉语言实时交互模型（未命名）</t>
+          <t>Qwen-RobotWorld</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>视觉语言智能体</t>
+          <t>具身智能世界模型</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -598,17 +598,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>支持摄像头/直播流/监控流+语音I/O的实时流式交互模型，计划开源权重、数据、训练方法及完整系统</t>
+          <t>千问具身智能大模型系列中的世界模型大脑组件，在WorldModelBench评测中总分8.99（开源模型第一），专注物理因果推演与仿真</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-18 02:41</t>
+          <t>2026-06-20 02:12</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-19 02:50</t>
+          <t>2026-06-21 02:35</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -631,14 +631,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>HappyOyster 1.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,25 +650,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>交互式世界模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.happyoyster.cn</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MiniMax于6月1日发布的旗舰原生多模态模型，支持150万Token超长上下文、高阶智能体能力，编程评测成绩超越GPT-5.5</t>
+          <t>面向交互式内容生成的世界模型，支持动态环境建模与多轮具身交互推演</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-19 02:51</t>
+          <t>2026-06-20 02:12</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,20 +685,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GPT-5.6</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google/DeepMind</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -706,7 +714,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>个人智能体</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -714,17 +722,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>OpenAI于2026年6月正式发布的GPT-5.6版本，重点优化编码效率与智能体工作流能力，强化企业级权限管控与语音交互支持</t>
+          <t>谷歌I/O发布的全天候主动式个人智能体，重构搜索引擎从被动查询到主动服务范式</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-19 02:51</t>
+          <t>2026-06-20 02:12</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -737,20 +745,24 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>&gt;&lt;former (v1.0)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>MIT &amp; MIT-IBM Watson AI Lab</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -762,29 +774,25 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>轻量级多模态大语言模型</t>
+          <t>neural network architecture</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>谷歌I/O 2026推出的极速版模型，专为低延迟智能体服务设计，支撑全天候个人智能体Spark实时响应</t>
+          <t>一种颠覆性‘中间瘦两头胖’结构的新型Transformer变体，挑战传统等宽层设计，旨在提升能效比与推理效率。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-19 02:51</t>
+          <t>2026-06-21 02:36</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -803,14 +811,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gemma 4 12B</t>
+          <t>Vera CPU (first-generation)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -822,7 +830,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>开源轻量多模态模型</t>
+          <t>AI-optimized CPU</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -830,17 +838,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>谷歌同步开源的12B参数多模态模型，支持原生音频输入，可在普通终端设备本地运行，显著降低AI开发与部署门槛</t>
+          <t>英伟达首款独立CPU产品线，专为AI智能体时代token级低延迟调度与多智能体协同推理设计，已交付OpenAI和Anthropic首批试用。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-19 02:51</t>
+          <t>2026-06-21 02:36</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -859,14 +867,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AstraBrain-WBC 0.5</t>
+          <t>Mythos (unreleased public version, but newly designated as 'Frontier Model' under US executive order)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>银河通用机器人</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -878,7 +886,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>人形机器人通用小脑基础模型</t>
+          <t>frontier multimodal LLM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -886,17 +894,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>全球首个人形机器人通用小脑GPT基础模型，基于2万小时人类动作数据训练，8040万参数，支持全身实时运动控制</t>
+          <t>虽未正式对外发布新版本，但特朗普6月2日签署行政令明确将Anthropic Mythos列为首批纳入联邦高风险模型评估体系的‘前沿模型’，标志其完成内部迭代并进入监管认定阶段。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-20 02:12</t>
+          <t>2026-06-21 02:36</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -911,174 +919,6 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Qwen-RobotWorld</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>阿里巴巴/通义</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>具身智能世界模型</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>千问具身智能大模型系列中的世界模型大脑组件，在WorldModelBench评测中总分8.99（开源模型第一），专注物理因果推演与仿真</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-06-20 02:12</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HappyOyster 1.0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>阿里巴巴/通义</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>交互式世界模型</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>面向交互式内容生成的世界模型，支持动态环境建模与多轮具身交互推演</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-06-20 02:12</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Spark</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Google/DeepMind</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>个人智能体</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>谷歌I/O发布的全天候主动式个人智能体，重构搜索引擎从被动查询到主动服务范式</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-06-20 02:12</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,7 +835,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://nvidianews.nvidia.com/news/nvidia-announces-next-generation-ai-platform-rubin-vera-and-nvlink-6</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>英伟达首款独立CPU产品线，专为AI智能体时代token级低延迟调度与多智能体协同推理设计，已交付OpenAI和Anthropic首批试用。</t>
@@ -920,6 +924,286 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OpenAI Personal AGI Assistant (v0.1 prototype)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>智能体（Personal AGI Assistant）</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OpenAI发布首个面向个人用户的AGI助手原型愿景，聚焦于日常任务、工作、学习与探索的高能力自主智能体，非开源模型，处于内部研究加速阶段规划中。</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>微信小微（测试版）</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>原生AI智能体</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>腾讯在微信主界面上线小范围灰度测试的原生AI助手‘小微’，支持文字/语音交互操控微信原生功能，融合腾讯自研及优质开源多模型技术栈。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GLM-5.2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>智谱AI正式开源GLM-5.2，为GLM-5系列最新迭代版本，强化长上下文理解、工具调用与多步推理能力，支持1M tokens上下文与结构化输出。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kimi-Max v2026.06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>月之暗面</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>混元T3-Agent</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>智能体框架</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>腾讯混元团队发布轻量化智能体运行时框架T3-Agent，支持低延迟本地化部署、多工具自动编排与微信生态深度协同，面向小程序与企业服务场景开放内测。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AstraBrain-WBC 0.5</t>
+          <t>OpenAI Personal AGI Assistant (v0.1 prototype)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>银河通用机器人</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>人形机器人通用小脑基础模型</t>
+          <t>智能体（Personal AGI Assistant）</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -538,17 +538,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>全球首个人形机器人通用小脑GPT基础模型，基于2万小时人类动作数据训练，8040万参数，支持全身实时运动控制</t>
+          <t>OpenAI发布首个面向个人用户的AGI助手原型愿景，聚焦于日常任务、工作、学习与探索的高能力自主智能体，非开源模型，处于内部研究加速阶段规划中。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-20 02:12</t>
+          <t>2026-06-22 02:40</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-21 02:35</t>
+          <t>2026-06-23 02:05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -571,14 +571,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Qwen-RobotWorld</t>
+          <t>微信小微（测试版）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>腾讯</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>具身智能世界模型</t>
+          <t>原生AI智能体</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -598,17 +598,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>千问具身智能大模型系列中的世界模型大脑组件，在WorldModelBench评测中总分8.99（开源模型第一），专注物理因果推演与仿真</t>
+          <t>腾讯在微信主界面上线小范围灰度测试的原生AI助手‘小微’，支持文字/语音交互操控微信原生功能，融合腾讯自研及优质开源多模型技术栈。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-20 02:12</t>
+          <t>2026-06-22 02:40</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-21 02:35</t>
+          <t>2026-06-23 02:05</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -631,14 +631,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HappyOyster 1.0</t>
+          <t>Kimi-Max v2026.06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>月之暗面</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,29 +650,25 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>交互式世界模型</t>
+          <t>多模态大语言模型</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://www.happyoyster.cn</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>面向交互式内容生成的世界模型，支持动态环境建模与多轮具身交互推演</t>
+          <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-20 02:12</t>
+          <t>2026-06-22 02:40</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -687,7 +683,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-21 02:35</t>
+          <t>2026-06-23 02:05</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -695,26 +691,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>混元T3-Agent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Google/DeepMind</t>
+          <t>腾讯</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>个人智能体</t>
+          <t>智能体框架</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -722,17 +718,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>谷歌I/O发布的全天候主动式个人智能体，重构搜索引擎从被动查询到主动服务范式</t>
+          <t>腾讯混元团队发布轻量化智能体运行时框架T3-Agent，支持低延迟本地化部署、多工具自动编排与微信生态深度协同，面向小程序与企业服务场景开放内测。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-20 02:12</t>
+          <t>2026-06-22 02:40</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -747,462 +743,10 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-21 02:35</t>
+          <t>2026-06-23 02:05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>&gt;&lt;former (v1.0)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MIT &amp; MIT-IBM Watson AI Lab</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>neural network architecture</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>一种颠覆性‘中间瘦两头胖’结构的新型Transformer变体，挑战传统等宽层设计，旨在提升能效比与推理效率。</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-06-21 02:36</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Vera CPU (first-generation)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AI-optimized CPU</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://nvidianews.nvidia.com/news/nvidia-announces-next-generation-ai-platform-rubin-vera-and-nvlink-6</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>英伟达首款独立CPU产品线，专为AI智能体时代token级低延迟调度与多智能体协同推理设计，已交付OpenAI和Anthropic首批试用。</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-06-21 02:36</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mythos (unreleased public version, but newly designated as 'Frontier Model' under US executive order)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>frontier multimodal LLM</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>虽未正式对外发布新版本，但特朗普6月2日签署行政令明确将Anthropic Mythos列为首批纳入联邦高风险模型评估体系的‘前沿模型’，标志其完成内部迭代并进入监管认定阶段。</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-06-21 02:36</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OpenAI Personal AGI Assistant (v0.1 prototype)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>智能体（Personal AGI Assistant）</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>OpenAI发布首个面向个人用户的AGI助手原型愿景，聚焦于日常任务、工作、学习与探索的高能力自主智能体，非开源模型，处于内部研究加速阶段规划中。</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:40</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>微信小微（测试版）</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>腾讯</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>原生AI智能体</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>腾讯在微信主界面上线小范围灰度测试的原生AI助手‘小微’，支持文字/语音交互操控微信原生功能，融合腾讯自研及优质开源多模型技术栈。</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:40</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GLM-5.2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>智谱AI</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>大语言模型</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>智谱AI正式开源GLM-5.2，为GLM-5系列最新迭代版本，强化长上下文理解、工具调用与多步推理能力，支持1M tokens上下文与结构化输出。</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:40</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Kimi-Max v2026.06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>月之暗面</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>多模态大语言模型</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:40</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>混元T3-Agent</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>腾讯</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>智能体框架</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>腾讯混元团队发布轻量化智能体运行时框架T3-Agent，支持低延迟本地化部署、多工具自动编排与微信生态深度协同，面向小程序与企业服务场景开放内测。</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:40</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://kimi.moonshot.cn/</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
@@ -747,6 +751,174 @@
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stellaris-VL 0.8B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>极视角</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>视觉语言大模型（端侧轻量多模态）</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>面向端侧与嵌入式设备的0.8B参数星际视觉语言大模型，支持高性能实时多模态理解与生成。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UnisonMind</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>一念科技（清华团队）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>具身智能体/实时多模态世界模型</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>首个支持流式推理、全模态输入输出、端侧部署的统一具身智能大脑，已实机部署于机器狗、轮椅及服务机器人并完成复杂长程任务验证。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fugu Ultra</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sakana</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>多智能体编排系统（非单体模型，但属新型AI智能体架构）</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>面向大模型访问中断场景设计的开源多智能体调度与编排系统，支持跨供应商模型路由、动态负载均衡与任务分解，解决前沿模型可用性瓶颈。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OpenAI Personal AGI Assistant (v0.1 prototype)</t>
+          <t>Stellaris-VL 0.8B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>极视角</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>智能体（Personal AGI Assistant）</t>
+          <t>视觉语言大模型（端侧轻量多模态）</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -538,17 +538,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OpenAI发布首个面向个人用户的AGI助手原型愿景，聚焦于日常任务、工作、学习与探索的高能力自主智能体，非开源模型，处于内部研究加速阶段规划中。</t>
+          <t>面向端侧与嵌入式设备的0.8B参数星际视觉语言大模型，支持高性能实时多模态理解与生成。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-22 02:40</t>
+          <t>2026-06-24 02:08</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-23 02:05</t>
+          <t>2026-06-25 02:07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -571,26 +571,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>微信小微（测试版）</t>
+          <t>UnisonMind</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>腾讯</t>
+          <t>一念科技（清华团队）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>原生AI智能体</t>
+          <t>具身智能体/实时多模态世界模型</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -598,17 +598,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>腾讯在微信主界面上线小范围灰度测试的原生AI助手‘小微’，支持文字/语音交互操控微信原生功能，融合腾讯自研及优质开源多模型技术栈。</t>
+          <t>首个支持流式推理、全模态输入输出、端侧部署的统一具身智能大脑，已实机部署于机器狗、轮椅及服务机器人并完成复杂长程任务验证。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-22 02:40</t>
+          <t>2026-06-24 02:08</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-23 02:05</t>
+          <t>2026-06-25 02:07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -631,48 +631,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kimi-Max v2026.06</t>
+          <t>Fugu Ultra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>月之暗面</t>
+          <t>Sakana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多模态大语言模型</t>
+          <t>多智能体编排系统（非单体模型，但属新型AI智能体架构）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://kimi.moonshot.cn/</t>
+          <t>https://sakana.ai/fugu</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
+          <t>面向大模型访问中断场景设计的开源多智能体调度与编排系统，支持跨供应商模型路由、动态负载均衡与任务分解，解决前沿模型可用性瓶颈。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-22 02:40</t>
+          <t>2026-06-24 02:08</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-23 02:05</t>
+          <t>2026-06-25 02:07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -695,26 +695,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>混元T3-Agent</t>
+          <t>鲁班超级智能体（v1.0）</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>腾讯</t>
+          <t>新大陆数字技术</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>智能体框架</t>
+          <t>智能体</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -722,17 +722,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>腾讯混元团队发布轻量化智能体运行时框架T3-Agent，支持低延迟本地化部署、多工具自动编排与微信生态深度协同，面向小程序与企业服务场景开放内测。</t>
+          <t>面向商户全场景经营的AI超级智能体，深度融合Claw互联调度与Hermes智能进化架构，首发36项专属技能，已接入星驿付及慧徕店SaaS体系。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-22 02:40</t>
+          <t>2026-06-25 02:08</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -745,24 +745,20 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-06-23 02:05</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Stellaris-VL 0.8B</t>
+          <t>ava数字员工矩阵（含ava me+、avavox、ava app）</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>极视角</t>
+          <t>神州泰岳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -774,7 +770,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>视觉语言大模型（端侧轻量多模态）</t>
+          <t>智能体/数字员工平台</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -782,17 +778,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>面向端侧与嵌入式设备的0.8B参数星际视觉语言大模型，支持高性能实时多模态理解与生成。</t>
+          <t>在MWC上海正式发布的轻量化企业级数字员工产品矩阵，支持角色化、长期记忆、多Agent协作与统一治理，标志从AI Agent向数字员工范式跃迁。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-24 02:08</t>
+          <t>2026-06-25 02:08</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -807,118 +803,6 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>UnisonMind</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>一念科技（清华团队）</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>具身智能体/实时多模态世界模型</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>首个支持流式推理、全模态输入输出、端侧部署的统一具身智能大脑，已实机部署于机器狗、轮椅及服务机器人并完成复杂长程任务验证。</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-06-24 02:08</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fugu Ultra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sakana</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>多智能体编排系统（非单体模型，但属新型AI智能体架构）</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>面向大模型访问中断场景设计的开源多智能体调度与编排系统，支持跨供应商模型路由、动态负载均衡与任务分解，解决前沿模型可用性瓶颈。</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-06-24 02:08</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,59 +511,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stellaris-VL 0.8B</t>
+          <t>Qwen3-ForcedAligner-0.6B-hf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>极视角</t>
+          <t>阿里</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.6B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>视觉语言大模型（端侧轻量多模态）</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/Qwen/Qwen3-ForcedAligner-0.6B-hf</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>面向端侧与嵌入式设备的0.8B参数星际视觉语言大模型，支持高性能实时多模态理解与生成。</t>
+          <t>HuggingFace token-classification</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-24 02:08</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ForcedAligner-0.6B-hf)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07</t>
+          <t>2026-06-27 02:04</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -571,59 +583,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UnisonMind</t>
+          <t>Qwen3-ASR-0.6B-hf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>一念科技（清华团队）</t>
+          <t>阿里</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6B</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>具身智能体/实时多模态世界模型</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/Qwen/Qwen3-ASR-0.6B-hf</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>首个支持流式推理、全模态输入输出、端侧部署的统一具身智能大脑，已实机部署于机器狗、轮椅及服务机器人并完成复杂长程任务验证。</t>
+          <t>HuggingFace automatic-speech-recognition</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:08</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-0.6B-hf)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07</t>
+          <t>2026-06-27 02:04</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -631,63 +655,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fugu Ultra</t>
+          <t>Qwen3-ASR-1.7B-hf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sakana</t>
+          <t>阿里</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.7B</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>多智能体编排系统（非单体模型，但属新型AI智能体架构）</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://sakana.ai/fugu</t>
+          <t>https://huggingface.co/Qwen/Qwen3-ASR-1.7B-hf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>面向大模型访问中断场景设计的开源多智能体调度与编排系统，支持跨供应商模型路由、动态负载均衡与任务分解，解决前沿模型可用性瓶颈。</t>
+          <t>HuggingFace automatic-speech-recognition</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-24 02:08</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-1.7B-hf)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07</t>
+          <t>2026-06-27 02:04</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -695,14 +727,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>鲁班超级智能体（v1.0）</t>
+          <t>c-fast-foundationstereo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新大陆数字技术</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,99 +742,55 @@
           <t>国外</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>智能体</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/c-fast-foundationstereo</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>面向商户全场景经营的AI超级智能体，深度融合Claw互联调度与Hermes智能进化架构，首发36项专属技能，已接入星驿付及慧徕店SaaS体系。</t>
+          <t>HuggingFace depth-estimation</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-25 02:08</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/c-fast-foundationstereo)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-27 02:04</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ava数字员工矩阵（含ava me+、avavox、ava app）</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>神州泰岳</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>智能体/数字员工平台</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>在MWC上海正式发布的轻量化企业级数字员工产品矩阵，支持角色化、长期记忆、多Agent协作与统一治理，标志从AI Agent向数字员工范式跃迁。</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-06-25 02:08</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qwen3-ForcedAligner-0.6B-hf</t>
+          <t>DeepSeek-V4-Pro-DSpark</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>阿里</t>
+          <t>深度求索</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,11 +531,7 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.6B</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>基座</t>
@@ -543,39 +539,39 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Qwen/Qwen3-ForcedAligner-0.6B-hf</t>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Pro-DSpark</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace token-classification</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ForcedAligner-0.6B-hf)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Pro-DSpark)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-27 02:04</t>
+          <t>2026-06-28 02:15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -583,14 +579,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Qwen3-ASR-0.6B-hf</t>
+          <t>DeepSeek-V4-Flash-DSpark</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>阿里</t>
+          <t>深度求索</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -603,11 +599,7 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.6B</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>基座</t>
@@ -615,182 +607,42 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Qwen/Qwen3-ASR-0.6B-hf</t>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-DSpark</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace automatic-speech-recognition</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-0.6B-hf)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-DSpark)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-27 02:04</t>
+          <t>2026-06-28 02:15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Qwen3-ASR-1.7B-hf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.7B</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/Qwen/Qwen3-ASR-1.7B-hf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HuggingFace automatic-speech-recognition</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-1.7B-hf)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-06-27 02:04</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>c-fast-foundationstereo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/c-fast-foundationstereo</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>HuggingFace depth-estimation</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/c-fast-foundationstereo)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-06-27 02:04</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DeepSeek-V4-Pro-DSpark</t>
+          <t>eagle3_gemma4_12b_ttt7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -539,39 +539,39 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>non-thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Pro-DSpark</t>
+          <t>https://huggingface.co/deepseek-ai/eagle3_gemma4_12b_ttt7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Pro-DSpark)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_gemma4_12b_ttt7)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-28 02:15</t>
+          <t>2026-06-29 02:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DeepSeek-V4-Flash-DSpark</t>
+          <t>eagle3_qwen3_14b_ttt7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -607,42 +607,722 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>non-thinking</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-DSpark</t>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_14b_ttt7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-DSpark)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_14b_ttt7)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-28 02:15</t>
+          <t>2026-06-29 02:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eagle3_qwen3_8b_ttt7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_8b_ttt7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_8b_ttt7)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eagle3_qwen3_4b_ttt7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_4b_ttt7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_4b_ttt7)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dflash_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_gemma4_12b_block7)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_14b_block7)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_8b_block7)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_4b_block7)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dspark_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_gemma4_12b_block7)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_14b_block7)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_8b_block7)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_4b_block7)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5</t>
+          <t>HARC-Qwen2.5-7B-Instruct</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,58 +528,54 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/claude-sonnet-5</t>
+          <t>https://huggingface.co/microsoft/HARC-Qwen2.5-7B-Instruct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1000k上下文；顶级编码能力</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Qwen2.5-7B-Instruct)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-01 02:13</t>
+          <t>2026-07-03 01:50</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -587,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GELab-Zero-4B-preview-Sico-Evolution</t>
+          <t>HARC-Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -609,12 +605,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,33 +621,33 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/GELab-Zero-4B-preview-Sico-Evolution</t>
+          <t>https://huggingface.co/microsoft/HARC-Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace image-text-to-text</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/GELab-Zero-4B-preview-Sico-Evolution)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Llama-3.1-8B-Instruct)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-01 02:13</t>
+          <t>2026-07-03 01:50</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HARC-Qwen2.5-7B-Instruct</t>
+          <t>gr00t17-lerobot-libero_goal-640</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,14 +531,10 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -549,33 +545,33 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/HARC-Qwen2.5-7B-Instruct</t>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_goal-640</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>HuggingFace robotics</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Qwen2.5-7B-Instruct)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_goal-640)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-03 01:50</t>
+          <t>2026-07-06 02:02</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -583,14 +579,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HARC-Llama-3.1-8B-Instruct</t>
+          <t>gr00t17-lerobot-libero_10-640</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -603,14 +599,10 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -621,36 +613,172 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/HARC-Llama-3.1-8B-Instruct</t>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_10-640</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>HuggingFace robotics</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Llama-3.1-8B-Instruct)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_10-640)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-03 01:50</t>
+          <t>2026-07-06 02:02</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_object-640</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_object-640</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_object-640)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_spatial-640</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_spatial-640</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_spatial-640)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gr00t17-lerobot-libero_goal-640</t>
+          <t>CWIP-1.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -545,240 +545,36 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_goal-640</t>
+          <t>https://huggingface.co/nvidia/CWIP-1.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace robotics</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_goal-640)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/CWIP-1.0)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-06 02:02</t>
+          <t>2026-07-08 01:27</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gr00t17-lerobot-libero_10-640</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_10-640</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>HuggingFace robotics</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_10-640)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-07-06 02:02</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gr00t17-lerobot-libero_object-640</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_object-640</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HuggingFace robotics</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_object-640)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-07-06 02:02</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gr00t17-lerobot-libero_spatial-640</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_spatial-640</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>HuggingFace robotics</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_spatial-640)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-07-06 02:02</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CWIP-1.0</t>
+          <t>nvDock</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -545,7 +545,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/CWIP-1.0</t>
+          <t>https://huggingface.co/nvidia/nvDock</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -555,23 +555,23 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/CWIP-1.0)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/nvDock)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-08 01:27</t>
+          <t>2026-07-09 01:49</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nvDock</t>
+          <t>Nemotron-3-Embed-1B-NVFP4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -531,21 +531,25 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/nvDock</t>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-NVFP4</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -555,26 +559,170 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/nvDock)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-NVFP4)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-09 01:49</t>
+          <t>2026-07-15 01:16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nemotron-3-Embed-8B-BF16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-8B-BF16</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HuggingFace sentence-similarity</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-8B-BF16)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-07-15 01:16</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nemotron-3-Embed-1B-BF16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-BF16</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace sentence-similarity</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-BF16)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-07-15 01:16</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nemotron-3-Embed-1B-NVFP4</t>
+          <t>bitnet-embedding-0.6b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,23 +533,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>0.6B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>non-thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-NVFP4</t>
+          <t>https://huggingface.co/microsoft/bitnet-embedding-0.6b</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -559,23 +559,23 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-NVFP4)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-0.6b)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-15 01:16</t>
+          <t>2026-07-16 01:26</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -583,14 +583,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nemotron-3-Embed-8B-BF16</t>
+          <t>bitnet-embedding-270m</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -605,124 +605,52 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>270M</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>thinking</t>
+          <t>non-thinking</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-8B-BF16</t>
+          <t>https://huggingface.co/microsoft/bitnet-embedding-270m</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace sentence-similarity</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-8B-BF16)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-270m)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-15 01:16</t>
+          <t>2026-07-16 01:26</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nemotron-3-Embed-1B-BF16</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-BF16</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HuggingFace sentence-similarity</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-BF16)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-07-15 01:16</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bitnet-embedding-0.6b</t>
+          <t>Gemini 3.5 Flash Cyber</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,17 +528,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.6B</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -546,36 +542,44 @@
           <t>non-thinking</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/bitnet-embedding-0.6b</t>
+          <t>https://llm-stats.com/models/gemini-3.5-flash-cyber</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>针对网络安全用途；协助发现、验证及修补软件漏洞；仅向政府及受信任合作伙伴开放</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-0.6b)</t>
+          <t>llm-stats.com 排行榜</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-16 01:26</t>
+          <t>2026-07-22 01:25</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -583,14 +587,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bitnet-embedding-270m</t>
+          <t>Gemini 3.5 Flash-Lite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,17 +604,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>270M</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -618,39 +618,123 @@
           <t>non-thinking</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/bitnet-embedding-270m</t>
+          <t>https://llm-stats.com/models/gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>1048k上下文</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-270m)</t>
+          <t>llm-stats.com 排行榜</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-16 01:26</t>
+          <t>2026-07-22 01:25</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gemini 3.6 Flash</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.6-flash</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1048k上下文</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-07-22 01:25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash Cyber</t>
+          <t>Claude Opus 5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,12 +534,12 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -549,22 +549,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/gemini-3.5-flash-cyber</t>
+          <t>https://llm-stats.com/models/claude-opus-5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>针对网络安全用途；协助发现、验证及修补软件漏洞；仅向政府及受信任合作伙伴开放</t>
+          <t>1000k上下文；高端定价</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-22 01:25</t>
+          <t>2026-07-25 01:29</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -587,14 +587,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash-Lite</t>
+          <t>VibeVoice-ASR-BitNet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,13 +604,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>闭源</t>
+          <t>开源</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -618,123 +618,39 @@
           <t>non-thinking</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/gemini-3.5-flash-lite</t>
+          <t>https://huggingface.co/microsoft/VibeVoice-ASR-BitNet</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1048k上下文</t>
+          <t>HuggingFace automatic-speech-recognition</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/VibeVoice-ASR-BitNet)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-22 01:25</t>
+          <t>2026-07-25 01:29</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gemini 3.6 Flash</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1048k上下文</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>llm-stats.com 排行榜</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:25</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Opus 5</t>
+          <t>Mage-ViT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,129 +528,53 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>闭源</t>
+          <t>开源</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/claude-opus-5</t>
+          <t>https://huggingface.co/microsoft/Mage-ViT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1000k上下文；高端定价</t>
+          <t>HuggingFace image-feature-extraction</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/Mage-ViT)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-25 01:29</t>
+          <t>2026-07-27 01:50</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>VibeVoice-ASR-BitNet</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>微软</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/microsoft/VibeVoice-ASR-BitNet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>HuggingFace automatic-speech-recognition</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/VibeVoice-ASR-BitNet)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-07-25 01:29</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mage-ViT</t>
+          <t>K-EXAONE-2.0-750B-A37B-DSpark</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,7 +531,11 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>未知</t>
@@ -545,36 +549,180 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/microsoft/Mage-ViT</t>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-DSpark</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace image-feature-extraction</t>
+          <t>HuggingFace text-generation</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(微软/Mage-ViT)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-DSpark)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-27 01:50</t>
+          <t>2026-07-31 01:45</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>K-EXAONE-2.0-750B-A37B-NVFP4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-NVFP4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-NVFP4)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K-EXAONE-2.0-750B-A37B-FP8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-FP8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-FP8)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,19 +511,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K-EXAONE-2.0-750B-A37B-DSpark</t>
+          <t>DeepSeek-V4-Flash-0731</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>深度求索</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -531,25 +531,21 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>750B(A37B)</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-DSpark</t>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-0731</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -559,170 +555,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-DSpark)</t>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-0731)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45</t>
+          <t>2026-08-01 01:46</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>K-EXAONE-2.0-750B-A37B-NVFP4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>750B(A37B)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-NVFP4</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-NVFP4)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-07-31 01:45</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K-EXAONE-2.0-750B-A37B-FP8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>750B(A37B)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>non-thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-FP8</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-FP8)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-07-31 01:45</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -511,19 +511,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DeepSeek-V4-Flash-0731</t>
+          <t>Nemotron 3.5 Lightning (30B A3B)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>深度求索</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -531,7 +531,11 @@
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30B</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>基座</t>
@@ -542,36 +546,44 @@
           <t>thinking</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-0731</t>
+          <t>https://llm-stats.com/models/nemotron-3.5-lightning-30b-a3b</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HuggingFace text-generation</t>
+          <t>MoE架构；30B参数；262k上下文；低成本；Openmdw</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-0731)</t>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(nvidia/Nemotron 3.5 Lightning (30B A3B))</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-01 01:46</t>
+          <t>2026-08-12 00:58</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nemotron 3.5 Lightning (30B A3B)</t>
+          <t>Grok 4.6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,65 +528,141 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/grok-4.6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>500k上下文</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-08-13 01:00</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LFM2.5-VL-3B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Liquid AI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>开源</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30B</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>通用对话</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/nemotron-3.5-lightning-30b-a3b</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MoE架构；30B参数；262k上下文；低成本；Openmdw</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/lfm-2.5-vl-3b</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Lfm1 0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(nvidia/Nemotron 3.5 Lightning (30B A3B))</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-08-12 00:58</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(liquid-ai/LFM2.5-VL-3B)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-13 01:00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -511,30 +511,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Grok 4.6</t>
+          <t>DeepSeek-V4-Pro-0813</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2T</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -549,22 +553,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/grok-4.6</t>
+          <t>https://llm-stats.com/models/deepseek-v4-pro-0813</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>500k上下文</t>
+          <t>MoE架构；2T参数；1048k上下文；MIT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -574,12 +578,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜</t>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(deepseek/DeepSeek-V4-Pro-0813)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-13 01:00</t>
+          <t>2026-08-14 00:59</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -587,14 +591,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LFM2.5-VL-3B</t>
+          <t>Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Liquid AI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,14 +608,10 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>多模态</t>
@@ -619,7 +619,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>non-thinking</t>
+          <t>thinking</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/lfm-2.5-vl-3b</t>
+          <t>https://llm-stats.com/models/gemini-3.7-flash</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Lfm1 0</t>
+          <t>1048k上下文</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(liquid-ai/LFM2.5-VL-3B)</t>
+          <t>llm-stats.com 排行榜</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-13 01:00</t>
+          <t>2026-08-14 00:59</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DeepSeek-V4-Pro-0813</t>
+          <t>Qwen3.8-27B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba Cloud / Qwen Team</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,12 +533,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2T</t>
+          <t>28B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -553,22 +553,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/deepseek-v4-pro-0813</t>
+          <t>https://llm-stats.com/models/qwen3.8-27b</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MoE架构；2T参数；1048k上下文；MIT</t>
+          <t>强推理能力；Apache 2.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(deepseek/DeepSeek-V4-Pro-0813)</t>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(alibaba-cloud-/Qwen3.8-27B)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-14 00:59</t>
+          <t>2026-08-15 00:34</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -591,78 +591,422 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Zhipu AI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>753B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/glm-5.3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MoE架构；753B参数；Unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Chat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>国外</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>多模态</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>thinking</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/gemini-3.7-flash</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1048k上下文</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Chat</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>llm-stats.com 排行榜</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:59</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Chat)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-STEM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-STEM</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-STEM)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models-Updated.xlsx
+++ b/Model_Navigate/data/Object-Models-Updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,14 +511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qwen3.8-27B</t>
+          <t>DeepSeek-V4-Flash-Vision-Exp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alibaba Cloud / Qwen Team</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,14 +528,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>28B</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>多模态</t>
@@ -553,22 +549,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/qwen3.8-27b</t>
+          <t>https://llm-stats.com/models/deepseek-v4-flash-vision-exp</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>强推理能力；Apache 2.0</t>
+          <t>1048k上下文；低成本；Unknown</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -578,435 +574,15 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录(alibaba-cloud-/Qwen3.8-27B)</t>
+          <t>llm-stats.com 排行榜</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-15 00:34</t>
+          <t>2026-08-22 00:34</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GLM-5.3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Zhipu AI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>闭源</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>753B</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>通用对话</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://llm-stats.com/models/glm-5.3</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MoE架构；753B参数；Unknown</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>llm-stats.com 排行榜</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NVIDIA-Nemotron-Labs-Teacher-Chat</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Chat</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Chat)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning)</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NVIDIA-Nemotron-Labs-Teacher-STEM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>基座</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>thinking</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-STEM</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>HuggingFace text-generation</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-STEM)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-08-15 00:34</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
